--- a/backlinks.xlsx
+++ b/backlinks.xlsx
@@ -5513,7 +5513,11 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G153" s="4" t="inlineStr"/>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="H153" s="4" t="inlineStr"/>
       <c r="I153" s="4" t="inlineStr"/>
     </row>
@@ -5575,7 +5579,11 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G155" s="4" t="inlineStr"/>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="H155" s="4" t="inlineStr"/>
       <c r="I155" s="4" t="inlineStr"/>
     </row>
@@ -5637,7 +5645,11 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G157" s="4" t="inlineStr"/>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
@@ -5703,7 +5715,11 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G159" s="4" t="inlineStr"/>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="H159" s="4" t="inlineStr"/>
       <c r="I159" s="4" t="inlineStr"/>
     </row>

--- a/backlinks.xlsx
+++ b/backlinks.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>有表单</t>
+          <t>失败</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -813,9 +813,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>待审核</t>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>需验证码</t>
+          <t>失败</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1066,19 +1066,19 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
     </row>
@@ -1144,19 +1144,19 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
     </row>
@@ -1187,19 +1187,19 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
     </row>
@@ -1991,19 +1991,19 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
     </row>
@@ -2034,19 +2034,19 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
     </row>
@@ -2120,19 +2120,19 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
     </row>
@@ -2163,19 +2163,19 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
     </row>
@@ -2276,19 +2276,19 @@
           <t>multi</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
     </row>
@@ -2319,19 +2319,19 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
     </row>
@@ -5513,11 +5513,7 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G153" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
+      <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr"/>
       <c r="I153" s="4" t="inlineStr"/>
     </row>
@@ -5579,11 +5575,7 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
+      <c r="G155" s="4" t="inlineStr"/>
       <c r="H155" s="4" t="inlineStr"/>
       <c r="I155" s="4" t="inlineStr"/>
     </row>
@@ -5645,16 +5637,8 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>需付费</t>
-        </is>
-      </c>
+      <c r="G157" s="4" t="inlineStr"/>
+      <c r="H157" s="4" t="inlineStr"/>
       <c r="I157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
@@ -5715,11 +5699,7 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G159" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
+      <c r="G159" s="4" t="inlineStr"/>
       <c r="H159" s="4" t="inlineStr"/>
       <c r="I159" s="4" t="inlineStr"/>
     </row>
@@ -8044,11 +8024,7 @@
         </is>
       </c>
       <c r="G243" s="4" t="inlineStr"/>
-      <c r="H243" s="4" t="inlineStr">
-        <is>
-          <t>垃圾网站</t>
-        </is>
-      </c>
+      <c r="H243" s="4" t="inlineStr"/>
       <c r="I243" s="4" t="inlineStr"/>
     </row>
     <row r="244">

--- a/backlinks.xlsx
+++ b/backlinks.xlsx
@@ -73,13 +73,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L523"/>
+  <dimension ref="A1:I523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -496,27 +496,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>extractkeywords.com</t>
+          <t>heicpdf</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>heicpdf</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>heicpdf.to</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
           <t>tryschedule</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tryschedule.com</t>
         </is>
       </c>
     </row>
@@ -551,20 +536,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>需登录</t>
+        </is>
+      </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>需登录</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr">
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -601,20 +583,17 @@
           <t>multi</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -647,20 +626,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -689,12 +665,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -723,20 +696,17 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -769,16 +739,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -811,16 +778,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -849,20 +813,17 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -895,16 +856,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -933,20 +891,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -975,16 +930,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1013,16 +965,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1051,16 +1000,13 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1089,16 +1035,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1127,20 +1070,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1173,16 +1113,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1211,20 +1148,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1257,20 +1191,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1303,12 +1234,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1337,16 +1265,13 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1375,16 +1300,13 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1413,16 +1335,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1451,16 +1370,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1489,16 +1405,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1527,16 +1440,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1565,12 +1475,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1599,12 +1506,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1633,12 +1537,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1667,20 +1568,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -1713,12 +1611,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1747,20 +1642,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -1793,12 +1685,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1827,12 +1716,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1861,12 +1747,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1895,12 +1778,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1929,12 +1809,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1963,12 +1840,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1997,12 +1871,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2031,12 +1902,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2065,12 +1933,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2099,12 +1964,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2133,20 +1995,17 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2179,20 +2038,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2225,20 +2081,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -2271,20 +2124,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2317,20 +2167,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2363,16 +2210,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2401,16 +2245,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2439,20 +2280,17 @@
           <t>multi</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="4" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2485,20 +2323,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="4" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2531,20 +2366,17 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -2577,16 +2409,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2615,16 +2444,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2653,12 +2479,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2687,12 +2510,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2721,12 +2541,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2755,12 +2572,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2789,12 +2603,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2823,12 +2634,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2857,12 +2665,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2891,12 +2696,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2925,12 +2727,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2959,12 +2758,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2993,12 +2789,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3027,12 +2820,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3061,12 +2851,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3095,12 +2882,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3129,12 +2913,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+      <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3163,12 +2944,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3197,12 +2975,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
+      <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3231,12 +3006,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3265,12 +3037,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3299,12 +3068,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr"/>
+      <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3333,12 +3099,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr"/>
+      <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3367,12 +3130,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr"/>
+      <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3401,12 +3161,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr"/>
+      <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3435,12 +3192,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr"/>
+      <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3469,12 +3223,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr"/>
+      <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3503,12 +3254,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr"/>
+      <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3537,12 +3285,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr"/>
+      <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3571,12 +3316,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr"/>
+      <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3605,12 +3347,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr"/>
+      <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3639,12 +3378,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3673,12 +3409,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr"/>
+      <c r="G85" s="4" t="inlineStr"/>
+      <c r="H85" s="4" t="inlineStr"/>
+      <c r="I85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3707,12 +3440,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3741,12 +3471,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3775,12 +3502,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr"/>
+      <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3809,12 +3533,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3843,12 +3564,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr"/>
+      <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3877,12 +3595,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3911,12 +3626,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr"/>
+      <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3945,12 +3657,9 @@
           <t>multi</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr"/>
+      <c r="G93" s="4" t="inlineStr"/>
+      <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3979,12 +3688,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4013,12 +3719,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr"/>
+      <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4047,12 +3750,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4081,12 +3781,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr"/>
+      <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4115,12 +3812,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4149,12 +3843,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr"/>
+      <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4183,12 +3874,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4217,12 +3905,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr"/>
+      <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4251,12 +3936,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4285,12 +3967,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
+      <c r="G103" s="4" t="inlineStr"/>
+      <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4319,12 +3998,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr"/>
+      <c r="G104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4353,12 +4029,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr"/>
+      <c r="G105" s="4" t="inlineStr"/>
+      <c r="H105" s="4" t="inlineStr"/>
+      <c r="I105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4387,12 +4060,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4421,12 +4091,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr"/>
+      <c r="G107" s="4" t="inlineStr"/>
+      <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4455,12 +4122,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
+      <c r="G108" s="4" t="inlineStr"/>
+      <c r="H108" s="4" t="inlineStr"/>
+      <c r="I108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4489,12 +4153,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr"/>
+      <c r="G109" s="4" t="inlineStr"/>
+      <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4523,12 +4184,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr"/>
+      <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4557,12 +4215,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-      <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr"/>
+      <c r="H111" s="4" t="inlineStr"/>
+      <c r="I111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4591,12 +4246,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-      <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="2" t="inlineStr"/>
+      <c r="G112" s="4" t="inlineStr"/>
+      <c r="H112" s="4" t="inlineStr"/>
+      <c r="I112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4625,12 +4277,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-      <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="inlineStr"/>
+      <c r="G113" s="4" t="inlineStr"/>
+      <c r="H113" s="4" t="inlineStr"/>
+      <c r="I113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4659,12 +4308,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="inlineStr"/>
+      <c r="G114" s="4" t="inlineStr"/>
+      <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4693,12 +4339,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-      <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="2" t="inlineStr"/>
+      <c r="G115" s="4" t="inlineStr"/>
+      <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4727,12 +4370,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr"/>
+      <c r="G116" s="4" t="inlineStr"/>
+      <c r="H116" s="4" t="inlineStr"/>
+      <c r="I116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4761,12 +4401,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-      <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="inlineStr"/>
+      <c r="G117" s="4" t="inlineStr"/>
+      <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4795,12 +4432,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
+      <c r="G118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr"/>
+      <c r="I118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4829,12 +4463,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr"/>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-      <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="2" t="inlineStr"/>
+      <c r="G119" s="4" t="inlineStr"/>
+      <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4863,12 +4494,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="inlineStr"/>
+      <c r="G120" s="4" t="inlineStr"/>
+      <c r="H120" s="4" t="inlineStr"/>
+      <c r="I120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4897,12 +4525,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-      <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="2" t="inlineStr"/>
+      <c r="G121" s="4" t="inlineStr"/>
+      <c r="H121" s="4" t="inlineStr"/>
+      <c r="I121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4931,12 +4556,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr"/>
+      <c r="G122" s="4" t="inlineStr"/>
+      <c r="H122" s="4" t="inlineStr"/>
+      <c r="I122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4965,12 +4587,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-      <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="2" t="inlineStr"/>
+      <c r="G123" s="4" t="inlineStr"/>
+      <c r="H123" s="4" t="inlineStr"/>
+      <c r="I123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4999,12 +4618,9 @@
           <t>multi</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr"/>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr"/>
+      <c r="G124" s="4" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5033,12 +4649,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-      <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="2" t="inlineStr"/>
+      <c r="G125" s="4" t="inlineStr"/>
+      <c r="H125" s="4" t="inlineStr"/>
+      <c r="I125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5067,12 +4680,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr"/>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-      <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="inlineStr"/>
+      <c r="G126" s="4" t="inlineStr"/>
+      <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5101,12 +4711,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr"/>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-      <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="2" t="inlineStr"/>
+      <c r="G127" s="4" t="inlineStr"/>
+      <c r="H127" s="4" t="inlineStr"/>
+      <c r="I127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5135,12 +4742,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-      <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="inlineStr"/>
+      <c r="G128" s="4" t="inlineStr"/>
+      <c r="H128" s="4" t="inlineStr"/>
+      <c r="I128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5169,12 +4773,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-      <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="2" t="inlineStr"/>
+      <c r="G129" s="4" t="inlineStr"/>
+      <c r="H129" s="4" t="inlineStr"/>
+      <c r="I129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5203,12 +4804,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-      <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="inlineStr"/>
+      <c r="G130" s="4" t="inlineStr"/>
+      <c r="H130" s="4" t="inlineStr"/>
+      <c r="I130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5237,12 +4835,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-      <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="inlineStr"/>
+      <c r="G131" s="4" t="inlineStr"/>
+      <c r="H131" s="4" t="inlineStr"/>
+      <c r="I131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5271,12 +4866,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr"/>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-      <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="inlineStr"/>
+      <c r="G132" s="4" t="inlineStr"/>
+      <c r="H132" s="4" t="inlineStr"/>
+      <c r="I132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5305,12 +4897,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-      <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="2" t="inlineStr"/>
+      <c r="G133" s="4" t="inlineStr"/>
+      <c r="H133" s="4" t="inlineStr"/>
+      <c r="I133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5339,12 +4928,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-      <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr"/>
+      <c r="G134" s="4" t="inlineStr"/>
+      <c r="H134" s="4" t="inlineStr"/>
+      <c r="I134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5373,12 +4959,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-      <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="2" t="inlineStr"/>
+      <c r="G135" s="4" t="inlineStr"/>
+      <c r="H135" s="4" t="inlineStr"/>
+      <c r="I135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5407,12 +4990,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-      <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="2" t="inlineStr"/>
+      <c r="G136" s="4" t="inlineStr"/>
+      <c r="H136" s="4" t="inlineStr"/>
+      <c r="I136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5441,12 +5021,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr"/>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-      <c r="K137" s="2" t="inlineStr"/>
-      <c r="L137" s="2" t="inlineStr"/>
+      <c r="G137" s="4" t="inlineStr"/>
+      <c r="H137" s="4" t="inlineStr"/>
+      <c r="I137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5475,12 +5052,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-      <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="inlineStr"/>
+      <c r="G138" s="4" t="inlineStr"/>
+      <c r="H138" s="4" t="inlineStr"/>
+      <c r="I138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5509,12 +5083,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-      <c r="K139" s="2" t="inlineStr"/>
-      <c r="L139" s="2" t="inlineStr"/>
+      <c r="G139" s="4" t="inlineStr"/>
+      <c r="H139" s="4" t="inlineStr"/>
+      <c r="I139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5543,12 +5114,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-      <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="inlineStr"/>
+      <c r="G140" s="4" t="inlineStr"/>
+      <c r="H140" s="4" t="inlineStr"/>
+      <c r="I140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5577,12 +5145,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-      <c r="K141" s="2" t="inlineStr"/>
-      <c r="L141" s="2" t="inlineStr"/>
+      <c r="G141" s="4" t="inlineStr"/>
+      <c r="H141" s="4" t="inlineStr"/>
+      <c r="I141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5611,12 +5176,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-      <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="2" t="inlineStr"/>
+      <c r="G142" s="4" t="inlineStr"/>
+      <c r="H142" s="4" t="inlineStr"/>
+      <c r="I142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5645,12 +5207,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-      <c r="K143" s="2" t="inlineStr"/>
-      <c r="L143" s="2" t="inlineStr"/>
+      <c r="G143" s="4" t="inlineStr"/>
+      <c r="H143" s="4" t="inlineStr"/>
+      <c r="I143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5679,12 +5238,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr"/>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-      <c r="K144" s="2" t="inlineStr"/>
-      <c r="L144" s="2" t="inlineStr"/>
+      <c r="G144" s="4" t="inlineStr"/>
+      <c r="H144" s="4" t="inlineStr"/>
+      <c r="I144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5713,12 +5269,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr"/>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-      <c r="K145" s="2" t="inlineStr"/>
-      <c r="L145" s="2" t="inlineStr"/>
+      <c r="G145" s="4" t="inlineStr"/>
+      <c r="H145" s="4" t="inlineStr"/>
+      <c r="I145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5747,12 +5300,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr"/>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-      <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="2" t="inlineStr"/>
+      <c r="G146" s="4" t="inlineStr"/>
+      <c r="H146" s="4" t="inlineStr"/>
+      <c r="I146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5781,12 +5331,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr"/>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-      <c r="K147" s="2" t="inlineStr"/>
-      <c r="L147" s="2" t="inlineStr"/>
+      <c r="G147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5815,12 +5362,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr"/>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-      <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="2" t="inlineStr"/>
+      <c r="G148" s="4" t="inlineStr"/>
+      <c r="H148" s="4" t="inlineStr"/>
+      <c r="I148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5849,12 +5393,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr"/>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-      <c r="K149" s="2" t="inlineStr"/>
-      <c r="L149" s="2" t="inlineStr"/>
+      <c r="G149" s="4" t="inlineStr"/>
+      <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5883,12 +5424,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr"/>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-      <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="2" t="inlineStr"/>
+      <c r="G150" s="4" t="inlineStr"/>
+      <c r="H150" s="4" t="inlineStr"/>
+      <c r="I150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5917,12 +5455,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr"/>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-      <c r="K151" s="2" t="inlineStr"/>
-      <c r="L151" s="2" t="inlineStr"/>
+      <c r="G151" s="4" t="inlineStr"/>
+      <c r="H151" s="4" t="inlineStr"/>
+      <c r="I151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5951,12 +5486,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr"/>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-      <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="2" t="inlineStr"/>
+      <c r="G152" s="4" t="inlineStr"/>
+      <c r="H152" s="4" t="inlineStr"/>
+      <c r="I152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5985,16 +5517,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-      <c r="K153" s="2" t="inlineStr"/>
-      <c r="L153" s="2" t="inlineStr"/>
+      <c r="G153" s="4" t="inlineStr"/>
+      <c r="H153" s="4" t="inlineStr"/>
+      <c r="I153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6023,12 +5548,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr"/>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-      <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="inlineStr"/>
+      <c r="G154" s="4" t="inlineStr"/>
+      <c r="H154" s="4" t="inlineStr"/>
+      <c r="I154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6057,16 +5579,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-      <c r="K155" s="2" t="inlineStr"/>
-      <c r="L155" s="2" t="inlineStr"/>
+      <c r="G155" s="4" t="inlineStr"/>
+      <c r="H155" s="4" t="inlineStr"/>
+      <c r="I155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6095,12 +5610,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr"/>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-      <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="2" t="inlineStr"/>
+      <c r="G156" s="4" t="inlineStr"/>
+      <c r="H156" s="4" t="inlineStr"/>
+      <c r="I156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6129,20 +5641,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>需付费</t>
-        </is>
-      </c>
-      <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="2" t="inlineStr"/>
+      <c r="G157" s="4" t="inlineStr"/>
+      <c r="H157" s="4" t="inlineStr"/>
+      <c r="I157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6171,12 +5672,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr"/>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-      <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="2" t="inlineStr"/>
+      <c r="G158" s="4" t="inlineStr"/>
+      <c r="H158" s="4" t="inlineStr"/>
+      <c r="I158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6205,16 +5703,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-      <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="2" t="inlineStr"/>
+      <c r="G159" s="4" t="inlineStr"/>
+      <c r="H159" s="4" t="inlineStr"/>
+      <c r="I159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6243,12 +5734,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr"/>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-      <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="2" t="inlineStr"/>
+      <c r="G160" s="4" t="inlineStr"/>
+      <c r="H160" s="4" t="inlineStr"/>
+      <c r="I160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6277,12 +5765,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr"/>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-      <c r="K161" s="2" t="inlineStr"/>
-      <c r="L161" s="2" t="inlineStr"/>
+      <c r="G161" s="4" t="inlineStr"/>
+      <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -6303,24 +5788,21 @@
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr"/>
-      <c r="I162" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="inlineStr"/>
-      <c r="K162" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="inlineStr"/>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6345,24 +5827,21 @@
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
-      <c r="G163" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr"/>
-      <c r="I163" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="inlineStr"/>
-      <c r="K163" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="inlineStr"/>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
@@ -6383,24 +5862,21 @@
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
-      <c r="G164" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr"/>
-      <c r="I164" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="inlineStr"/>
-      <c r="K164" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="inlineStr"/>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
@@ -6421,24 +5897,21 @@
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
-      <c r="G165" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr"/>
-      <c r="I165" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr"/>
-      <c r="K165" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="inlineStr"/>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
@@ -6459,24 +5932,21 @@
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr"/>
-      <c r="I166" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="inlineStr"/>
-      <c r="K166" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="inlineStr"/>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
@@ -6497,24 +5967,21 @@
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr"/>
-      <c r="I167" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="inlineStr"/>
-      <c r="K167" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr"/>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
@@ -6535,24 +6002,21 @@
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
-      <c r="G168" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr"/>
-      <c r="I168" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="inlineStr"/>
-      <c r="K168" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L168" s="2" t="inlineStr"/>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
@@ -6573,24 +6037,21 @@
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr"/>
-      <c r="I169" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr"/>
-      <c r="K169" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr"/>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
@@ -6611,24 +6072,21 @@
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr"/>
-      <c r="I170" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="inlineStr"/>
-      <c r="K170" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L170" s="2" t="inlineStr"/>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
@@ -6649,24 +6107,21 @@
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
-      <c r="G171" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr"/>
-      <c r="I171" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr"/>
-      <c r="K171" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr"/>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
@@ -6687,24 +6142,21 @@
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr"/>
-      <c r="I172" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr"/>
-      <c r="K172" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L172" s="2" t="inlineStr"/>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
@@ -6725,16 +6177,13 @@
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr"/>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-      <c r="K173" s="2" t="inlineStr">
+      <c r="G173" s="4" t="inlineStr"/>
+      <c r="H173" s="4" t="inlineStr"/>
+      <c r="I173" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
@@ -6755,16 +6204,13 @@
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr"/>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
-      <c r="K174" s="2" t="inlineStr">
+      <c r="G174" s="4" t="inlineStr"/>
+      <c r="H174" s="4" t="inlineStr"/>
+      <c r="I174" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
@@ -6785,16 +6231,13 @@
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr"/>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
-      <c r="K175" s="2" t="inlineStr">
+      <c r="G175" s="4" t="inlineStr"/>
+      <c r="H175" s="4" t="inlineStr"/>
+      <c r="I175" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
@@ -6815,16 +6258,13 @@
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr"/>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr"/>
-      <c r="K176" s="2" t="inlineStr">
+      <c r="G176" s="4" t="inlineStr"/>
+      <c r="H176" s="4" t="inlineStr"/>
+      <c r="I176" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
@@ -6845,16 +6285,13 @@
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr"/>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr"/>
-      <c r="K177" s="2" t="inlineStr">
+      <c r="G177" s="4" t="inlineStr"/>
+      <c r="H177" s="4" t="inlineStr"/>
+      <c r="I177" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
@@ -6875,16 +6312,13 @@
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr"/>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
-      <c r="K178" s="3" t="inlineStr">
+      <c r="G178" s="4" t="inlineStr"/>
+      <c r="H178" s="4" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="L178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr"/>
@@ -6905,16 +6339,13 @@
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr"/>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
-      <c r="K179" s="3" t="inlineStr">
+      <c r="G179" s="4" t="inlineStr"/>
+      <c r="H179" s="4" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="L179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
@@ -6935,16 +6366,13 @@
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr"/>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
-      <c r="K180" s="3" t="inlineStr">
+      <c r="G180" s="4" t="inlineStr"/>
+      <c r="H180" s="4" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="L180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>
@@ -6965,16 +6393,13 @@
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr"/>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
-      <c r="K181" s="3" t="inlineStr">
+      <c r="G181" s="4" t="inlineStr"/>
+      <c r="H181" s="4" t="inlineStr"/>
+      <c r="I181" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="L181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr"/>
@@ -6995,16 +6420,13 @@
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr"/>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr"/>
-      <c r="K182" s="2" t="inlineStr">
+      <c r="G182" s="4" t="inlineStr"/>
+      <c r="H182" s="4" t="inlineStr"/>
+      <c r="I182" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7033,16 +6455,13 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G183" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr"/>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="2" t="inlineStr"/>
+      <c r="H183" s="4" t="inlineStr"/>
+      <c r="I183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7071,16 +6490,13 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G184" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr"/>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="2" t="inlineStr"/>
+      <c r="H184" s="4" t="inlineStr"/>
+      <c r="I184" s="4" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7109,16 +6525,13 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G185" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr"/>
-      <c r="K185" s="2" t="inlineStr"/>
-      <c r="L185" s="2" t="inlineStr"/>
+      <c r="H185" s="4" t="inlineStr"/>
+      <c r="I185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7147,16 +6560,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G186" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="2" t="inlineStr"/>
+      <c r="H186" s="4" t="inlineStr"/>
+      <c r="I186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7185,16 +6595,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G187" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr"/>
-      <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="2" t="inlineStr"/>
+      <c r="H187" s="4" t="inlineStr"/>
+      <c r="I187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7223,16 +6630,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G188" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr"/>
-      <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="2" t="inlineStr"/>
+      <c r="H188" s="4" t="inlineStr"/>
+      <c r="I188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7261,16 +6665,13 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G189" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr"/>
-      <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="2" t="inlineStr"/>
+      <c r="H189" s="4" t="inlineStr"/>
+      <c r="I189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7299,16 +6700,13 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G190" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="2" t="inlineStr"/>
+      <c r="H190" s="4" t="inlineStr"/>
+      <c r="I190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7337,16 +6735,13 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="G191" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr"/>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="2" t="inlineStr"/>
+      <c r="H191" s="4" t="inlineStr"/>
+      <c r="I191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7375,16 +6770,13 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G192" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr"/>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="2" t="inlineStr"/>
+      <c r="H192" s="4" t="inlineStr"/>
+      <c r="I192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7413,16 +6805,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G193" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr"/>
-      <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="2" t="inlineStr"/>
+      <c r="H193" s="4" t="inlineStr"/>
+      <c r="I193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7451,16 +6840,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G194" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr"/>
-      <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="2" t="inlineStr"/>
+      <c r="H194" s="4" t="inlineStr"/>
+      <c r="I194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7489,16 +6875,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G195" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" s="2" t="inlineStr"/>
-      <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="2" t="inlineStr"/>
+      <c r="H195" s="4" t="inlineStr"/>
+      <c r="I195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7527,16 +6910,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G196" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" s="2" t="inlineStr"/>
-      <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="2" t="inlineStr"/>
+      <c r="H196" s="4" t="inlineStr"/>
+      <c r="I196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7565,16 +6945,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G197" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" s="2" t="inlineStr"/>
-      <c r="K197" s="2" t="inlineStr"/>
-      <c r="L197" s="2" t="inlineStr"/>
+      <c r="H197" s="4" t="inlineStr"/>
+      <c r="I197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7603,16 +6980,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G198" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="2" t="inlineStr"/>
-      <c r="K198" s="2" t="inlineStr"/>
-      <c r="L198" s="2" t="inlineStr"/>
+      <c r="H198" s="4" t="inlineStr"/>
+      <c r="I198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7641,16 +7015,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G199" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr"/>
-      <c r="K199" s="2" t="inlineStr"/>
-      <c r="L199" s="2" t="inlineStr"/>
+      <c r="H199" s="4" t="inlineStr"/>
+      <c r="I199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7679,16 +7050,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G200" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr"/>
-      <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="2" t="inlineStr"/>
+      <c r="H200" s="4" t="inlineStr"/>
+      <c r="I200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7717,16 +7085,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G201" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I201" s="2" t="inlineStr"/>
-      <c r="J201" s="2" t="inlineStr"/>
-      <c r="K201" s="2" t="inlineStr"/>
-      <c r="L201" s="2" t="inlineStr"/>
+      <c r="H201" s="4" t="inlineStr"/>
+      <c r="I201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7755,16 +7120,13 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G202" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr"/>
-      <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="2" t="inlineStr"/>
+      <c r="H202" s="4" t="inlineStr"/>
+      <c r="I202" s="4" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7793,16 +7155,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G203" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="2" t="inlineStr"/>
-      <c r="K203" s="2" t="inlineStr"/>
-      <c r="L203" s="2" t="inlineStr"/>
+      <c r="H203" s="4" t="inlineStr"/>
+      <c r="I203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7831,16 +7190,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G204" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr"/>
-      <c r="J204" s="2" t="inlineStr"/>
-      <c r="K204" s="2" t="inlineStr"/>
-      <c r="L204" s="2" t="inlineStr"/>
+      <c r="H204" s="4" t="inlineStr"/>
+      <c r="I204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7869,16 +7225,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G205" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I205" s="2" t="inlineStr"/>
-      <c r="J205" s="2" t="inlineStr"/>
-      <c r="K205" s="2" t="inlineStr"/>
-      <c r="L205" s="2" t="inlineStr"/>
+      <c r="H205" s="4" t="inlineStr"/>
+      <c r="I205" s="4" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7907,16 +7260,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G206" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I206" s="2" t="inlineStr"/>
-      <c r="J206" s="2" t="inlineStr"/>
-      <c r="K206" s="2" t="inlineStr"/>
-      <c r="L206" s="2" t="inlineStr"/>
+      <c r="H206" s="4" t="inlineStr"/>
+      <c r="I206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7945,16 +7295,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G207" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I207" s="2" t="inlineStr"/>
-      <c r="J207" s="2" t="inlineStr"/>
-      <c r="K207" s="2" t="inlineStr"/>
-      <c r="L207" s="2" t="inlineStr"/>
+      <c r="H207" s="4" t="inlineStr"/>
+      <c r="I207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7983,16 +7330,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G208" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I208" s="2" t="inlineStr"/>
-      <c r="J208" s="2" t="inlineStr"/>
-      <c r="K208" s="2" t="inlineStr"/>
-      <c r="L208" s="2" t="inlineStr"/>
+      <c r="H208" s="4" t="inlineStr"/>
+      <c r="I208" s="4" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8021,16 +7365,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G209" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I209" s="2" t="inlineStr"/>
-      <c r="J209" s="2" t="inlineStr"/>
-      <c r="K209" s="2" t="inlineStr"/>
-      <c r="L209" s="2" t="inlineStr"/>
+      <c r="H209" s="4" t="inlineStr"/>
+      <c r="I209" s="4" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8059,16 +7400,13 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G210" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr"/>
-      <c r="J210" s="2" t="inlineStr"/>
-      <c r="K210" s="2" t="inlineStr"/>
-      <c r="L210" s="2" t="inlineStr"/>
+      <c r="H210" s="4" t="inlineStr"/>
+      <c r="I210" s="4" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8089,12 +7427,9 @@
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr"/>
-      <c r="I211" s="2" t="inlineStr"/>
-      <c r="J211" s="2" t="inlineStr"/>
-      <c r="K211" s="2" t="inlineStr"/>
-      <c r="L211" s="2" t="inlineStr"/>
+      <c r="G211" s="4" t="inlineStr"/>
+      <c r="H211" s="4" t="inlineStr"/>
+      <c r="I211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8115,12 +7450,9 @@
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr"/>
-      <c r="I212" s="2" t="inlineStr"/>
-      <c r="J212" s="2" t="inlineStr"/>
-      <c r="K212" s="2" t="inlineStr"/>
-      <c r="L212" s="2" t="inlineStr"/>
+      <c r="G212" s="4" t="inlineStr"/>
+      <c r="H212" s="4" t="inlineStr"/>
+      <c r="I212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8141,12 +7473,9 @@
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr"/>
-      <c r="I213" s="2" t="inlineStr"/>
-      <c r="J213" s="2" t="inlineStr"/>
-      <c r="K213" s="2" t="inlineStr"/>
-      <c r="L213" s="2" t="inlineStr"/>
+      <c r="G213" s="4" t="inlineStr"/>
+      <c r="H213" s="4" t="inlineStr"/>
+      <c r="I213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8167,12 +7496,9 @@
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr"/>
-      <c r="I214" s="2" t="inlineStr"/>
-      <c r="J214" s="2" t="inlineStr"/>
-      <c r="K214" s="2" t="inlineStr"/>
-      <c r="L214" s="2" t="inlineStr"/>
+      <c r="G214" s="4" t="inlineStr"/>
+      <c r="H214" s="4" t="inlineStr"/>
+      <c r="I214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8193,12 +7519,9 @@
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr"/>
-      <c r="I215" s="2" t="inlineStr"/>
-      <c r="J215" s="2" t="inlineStr"/>
-      <c r="K215" s="2" t="inlineStr"/>
-      <c r="L215" s="2" t="inlineStr"/>
+      <c r="G215" s="4" t="inlineStr"/>
+      <c r="H215" s="4" t="inlineStr"/>
+      <c r="I215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8219,12 +7542,9 @@
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr"/>
-      <c r="I216" s="2" t="inlineStr"/>
-      <c r="J216" s="2" t="inlineStr"/>
-      <c r="K216" s="2" t="inlineStr"/>
-      <c r="L216" s="2" t="inlineStr"/>
+      <c r="G216" s="4" t="inlineStr"/>
+      <c r="H216" s="4" t="inlineStr"/>
+      <c r="I216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8245,12 +7565,9 @@
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr"/>
-      <c r="I217" s="2" t="inlineStr"/>
-      <c r="J217" s="2" t="inlineStr"/>
-      <c r="K217" s="2" t="inlineStr"/>
-      <c r="L217" s="2" t="inlineStr"/>
+      <c r="G217" s="4" t="inlineStr"/>
+      <c r="H217" s="4" t="inlineStr"/>
+      <c r="I217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8271,12 +7588,9 @@
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr"/>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr"/>
-      <c r="I218" s="2" t="inlineStr"/>
-      <c r="J218" s="2" t="inlineStr"/>
-      <c r="K218" s="2" t="inlineStr"/>
-      <c r="L218" s="2" t="inlineStr"/>
+      <c r="G218" s="4" t="inlineStr"/>
+      <c r="H218" s="4" t="inlineStr"/>
+      <c r="I218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8297,12 +7611,9 @@
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr"/>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr"/>
-      <c r="I219" s="2" t="inlineStr"/>
-      <c r="J219" s="2" t="inlineStr"/>
-      <c r="K219" s="2" t="inlineStr"/>
-      <c r="L219" s="2" t="inlineStr"/>
+      <c r="G219" s="4" t="inlineStr"/>
+      <c r="H219" s="4" t="inlineStr"/>
+      <c r="I219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8323,12 +7634,9 @@
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr"/>
-      <c r="I220" s="2" t="inlineStr"/>
-      <c r="J220" s="2" t="inlineStr"/>
-      <c r="K220" s="2" t="inlineStr"/>
-      <c r="L220" s="2" t="inlineStr"/>
+      <c r="G220" s="4" t="inlineStr"/>
+      <c r="H220" s="4" t="inlineStr"/>
+      <c r="I220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8349,12 +7657,9 @@
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr"/>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr"/>
-      <c r="I221" s="2" t="inlineStr"/>
-      <c r="J221" s="2" t="inlineStr"/>
-      <c r="K221" s="2" t="inlineStr"/>
-      <c r="L221" s="2" t="inlineStr"/>
+      <c r="G221" s="4" t="inlineStr"/>
+      <c r="H221" s="4" t="inlineStr"/>
+      <c r="I221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8375,12 +7680,9 @@
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr"/>
-      <c r="I222" s="2" t="inlineStr"/>
-      <c r="J222" s="2" t="inlineStr"/>
-      <c r="K222" s="2" t="inlineStr"/>
-      <c r="L222" s="2" t="inlineStr"/>
+      <c r="G222" s="4" t="inlineStr"/>
+      <c r="H222" s="4" t="inlineStr"/>
+      <c r="I222" s="4" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8401,12 +7703,9 @@
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr"/>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr"/>
-      <c r="I223" s="2" t="inlineStr"/>
-      <c r="J223" s="2" t="inlineStr"/>
-      <c r="K223" s="2" t="inlineStr"/>
-      <c r="L223" s="2" t="inlineStr"/>
+      <c r="G223" s="4" t="inlineStr"/>
+      <c r="H223" s="4" t="inlineStr"/>
+      <c r="I223" s="4" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8427,12 +7726,9 @@
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr"/>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr"/>
-      <c r="I224" s="2" t="inlineStr"/>
-      <c r="J224" s="2" t="inlineStr"/>
-      <c r="K224" s="2" t="inlineStr"/>
-      <c r="L224" s="2" t="inlineStr"/>
+      <c r="G224" s="4" t="inlineStr"/>
+      <c r="H224" s="4" t="inlineStr"/>
+      <c r="I224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8453,12 +7749,9 @@
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr"/>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr"/>
-      <c r="I225" s="2" t="inlineStr"/>
-      <c r="J225" s="2" t="inlineStr"/>
-      <c r="K225" s="2" t="inlineStr"/>
-      <c r="L225" s="2" t="inlineStr"/>
+      <c r="G225" s="4" t="inlineStr"/>
+      <c r="H225" s="4" t="inlineStr"/>
+      <c r="I225" s="4" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8479,12 +7772,9 @@
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr"/>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr"/>
-      <c r="I226" s="2" t="inlineStr"/>
-      <c r="J226" s="2" t="inlineStr"/>
-      <c r="K226" s="2" t="inlineStr"/>
-      <c r="L226" s="2" t="inlineStr"/>
+      <c r="G226" s="4" t="inlineStr"/>
+      <c r="H226" s="4" t="inlineStr"/>
+      <c r="I226" s="4" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8505,12 +7795,9 @@
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr"/>
-      <c r="I227" s="2" t="inlineStr"/>
-      <c r="J227" s="2" t="inlineStr"/>
-      <c r="K227" s="2" t="inlineStr"/>
-      <c r="L227" s="2" t="inlineStr"/>
+      <c r="G227" s="4" t="inlineStr"/>
+      <c r="H227" s="4" t="inlineStr"/>
+      <c r="I227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8531,12 +7818,9 @@
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr"/>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr"/>
-      <c r="I228" s="2" t="inlineStr"/>
-      <c r="J228" s="2" t="inlineStr"/>
-      <c r="K228" s="2" t="inlineStr"/>
-      <c r="L228" s="2" t="inlineStr"/>
+      <c r="G228" s="4" t="inlineStr"/>
+      <c r="H228" s="4" t="inlineStr"/>
+      <c r="I228" s="4" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8557,12 +7841,9 @@
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr"/>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr"/>
-      <c r="I229" s="2" t="inlineStr"/>
-      <c r="J229" s="2" t="inlineStr"/>
-      <c r="K229" s="2" t="inlineStr"/>
-      <c r="L229" s="2" t="inlineStr"/>
+      <c r="G229" s="4" t="inlineStr"/>
+      <c r="H229" s="4" t="inlineStr"/>
+      <c r="I229" s="4" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8583,12 +7864,9 @@
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr"/>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr"/>
-      <c r="I230" s="2" t="inlineStr"/>
-      <c r="J230" s="2" t="inlineStr"/>
-      <c r="K230" s="2" t="inlineStr"/>
-      <c r="L230" s="2" t="inlineStr"/>
+      <c r="G230" s="4" t="inlineStr"/>
+      <c r="H230" s="4" t="inlineStr"/>
+      <c r="I230" s="4" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8609,12 +7887,9 @@
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr"/>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr"/>
-      <c r="I231" s="2" t="inlineStr"/>
-      <c r="J231" s="2" t="inlineStr"/>
-      <c r="K231" s="2" t="inlineStr"/>
-      <c r="L231" s="2" t="inlineStr"/>
+      <c r="G231" s="4" t="inlineStr"/>
+      <c r="H231" s="4" t="inlineStr"/>
+      <c r="I231" s="4" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8635,12 +7910,9 @@
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr"/>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr"/>
-      <c r="I232" s="2" t="inlineStr"/>
-      <c r="J232" s="2" t="inlineStr"/>
-      <c r="K232" s="2" t="inlineStr"/>
-      <c r="L232" s="2" t="inlineStr"/>
+      <c r="G232" s="4" t="inlineStr"/>
+      <c r="H232" s="4" t="inlineStr"/>
+      <c r="I232" s="4" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8661,12 +7933,9 @@
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr"/>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr"/>
-      <c r="I233" s="2" t="inlineStr"/>
-      <c r="J233" s="2" t="inlineStr"/>
-      <c r="K233" s="2" t="inlineStr"/>
-      <c r="L233" s="2" t="inlineStr"/>
+      <c r="G233" s="4" t="inlineStr"/>
+      <c r="H233" s="4" t="inlineStr"/>
+      <c r="I233" s="4" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8687,12 +7956,9 @@
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr"/>
-      <c r="I234" s="2" t="inlineStr"/>
-      <c r="J234" s="2" t="inlineStr"/>
-      <c r="K234" s="2" t="inlineStr"/>
-      <c r="L234" s="2" t="inlineStr"/>
+      <c r="G234" s="4" t="inlineStr"/>
+      <c r="H234" s="4" t="inlineStr"/>
+      <c r="I234" s="4" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8713,12 +7979,9 @@
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr"/>
-      <c r="I235" s="2" t="inlineStr"/>
-      <c r="J235" s="2" t="inlineStr"/>
-      <c r="K235" s="2" t="inlineStr"/>
-      <c r="L235" s="2" t="inlineStr"/>
+      <c r="G235" s="4" t="inlineStr"/>
+      <c r="H235" s="4" t="inlineStr"/>
+      <c r="I235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8747,12 +8010,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr"/>
-      <c r="I236" s="2" t="inlineStr"/>
-      <c r="J236" s="2" t="inlineStr"/>
-      <c r="K236" s="2" t="inlineStr"/>
-      <c r="L236" s="2" t="inlineStr"/>
+      <c r="G236" s="4" t="inlineStr"/>
+      <c r="H236" s="4" t="inlineStr"/>
+      <c r="I236" s="4" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8773,12 +8033,9 @@
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr"/>
-      <c r="I237" s="2" t="inlineStr"/>
-      <c r="J237" s="2" t="inlineStr"/>
-      <c r="K237" s="2" t="inlineStr"/>
-      <c r="L237" s="2" t="inlineStr"/>
+      <c r="G237" s="4" t="inlineStr"/>
+      <c r="H237" s="4" t="inlineStr"/>
+      <c r="I237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8799,12 +8056,9 @@
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr"/>
-      <c r="I238" s="2" t="inlineStr"/>
-      <c r="J238" s="2" t="inlineStr"/>
-      <c r="K238" s="2" t="inlineStr"/>
-      <c r="L238" s="2" t="inlineStr"/>
+      <c r="G238" s="4" t="inlineStr"/>
+      <c r="H238" s="4" t="inlineStr"/>
+      <c r="I238" s="4" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8825,12 +8079,9 @@
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr"/>
-      <c r="I239" s="2" t="inlineStr"/>
-      <c r="J239" s="2" t="inlineStr"/>
-      <c r="K239" s="2" t="inlineStr"/>
-      <c r="L239" s="2" t="inlineStr"/>
+      <c r="G239" s="4" t="inlineStr"/>
+      <c r="H239" s="4" t="inlineStr"/>
+      <c r="I239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8851,12 +8102,9 @@
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr"/>
-      <c r="I240" s="2" t="inlineStr"/>
-      <c r="J240" s="2" t="inlineStr"/>
-      <c r="K240" s="2" t="inlineStr"/>
-      <c r="L240" s="2" t="inlineStr"/>
+      <c r="G240" s="4" t="inlineStr"/>
+      <c r="H240" s="4" t="inlineStr"/>
+      <c r="I240" s="4" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8877,12 +8125,9 @@
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr"/>
-      <c r="I241" s="2" t="inlineStr"/>
-      <c r="J241" s="2" t="inlineStr"/>
-      <c r="K241" s="2" t="inlineStr"/>
-      <c r="L241" s="2" t="inlineStr"/>
+      <c r="G241" s="4" t="inlineStr"/>
+      <c r="H241" s="4" t="inlineStr"/>
+      <c r="I241" s="4" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8903,12 +8148,9 @@
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr"/>
-      <c r="I242" s="2" t="inlineStr"/>
-      <c r="J242" s="2" t="inlineStr"/>
-      <c r="K242" s="2" t="inlineStr"/>
-      <c r="L242" s="2" t="inlineStr"/>
+      <c r="G242" s="4" t="inlineStr"/>
+      <c r="H242" s="4" t="inlineStr"/>
+      <c r="I242" s="4" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8929,12 +8171,9 @@
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr"/>
-      <c r="I243" s="2" t="inlineStr"/>
-      <c r="J243" s="2" t="inlineStr"/>
-      <c r="K243" s="2" t="inlineStr"/>
-      <c r="L243" s="2" t="inlineStr"/>
+      <c r="G243" s="4" t="inlineStr"/>
+      <c r="H243" s="4" t="inlineStr"/>
+      <c r="I243" s="4" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8955,12 +8194,9 @@
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr"/>
-      <c r="I244" s="2" t="inlineStr"/>
-      <c r="J244" s="2" t="inlineStr"/>
-      <c r="K244" s="2" t="inlineStr"/>
-      <c r="L244" s="2" t="inlineStr"/>
+      <c r="G244" s="4" t="inlineStr"/>
+      <c r="H244" s="4" t="inlineStr"/>
+      <c r="I244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8981,12 +8217,9 @@
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr"/>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr"/>
-      <c r="I245" s="2" t="inlineStr"/>
-      <c r="J245" s="2" t="inlineStr"/>
-      <c r="K245" s="2" t="inlineStr"/>
-      <c r="L245" s="2" t="inlineStr"/>
+      <c r="G245" s="4" t="inlineStr"/>
+      <c r="H245" s="4" t="inlineStr"/>
+      <c r="I245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9007,12 +8240,9 @@
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr"/>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr"/>
-      <c r="I246" s="2" t="inlineStr"/>
-      <c r="J246" s="2" t="inlineStr"/>
-      <c r="K246" s="2" t="inlineStr"/>
-      <c r="L246" s="2" t="inlineStr"/>
+      <c r="G246" s="4" t="inlineStr"/>
+      <c r="H246" s="4" t="inlineStr"/>
+      <c r="I246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9033,12 +8263,9 @@
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr"/>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr"/>
-      <c r="I247" s="2" t="inlineStr"/>
-      <c r="J247" s="2" t="inlineStr"/>
-      <c r="K247" s="2" t="inlineStr"/>
-      <c r="L247" s="2" t="inlineStr"/>
+      <c r="G247" s="4" t="inlineStr"/>
+      <c r="H247" s="4" t="inlineStr"/>
+      <c r="I247" s="4" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9059,12 +8286,9 @@
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr"/>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr"/>
-      <c r="I248" s="2" t="inlineStr"/>
-      <c r="J248" s="2" t="inlineStr"/>
-      <c r="K248" s="2" t="inlineStr"/>
-      <c r="L248" s="2" t="inlineStr"/>
+      <c r="G248" s="4" t="inlineStr"/>
+      <c r="H248" s="4" t="inlineStr"/>
+      <c r="I248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9085,12 +8309,9 @@
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr"/>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr"/>
-      <c r="I249" s="2" t="inlineStr"/>
-      <c r="J249" s="2" t="inlineStr"/>
-      <c r="K249" s="2" t="inlineStr"/>
-      <c r="L249" s="2" t="inlineStr"/>
+      <c r="G249" s="4" t="inlineStr"/>
+      <c r="H249" s="4" t="inlineStr"/>
+      <c r="I249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9111,12 +8332,9 @@
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr"/>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr"/>
-      <c r="I250" s="2" t="inlineStr"/>
-      <c r="J250" s="2" t="inlineStr"/>
-      <c r="K250" s="2" t="inlineStr"/>
-      <c r="L250" s="2" t="inlineStr"/>
+      <c r="G250" s="4" t="inlineStr"/>
+      <c r="H250" s="4" t="inlineStr"/>
+      <c r="I250" s="4" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9137,12 +8355,9 @@
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr"/>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr"/>
-      <c r="I251" s="2" t="inlineStr"/>
-      <c r="J251" s="2" t="inlineStr"/>
-      <c r="K251" s="2" t="inlineStr"/>
-      <c r="L251" s="2" t="inlineStr"/>
+      <c r="G251" s="4" t="inlineStr"/>
+      <c r="H251" s="4" t="inlineStr"/>
+      <c r="I251" s="4" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9163,12 +8378,9 @@
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr"/>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr"/>
-      <c r="I252" s="2" t="inlineStr"/>
-      <c r="J252" s="2" t="inlineStr"/>
-      <c r="K252" s="2" t="inlineStr"/>
-      <c r="L252" s="2" t="inlineStr"/>
+      <c r="G252" s="4" t="inlineStr"/>
+      <c r="H252" s="4" t="inlineStr"/>
+      <c r="I252" s="4" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9189,12 +8401,9 @@
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr"/>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr"/>
-      <c r="I253" s="2" t="inlineStr"/>
-      <c r="J253" s="2" t="inlineStr"/>
-      <c r="K253" s="2" t="inlineStr"/>
-      <c r="L253" s="2" t="inlineStr"/>
+      <c r="G253" s="4" t="inlineStr"/>
+      <c r="H253" s="4" t="inlineStr"/>
+      <c r="I253" s="4" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9215,12 +8424,9 @@
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr"/>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="2" t="inlineStr"/>
-      <c r="I254" s="2" t="inlineStr"/>
-      <c r="J254" s="2" t="inlineStr"/>
-      <c r="K254" s="2" t="inlineStr"/>
-      <c r="L254" s="2" t="inlineStr"/>
+      <c r="G254" s="4" t="inlineStr"/>
+      <c r="H254" s="4" t="inlineStr"/>
+      <c r="I254" s="4" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9241,12 +8447,9 @@
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr"/>
-      <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="2" t="inlineStr"/>
-      <c r="I255" s="2" t="inlineStr"/>
-      <c r="J255" s="2" t="inlineStr"/>
-      <c r="K255" s="2" t="inlineStr"/>
-      <c r="L255" s="2" t="inlineStr"/>
+      <c r="G255" s="4" t="inlineStr"/>
+      <c r="H255" s="4" t="inlineStr"/>
+      <c r="I255" s="4" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr"/>
@@ -9267,16 +8470,13 @@
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr"/>
-      <c r="G256" s="2" t="inlineStr"/>
-      <c r="H256" s="2" t="inlineStr"/>
-      <c r="I256" s="2" t="inlineStr"/>
-      <c r="J256" s="2" t="inlineStr"/>
-      <c r="K256" s="2" t="inlineStr">
+      <c r="G256" s="4" t="inlineStr"/>
+      <c r="H256" s="4" t="inlineStr"/>
+      <c r="I256" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr"/>
@@ -9297,24 +8497,21 @@
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
-      <c r="G257" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H257" s="2" t="inlineStr"/>
-      <c r="I257" s="2" t="inlineStr">
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="J257" s="2" t="inlineStr"/>
-      <c r="K257" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L257" s="2" t="inlineStr"/>
+      <c r="I257" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr"/>
@@ -9335,16 +8532,13 @@
       </c>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr"/>
-      <c r="G258" s="2" t="inlineStr"/>
-      <c r="H258" s="2" t="inlineStr"/>
-      <c r="I258" s="2" t="inlineStr"/>
-      <c r="J258" s="2" t="inlineStr"/>
-      <c r="K258" s="2" t="inlineStr">
+      <c r="G258" s="4" t="inlineStr"/>
+      <c r="H258" s="4" t="inlineStr"/>
+      <c r="I258" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr"/>
@@ -9365,12 +8559,9 @@
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr"/>
-      <c r="G259" s="2" t="inlineStr"/>
-      <c r="H259" s="2" t="inlineStr"/>
-      <c r="I259" s="2" t="inlineStr"/>
-      <c r="J259" s="2" t="inlineStr"/>
-      <c r="K259" s="2" t="inlineStr"/>
-      <c r="L259" s="2" t="inlineStr"/>
+      <c r="G259" s="4" t="inlineStr"/>
+      <c r="H259" s="4" t="inlineStr"/>
+      <c r="I259" s="4" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr"/>
@@ -9391,12 +8582,9 @@
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr"/>
-      <c r="G260" s="2" t="inlineStr"/>
-      <c r="H260" s="2" t="inlineStr"/>
-      <c r="I260" s="2" t="inlineStr"/>
-      <c r="J260" s="2" t="inlineStr"/>
-      <c r="K260" s="2" t="inlineStr"/>
-      <c r="L260" s="2" t="inlineStr"/>
+      <c r="G260" s="4" t="inlineStr"/>
+      <c r="H260" s="4" t="inlineStr"/>
+      <c r="I260" s="4" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9425,12 +8613,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr"/>
-      <c r="H261" s="2" t="inlineStr"/>
-      <c r="I261" s="2" t="inlineStr"/>
-      <c r="J261" s="2" t="inlineStr"/>
-      <c r="K261" s="2" t="inlineStr"/>
-      <c r="L261" s="2" t="inlineStr"/>
+      <c r="G261" s="4" t="inlineStr"/>
+      <c r="H261" s="4" t="inlineStr"/>
+      <c r="I261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9451,12 +8636,9 @@
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr"/>
-      <c r="G262" s="2" t="inlineStr"/>
-      <c r="H262" s="2" t="inlineStr"/>
-      <c r="I262" s="2" t="inlineStr"/>
-      <c r="J262" s="2" t="inlineStr"/>
-      <c r="K262" s="2" t="inlineStr"/>
-      <c r="L262" s="2" t="inlineStr"/>
+      <c r="G262" s="4" t="inlineStr"/>
+      <c r="H262" s="4" t="inlineStr"/>
+      <c r="I262" s="4" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9485,16 +8667,13 @@
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
-      <c r="G263" s="2" t="inlineStr"/>
-      <c r="H263" s="2" t="inlineStr"/>
-      <c r="I263" s="2" t="inlineStr"/>
-      <c r="J263" s="3" t="inlineStr">
+      <c r="G263" s="4" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="K263" s="2" t="inlineStr"/>
-      <c r="L263" s="3" t="inlineStr">
+      <c r="I263" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -9527,12 +8706,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr"/>
-      <c r="H264" s="2" t="inlineStr"/>
-      <c r="I264" s="2" t="inlineStr"/>
-      <c r="J264" s="2" t="inlineStr"/>
-      <c r="K264" s="2" t="inlineStr"/>
-      <c r="L264" s="2" t="inlineStr"/>
+      <c r="G264" s="4" t="inlineStr"/>
+      <c r="H264" s="4" t="inlineStr"/>
+      <c r="I264" s="4" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9557,12 +8733,9 @@
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr"/>
-      <c r="G265" s="2" t="inlineStr"/>
-      <c r="H265" s="2" t="inlineStr"/>
-      <c r="I265" s="2" t="inlineStr"/>
-      <c r="J265" s="2" t="inlineStr"/>
-      <c r="K265" s="2" t="inlineStr"/>
-      <c r="L265" s="2" t="inlineStr"/>
+      <c r="G265" s="4" t="inlineStr"/>
+      <c r="H265" s="4" t="inlineStr"/>
+      <c r="I265" s="4" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9587,12 +8760,9 @@
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr"/>
-      <c r="G266" s="2" t="inlineStr"/>
-      <c r="H266" s="2" t="inlineStr"/>
-      <c r="I266" s="2" t="inlineStr"/>
-      <c r="J266" s="2" t="inlineStr"/>
-      <c r="K266" s="2" t="inlineStr"/>
-      <c r="L266" s="2" t="inlineStr"/>
+      <c r="G266" s="4" t="inlineStr"/>
+      <c r="H266" s="4" t="inlineStr"/>
+      <c r="I266" s="4" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9621,12 +8791,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr"/>
-      <c r="H267" s="2" t="inlineStr"/>
-      <c r="I267" s="2" t="inlineStr"/>
-      <c r="J267" s="2" t="inlineStr"/>
-      <c r="K267" s="2" t="inlineStr"/>
-      <c r="L267" s="2" t="inlineStr"/>
+      <c r="G267" s="4" t="inlineStr"/>
+      <c r="H267" s="4" t="inlineStr"/>
+      <c r="I267" s="4" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9651,12 +8818,9 @@
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr"/>
-      <c r="G268" s="2" t="inlineStr"/>
-      <c r="H268" s="2" t="inlineStr"/>
-      <c r="I268" s="2" t="inlineStr"/>
-      <c r="J268" s="2" t="inlineStr"/>
-      <c r="K268" s="2" t="inlineStr"/>
-      <c r="L268" s="2" t="inlineStr"/>
+      <c r="G268" s="4" t="inlineStr"/>
+      <c r="H268" s="4" t="inlineStr"/>
+      <c r="I268" s="4" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9681,12 +8845,9 @@
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr"/>
-      <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="2" t="inlineStr"/>
-      <c r="I269" s="2" t="inlineStr"/>
-      <c r="J269" s="2" t="inlineStr"/>
-      <c r="K269" s="2" t="inlineStr"/>
-      <c r="L269" s="2" t="inlineStr"/>
+      <c r="G269" s="4" t="inlineStr"/>
+      <c r="H269" s="4" t="inlineStr"/>
+      <c r="I269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9711,12 +8872,9 @@
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr"/>
-      <c r="G270" s="2" t="inlineStr"/>
-      <c r="H270" s="2" t="inlineStr"/>
-      <c r="I270" s="2" t="inlineStr"/>
-      <c r="J270" s="2" t="inlineStr"/>
-      <c r="K270" s="2" t="inlineStr"/>
-      <c r="L270" s="2" t="inlineStr"/>
+      <c r="G270" s="4" t="inlineStr"/>
+      <c r="H270" s="4" t="inlineStr"/>
+      <c r="I270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9741,12 +8899,9 @@
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr"/>
-      <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="2" t="inlineStr"/>
-      <c r="I271" s="2" t="inlineStr"/>
-      <c r="J271" s="2" t="inlineStr"/>
-      <c r="K271" s="2" t="inlineStr"/>
-      <c r="L271" s="2" t="inlineStr"/>
+      <c r="G271" s="4" t="inlineStr"/>
+      <c r="H271" s="4" t="inlineStr"/>
+      <c r="I271" s="4" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9771,12 +8926,9 @@
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr"/>
-      <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="2" t="inlineStr"/>
-      <c r="I272" s="2" t="inlineStr"/>
-      <c r="J272" s="2" t="inlineStr"/>
-      <c r="K272" s="2" t="inlineStr"/>
-      <c r="L272" s="2" t="inlineStr"/>
+      <c r="G272" s="4" t="inlineStr"/>
+      <c r="H272" s="4" t="inlineStr"/>
+      <c r="I272" s="4" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9801,12 +8953,9 @@
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr"/>
-      <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="2" t="inlineStr"/>
-      <c r="I273" s="2" t="inlineStr"/>
-      <c r="J273" s="2" t="inlineStr"/>
-      <c r="K273" s="2" t="inlineStr"/>
-      <c r="L273" s="2" t="inlineStr"/>
+      <c r="G273" s="4" t="inlineStr"/>
+      <c r="H273" s="4" t="inlineStr"/>
+      <c r="I273" s="4" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9831,12 +8980,9 @@
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr"/>
-      <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="2" t="inlineStr"/>
-      <c r="I274" s="2" t="inlineStr"/>
-      <c r="J274" s="2" t="inlineStr"/>
-      <c r="K274" s="2" t="inlineStr"/>
-      <c r="L274" s="2" t="inlineStr"/>
+      <c r="G274" s="4" t="inlineStr"/>
+      <c r="H274" s="4" t="inlineStr"/>
+      <c r="I274" s="4" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9861,12 +9007,9 @@
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
-      <c r="G275" s="2" t="inlineStr"/>
-      <c r="H275" s="2" t="inlineStr"/>
-      <c r="I275" s="2" t="inlineStr"/>
-      <c r="J275" s="2" t="inlineStr"/>
-      <c r="K275" s="2" t="inlineStr"/>
-      <c r="L275" s="2" t="inlineStr"/>
+      <c r="G275" s="4" t="inlineStr"/>
+      <c r="H275" s="4" t="inlineStr"/>
+      <c r="I275" s="4" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9891,12 +9034,9 @@
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr"/>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr"/>
-      <c r="I276" s="2" t="inlineStr"/>
-      <c r="J276" s="2" t="inlineStr"/>
-      <c r="K276" s="2" t="inlineStr"/>
-      <c r="L276" s="2" t="inlineStr"/>
+      <c r="G276" s="4" t="inlineStr"/>
+      <c r="H276" s="4" t="inlineStr"/>
+      <c r="I276" s="4" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9921,12 +9061,9 @@
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr"/>
-      <c r="G277" s="2" t="inlineStr"/>
-      <c r="H277" s="2" t="inlineStr"/>
-      <c r="I277" s="2" t="inlineStr"/>
-      <c r="J277" s="2" t="inlineStr"/>
-      <c r="K277" s="2" t="inlineStr"/>
-      <c r="L277" s="2" t="inlineStr"/>
+      <c r="G277" s="4" t="inlineStr"/>
+      <c r="H277" s="4" t="inlineStr"/>
+      <c r="I277" s="4" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9951,12 +9088,9 @@
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr"/>
-      <c r="G278" s="2" t="inlineStr"/>
-      <c r="H278" s="2" t="inlineStr"/>
-      <c r="I278" s="2" t="inlineStr"/>
-      <c r="J278" s="2" t="inlineStr"/>
-      <c r="K278" s="2" t="inlineStr"/>
-      <c r="L278" s="2" t="inlineStr"/>
+      <c r="G278" s="4" t="inlineStr"/>
+      <c r="H278" s="4" t="inlineStr"/>
+      <c r="I278" s="4" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9981,12 +9115,9 @@
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr"/>
-      <c r="G279" s="2" t="inlineStr"/>
-      <c r="H279" s="2" t="inlineStr"/>
-      <c r="I279" s="2" t="inlineStr"/>
-      <c r="J279" s="2" t="inlineStr"/>
-      <c r="K279" s="2" t="inlineStr"/>
-      <c r="L279" s="2" t="inlineStr"/>
+      <c r="G279" s="4" t="inlineStr"/>
+      <c r="H279" s="4" t="inlineStr"/>
+      <c r="I279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10011,12 +9142,9 @@
       </c>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr"/>
-      <c r="G280" s="2" t="inlineStr"/>
-      <c r="H280" s="2" t="inlineStr"/>
-      <c r="I280" s="2" t="inlineStr"/>
-      <c r="J280" s="2" t="inlineStr"/>
-      <c r="K280" s="2" t="inlineStr"/>
-      <c r="L280" s="2" t="inlineStr"/>
+      <c r="G280" s="4" t="inlineStr"/>
+      <c r="H280" s="4" t="inlineStr"/>
+      <c r="I280" s="4" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10041,12 +9169,9 @@
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr"/>
-      <c r="G281" s="2" t="inlineStr"/>
-      <c r="H281" s="2" t="inlineStr"/>
-      <c r="I281" s="2" t="inlineStr"/>
-      <c r="J281" s="2" t="inlineStr"/>
-      <c r="K281" s="2" t="inlineStr"/>
-      <c r="L281" s="2" t="inlineStr"/>
+      <c r="G281" s="4" t="inlineStr"/>
+      <c r="H281" s="4" t="inlineStr"/>
+      <c r="I281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10071,12 +9196,9 @@
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr"/>
-      <c r="G282" s="2" t="inlineStr"/>
-      <c r="H282" s="2" t="inlineStr"/>
-      <c r="I282" s="2" t="inlineStr"/>
-      <c r="J282" s="2" t="inlineStr"/>
-      <c r="K282" s="2" t="inlineStr"/>
-      <c r="L282" s="2" t="inlineStr"/>
+      <c r="G282" s="4" t="inlineStr"/>
+      <c r="H282" s="4" t="inlineStr"/>
+      <c r="I282" s="4" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10105,12 +9227,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr"/>
-      <c r="H283" s="2" t="inlineStr"/>
-      <c r="I283" s="2" t="inlineStr"/>
-      <c r="J283" s="2" t="inlineStr"/>
-      <c r="K283" s="2" t="inlineStr"/>
-      <c r="L283" s="2" t="inlineStr"/>
+      <c r="G283" s="4" t="inlineStr"/>
+      <c r="H283" s="4" t="inlineStr"/>
+      <c r="I283" s="4" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10139,12 +9258,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr"/>
-      <c r="H284" s="2" t="inlineStr"/>
-      <c r="I284" s="2" t="inlineStr"/>
-      <c r="J284" s="2" t="inlineStr"/>
-      <c r="K284" s="2" t="inlineStr"/>
-      <c r="L284" s="2" t="inlineStr"/>
+      <c r="G284" s="4" t="inlineStr"/>
+      <c r="H284" s="4" t="inlineStr"/>
+      <c r="I284" s="4" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10169,12 +9285,9 @@
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr"/>
-      <c r="G285" s="2" t="inlineStr"/>
-      <c r="H285" s="2" t="inlineStr"/>
-      <c r="I285" s="2" t="inlineStr"/>
-      <c r="J285" s="2" t="inlineStr"/>
-      <c r="K285" s="2" t="inlineStr"/>
-      <c r="L285" s="2" t="inlineStr"/>
+      <c r="G285" s="4" t="inlineStr"/>
+      <c r="H285" s="4" t="inlineStr"/>
+      <c r="I285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10199,12 +9312,9 @@
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr"/>
-      <c r="G286" s="2" t="inlineStr"/>
-      <c r="H286" s="2" t="inlineStr"/>
-      <c r="I286" s="2" t="inlineStr"/>
-      <c r="J286" s="2" t="inlineStr"/>
-      <c r="K286" s="2" t="inlineStr"/>
-      <c r="L286" s="2" t="inlineStr"/>
+      <c r="G286" s="4" t="inlineStr"/>
+      <c r="H286" s="4" t="inlineStr"/>
+      <c r="I286" s="4" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10229,12 +9339,9 @@
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr"/>
-      <c r="G287" s="2" t="inlineStr"/>
-      <c r="H287" s="2" t="inlineStr"/>
-      <c r="I287" s="2" t="inlineStr"/>
-      <c r="J287" s="2" t="inlineStr"/>
-      <c r="K287" s="2" t="inlineStr"/>
-      <c r="L287" s="2" t="inlineStr"/>
+      <c r="G287" s="4" t="inlineStr"/>
+      <c r="H287" s="4" t="inlineStr"/>
+      <c r="I287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10259,12 +9366,9 @@
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr"/>
-      <c r="G288" s="2" t="inlineStr"/>
-      <c r="H288" s="2" t="inlineStr"/>
-      <c r="I288" s="2" t="inlineStr"/>
-      <c r="J288" s="2" t="inlineStr"/>
-      <c r="K288" s="2" t="inlineStr"/>
-      <c r="L288" s="2" t="inlineStr"/>
+      <c r="G288" s="4" t="inlineStr"/>
+      <c r="H288" s="4" t="inlineStr"/>
+      <c r="I288" s="4" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10289,12 +9393,9 @@
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr"/>
-      <c r="G289" s="2" t="inlineStr"/>
-      <c r="H289" s="2" t="inlineStr"/>
-      <c r="I289" s="2" t="inlineStr"/>
-      <c r="J289" s="2" t="inlineStr"/>
-      <c r="K289" s="2" t="inlineStr"/>
-      <c r="L289" s="2" t="inlineStr"/>
+      <c r="G289" s="4" t="inlineStr"/>
+      <c r="H289" s="4" t="inlineStr"/>
+      <c r="I289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10319,12 +9420,9 @@
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr"/>
-      <c r="G290" s="2" t="inlineStr"/>
-      <c r="H290" s="2" t="inlineStr"/>
-      <c r="I290" s="2" t="inlineStr"/>
-      <c r="J290" s="2" t="inlineStr"/>
-      <c r="K290" s="2" t="inlineStr"/>
-      <c r="L290" s="2" t="inlineStr"/>
+      <c r="G290" s="4" t="inlineStr"/>
+      <c r="H290" s="4" t="inlineStr"/>
+      <c r="I290" s="4" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10349,12 +9447,9 @@
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr"/>
-      <c r="G291" s="2" t="inlineStr"/>
-      <c r="H291" s="2" t="inlineStr"/>
-      <c r="I291" s="2" t="inlineStr"/>
-      <c r="J291" s="2" t="inlineStr"/>
-      <c r="K291" s="2" t="inlineStr"/>
-      <c r="L291" s="2" t="inlineStr"/>
+      <c r="G291" s="4" t="inlineStr"/>
+      <c r="H291" s="4" t="inlineStr"/>
+      <c r="I291" s="4" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10379,12 +9474,9 @@
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr"/>
-      <c r="G292" s="2" t="inlineStr"/>
-      <c r="H292" s="2" t="inlineStr"/>
-      <c r="I292" s="2" t="inlineStr"/>
-      <c r="J292" s="2" t="inlineStr"/>
-      <c r="K292" s="2" t="inlineStr"/>
-      <c r="L292" s="2" t="inlineStr"/>
+      <c r="G292" s="4" t="inlineStr"/>
+      <c r="H292" s="4" t="inlineStr"/>
+      <c r="I292" s="4" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10409,12 +9501,9 @@
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr"/>
-      <c r="G293" s="2" t="inlineStr"/>
-      <c r="H293" s="2" t="inlineStr"/>
-      <c r="I293" s="2" t="inlineStr"/>
-      <c r="J293" s="2" t="inlineStr"/>
-      <c r="K293" s="2" t="inlineStr"/>
-      <c r="L293" s="2" t="inlineStr"/>
+      <c r="G293" s="4" t="inlineStr"/>
+      <c r="H293" s="4" t="inlineStr"/>
+      <c r="I293" s="4" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10439,12 +9528,9 @@
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr"/>
-      <c r="G294" s="2" t="inlineStr"/>
-      <c r="H294" s="2" t="inlineStr"/>
-      <c r="I294" s="2" t="inlineStr"/>
-      <c r="J294" s="2" t="inlineStr"/>
-      <c r="K294" s="2" t="inlineStr"/>
-      <c r="L294" s="2" t="inlineStr"/>
+      <c r="G294" s="4" t="inlineStr"/>
+      <c r="H294" s="4" t="inlineStr"/>
+      <c r="I294" s="4" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10469,12 +9555,9 @@
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr"/>
-      <c r="G295" s="2" t="inlineStr"/>
-      <c r="H295" s="2" t="inlineStr"/>
-      <c r="I295" s="2" t="inlineStr"/>
-      <c r="J295" s="2" t="inlineStr"/>
-      <c r="K295" s="2" t="inlineStr"/>
-      <c r="L295" s="2" t="inlineStr"/>
+      <c r="G295" s="4" t="inlineStr"/>
+      <c r="H295" s="4" t="inlineStr"/>
+      <c r="I295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10503,12 +9586,9 @@
           <t>zh</t>
         </is>
       </c>
-      <c r="G296" s="2" t="inlineStr"/>
-      <c r="H296" s="2" t="inlineStr"/>
-      <c r="I296" s="2" t="inlineStr"/>
-      <c r="J296" s="2" t="inlineStr"/>
-      <c r="K296" s="2" t="inlineStr"/>
-      <c r="L296" s="2" t="inlineStr"/>
+      <c r="G296" s="4" t="inlineStr"/>
+      <c r="H296" s="4" t="inlineStr"/>
+      <c r="I296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10537,12 +9617,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G297" s="2" t="inlineStr"/>
-      <c r="H297" s="2" t="inlineStr"/>
-      <c r="I297" s="2" t="inlineStr"/>
-      <c r="J297" s="2" t="inlineStr"/>
-      <c r="K297" s="2" t="inlineStr"/>
-      <c r="L297" s="2" t="inlineStr"/>
+      <c r="G297" s="4" t="inlineStr"/>
+      <c r="H297" s="4" t="inlineStr"/>
+      <c r="I297" s="4" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10571,12 +9648,9 @@
           <t>en</t>
         </is>
       </c>
-      <c r="G298" s="2" t="inlineStr"/>
-      <c r="H298" s="2" t="inlineStr"/>
-      <c r="I298" s="2" t="inlineStr"/>
-      <c r="J298" s="2" t="inlineStr"/>
-      <c r="K298" s="2" t="inlineStr"/>
-      <c r="L298" s="2" t="inlineStr"/>
+      <c r="G298" s="4" t="inlineStr"/>
+      <c r="H298" s="4" t="inlineStr"/>
+      <c r="I298" s="4" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr"/>
@@ -10597,16 +9671,13 @@
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
-      <c r="G299" s="2" t="inlineStr"/>
-      <c r="H299" s="2" t="inlineStr"/>
-      <c r="I299" s="2" t="inlineStr"/>
-      <c r="J299" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K299" s="2" t="inlineStr"/>
-      <c r="L299" s="4" t="inlineStr">
+      <c r="G299" s="4" t="inlineStr"/>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I299" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10631,16 +9702,13 @@
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
-      <c r="G300" s="2" t="inlineStr"/>
-      <c r="H300" s="2" t="inlineStr"/>
-      <c r="I300" s="2" t="inlineStr"/>
-      <c r="J300" s="3" t="inlineStr">
+      <c r="G300" s="4" t="inlineStr"/>
+      <c r="H300" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="K300" s="2" t="inlineStr"/>
-      <c r="L300" s="3" t="inlineStr">
+      <c r="I300" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -10665,16 +9733,13 @@
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
-      <c r="G301" s="2" t="inlineStr"/>
-      <c r="H301" s="2" t="inlineStr"/>
-      <c r="I301" s="2" t="inlineStr"/>
-      <c r="J301" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K301" s="2" t="inlineStr"/>
-      <c r="L301" s="4" t="inlineStr">
+      <c r="G301" s="4" t="inlineStr"/>
+      <c r="H301" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I301" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10699,16 +9764,13 @@
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
-      <c r="G302" s="2" t="inlineStr"/>
-      <c r="H302" s="2" t="inlineStr"/>
-      <c r="I302" s="2" t="inlineStr"/>
-      <c r="J302" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K302" s="2" t="inlineStr"/>
-      <c r="L302" s="4" t="inlineStr">
+      <c r="G302" s="4" t="inlineStr"/>
+      <c r="H302" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I302" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10733,20 +9795,17 @@
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
-      <c r="G303" s="2" t="inlineStr"/>
-      <c r="H303" s="2" t="inlineStr">
+      <c r="G303" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I303" s="2" t="inlineStr"/>
-      <c r="J303" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K303" s="2" t="inlineStr"/>
-      <c r="L303" s="4" t="inlineStr">
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I303" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10771,16 +9830,13 @@
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
-      <c r="G304" s="2" t="inlineStr"/>
-      <c r="H304" s="2" t="inlineStr"/>
-      <c r="I304" s="2" t="inlineStr"/>
-      <c r="J304" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K304" s="2" t="inlineStr"/>
-      <c r="L304" s="4" t="inlineStr">
+      <c r="G304" s="4" t="inlineStr"/>
+      <c r="H304" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I304" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10805,16 +9861,13 @@
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
-      <c r="G305" s="2" t="inlineStr"/>
-      <c r="H305" s="2" t="inlineStr"/>
-      <c r="I305" s="2" t="inlineStr"/>
-      <c r="J305" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K305" s="2" t="inlineStr"/>
-      <c r="L305" s="4" t="inlineStr">
+      <c r="G305" s="4" t="inlineStr"/>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I305" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10839,16 +9892,13 @@
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
-      <c r="G306" s="2" t="inlineStr"/>
-      <c r="H306" s="2" t="inlineStr"/>
-      <c r="I306" s="2" t="inlineStr"/>
-      <c r="J306" s="3" t="inlineStr">
+      <c r="G306" s="4" t="inlineStr"/>
+      <c r="H306" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="K306" s="2" t="inlineStr"/>
-      <c r="L306" s="3" t="inlineStr">
+      <c r="I306" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -10873,16 +9923,13 @@
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
-      <c r="G307" s="2" t="inlineStr"/>
-      <c r="H307" s="2" t="inlineStr"/>
-      <c r="I307" s="2" t="inlineStr"/>
-      <c r="J307" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K307" s="2" t="inlineStr"/>
-      <c r="L307" s="4" t="inlineStr">
+      <c r="G307" s="4" t="inlineStr"/>
+      <c r="H307" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I307" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10907,16 +9954,13 @@
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
-      <c r="G308" s="2" t="inlineStr"/>
-      <c r="H308" s="2" t="inlineStr"/>
-      <c r="I308" s="2" t="inlineStr"/>
-      <c r="J308" s="3" t="inlineStr">
+      <c r="G308" s="4" t="inlineStr"/>
+      <c r="H308" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="K308" s="2" t="inlineStr"/>
-      <c r="L308" s="3" t="inlineStr">
+      <c r="I308" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -10941,16 +9985,13 @@
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
-      <c r="G309" s="2" t="inlineStr"/>
-      <c r="H309" s="2" t="inlineStr"/>
-      <c r="I309" s="2" t="inlineStr"/>
-      <c r="J309" s="3" t="inlineStr">
+      <c r="G309" s="4" t="inlineStr"/>
+      <c r="H309" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="K309" s="2" t="inlineStr"/>
-      <c r="L309" s="3" t="inlineStr">
+      <c r="I309" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -10975,16 +10016,13 @@
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
-      <c r="G310" s="2" t="inlineStr"/>
-      <c r="H310" s="2" t="inlineStr"/>
-      <c r="I310" s="2" t="inlineStr"/>
-      <c r="J310" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K310" s="2" t="inlineStr"/>
-      <c r="L310" s="4" t="inlineStr">
+      <c r="G310" s="4" t="inlineStr"/>
+      <c r="H310" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I310" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11009,16 +10047,13 @@
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
-      <c r="G311" s="2" t="inlineStr"/>
-      <c r="H311" s="2" t="inlineStr"/>
-      <c r="I311" s="2" t="inlineStr"/>
-      <c r="J311" s="3" t="inlineStr">
+      <c r="G311" s="4" t="inlineStr"/>
+      <c r="H311" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="K311" s="2" t="inlineStr"/>
-      <c r="L311" s="3" t="inlineStr">
+      <c r="I311" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -11043,20 +10078,17 @@
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
-      <c r="G312" s="2" t="inlineStr"/>
-      <c r="H312" s="2" t="inlineStr">
+      <c r="G312" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I312" s="2" t="inlineStr"/>
-      <c r="J312" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K312" s="2" t="inlineStr"/>
-      <c r="L312" s="4" t="inlineStr">
+      <c r="H312" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I312" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11081,12 +10113,9 @@
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
-      <c r="G313" s="2" t="inlineStr"/>
-      <c r="H313" s="2" t="inlineStr"/>
-      <c r="I313" s="2" t="inlineStr"/>
-      <c r="J313" s="2" t="inlineStr"/>
-      <c r="K313" s="2" t="inlineStr"/>
-      <c r="L313" s="2" t="inlineStr"/>
+      <c r="G313" s="4" t="inlineStr"/>
+      <c r="H313" s="4" t="inlineStr"/>
+      <c r="I313" s="4" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr"/>
@@ -11107,16 +10136,13 @@
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
-      <c r="G314" s="2" t="inlineStr"/>
-      <c r="H314" s="2" t="inlineStr"/>
-      <c r="I314" s="2" t="inlineStr"/>
-      <c r="J314" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K314" s="2" t="inlineStr"/>
-      <c r="L314" s="4" t="inlineStr">
+      <c r="G314" s="4" t="inlineStr"/>
+      <c r="H314" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I314" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11141,12 +10167,9 @@
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
-      <c r="G315" s="2" t="inlineStr"/>
-      <c r="H315" s="2" t="inlineStr"/>
-      <c r="I315" s="2" t="inlineStr"/>
-      <c r="J315" s="2" t="inlineStr"/>
-      <c r="K315" s="2" t="inlineStr"/>
-      <c r="L315" s="2" t="inlineStr"/>
+      <c r="G315" s="4" t="inlineStr"/>
+      <c r="H315" s="4" t="inlineStr"/>
+      <c r="I315" s="4" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr"/>
@@ -11167,12 +10190,9 @@
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
-      <c r="G316" s="2" t="inlineStr"/>
-      <c r="H316" s="2" t="inlineStr"/>
-      <c r="I316" s="2" t="inlineStr"/>
-      <c r="J316" s="2" t="inlineStr"/>
-      <c r="K316" s="2" t="inlineStr"/>
-      <c r="L316" s="2" t="inlineStr"/>
+      <c r="G316" s="4" t="inlineStr"/>
+      <c r="H316" s="4" t="inlineStr"/>
+      <c r="I316" s="4" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr"/>
@@ -11193,12 +10213,9 @@
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
-      <c r="G317" s="2" t="inlineStr"/>
-      <c r="H317" s="2" t="inlineStr"/>
-      <c r="I317" s="2" t="inlineStr"/>
-      <c r="J317" s="2" t="inlineStr"/>
-      <c r="K317" s="2" t="inlineStr"/>
-      <c r="L317" s="2" t="inlineStr"/>
+      <c r="G317" s="4" t="inlineStr"/>
+      <c r="H317" s="4" t="inlineStr"/>
+      <c r="I317" s="4" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr"/>
@@ -11219,12 +10236,9 @@
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
-      <c r="G318" s="2" t="inlineStr"/>
-      <c r="H318" s="2" t="inlineStr"/>
-      <c r="I318" s="2" t="inlineStr"/>
-      <c r="J318" s="2" t="inlineStr"/>
-      <c r="K318" s="2" t="inlineStr"/>
-      <c r="L318" s="2" t="inlineStr"/>
+      <c r="G318" s="4" t="inlineStr"/>
+      <c r="H318" s="4" t="inlineStr"/>
+      <c r="I318" s="4" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr"/>
@@ -11245,12 +10259,9 @@
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
-      <c r="G319" s="2" t="inlineStr"/>
-      <c r="H319" s="2" t="inlineStr"/>
-      <c r="I319" s="2" t="inlineStr"/>
-      <c r="J319" s="2" t="inlineStr"/>
-      <c r="K319" s="2" t="inlineStr"/>
-      <c r="L319" s="2" t="inlineStr"/>
+      <c r="G319" s="4" t="inlineStr"/>
+      <c r="H319" s="4" t="inlineStr"/>
+      <c r="I319" s="4" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr"/>
@@ -11271,12 +10282,9 @@
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
-      <c r="G320" s="2" t="inlineStr"/>
-      <c r="H320" s="2" t="inlineStr"/>
-      <c r="I320" s="2" t="inlineStr"/>
-      <c r="J320" s="2" t="inlineStr"/>
-      <c r="K320" s="2" t="inlineStr"/>
-      <c r="L320" s="2" t="inlineStr"/>
+      <c r="G320" s="4" t="inlineStr"/>
+      <c r="H320" s="4" t="inlineStr"/>
+      <c r="I320" s="4" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr"/>
@@ -11297,12 +10305,9 @@
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
-      <c r="G321" s="2" t="inlineStr"/>
-      <c r="H321" s="2" t="inlineStr"/>
-      <c r="I321" s="2" t="inlineStr"/>
-      <c r="J321" s="2" t="inlineStr"/>
-      <c r="K321" s="2" t="inlineStr"/>
-      <c r="L321" s="2" t="inlineStr"/>
+      <c r="G321" s="4" t="inlineStr"/>
+      <c r="H321" s="4" t="inlineStr"/>
+      <c r="I321" s="4" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr"/>
@@ -11323,12 +10328,9 @@
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
-      <c r="G322" s="2" t="inlineStr"/>
-      <c r="H322" s="2" t="inlineStr"/>
-      <c r="I322" s="2" t="inlineStr"/>
-      <c r="J322" s="2" t="inlineStr"/>
-      <c r="K322" s="2" t="inlineStr"/>
-      <c r="L322" s="2" t="inlineStr"/>
+      <c r="G322" s="4" t="inlineStr"/>
+      <c r="H322" s="4" t="inlineStr"/>
+      <c r="I322" s="4" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr"/>
@@ -11349,12 +10351,9 @@
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
-      <c r="G323" s="2" t="inlineStr"/>
-      <c r="H323" s="2" t="inlineStr"/>
-      <c r="I323" s="2" t="inlineStr"/>
-      <c r="J323" s="2" t="inlineStr"/>
-      <c r="K323" s="2" t="inlineStr"/>
-      <c r="L323" s="2" t="inlineStr"/>
+      <c r="G323" s="4" t="inlineStr"/>
+      <c r="H323" s="4" t="inlineStr"/>
+      <c r="I323" s="4" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr"/>
@@ -11375,12 +10374,9 @@
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
-      <c r="G324" s="2" t="inlineStr"/>
-      <c r="H324" s="2" t="inlineStr"/>
-      <c r="I324" s="2" t="inlineStr"/>
-      <c r="J324" s="2" t="inlineStr"/>
-      <c r="K324" s="2" t="inlineStr"/>
-      <c r="L324" s="3" t="inlineStr">
+      <c r="G324" s="4" t="inlineStr"/>
+      <c r="H324" s="4" t="inlineStr"/>
+      <c r="I324" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
@@ -11405,12 +10401,9 @@
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
-      <c r="G325" s="2" t="inlineStr"/>
-      <c r="H325" s="2" t="inlineStr"/>
-      <c r="I325" s="2" t="inlineStr"/>
-      <c r="J325" s="2" t="inlineStr"/>
-      <c r="K325" s="2" t="inlineStr"/>
-      <c r="L325" s="2" t="inlineStr"/>
+      <c r="G325" s="4" t="inlineStr"/>
+      <c r="H325" s="4" t="inlineStr"/>
+      <c r="I325" s="4" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr"/>
@@ -11431,12 +10424,9 @@
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
-      <c r="G326" s="2" t="inlineStr"/>
-      <c r="H326" s="2" t="inlineStr"/>
-      <c r="I326" s="2" t="inlineStr"/>
-      <c r="J326" s="2" t="inlineStr"/>
-      <c r="K326" s="2" t="inlineStr"/>
-      <c r="L326" s="2" t="inlineStr"/>
+      <c r="G326" s="4" t="inlineStr"/>
+      <c r="H326" s="4" t="inlineStr"/>
+      <c r="I326" s="4" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr"/>
@@ -11457,12 +10447,9 @@
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
-      <c r="G327" s="2" t="inlineStr"/>
-      <c r="H327" s="2" t="inlineStr"/>
-      <c r="I327" s="2" t="inlineStr"/>
-      <c r="J327" s="2" t="inlineStr"/>
-      <c r="K327" s="2" t="inlineStr"/>
-      <c r="L327" s="2" t="inlineStr"/>
+      <c r="G327" s="4" t="inlineStr"/>
+      <c r="H327" s="4" t="inlineStr"/>
+      <c r="I327" s="4" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr"/>
@@ -11483,12 +10470,9 @@
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
-      <c r="G328" s="2" t="inlineStr"/>
-      <c r="H328" s="2" t="inlineStr"/>
-      <c r="I328" s="2" t="inlineStr"/>
-      <c r="J328" s="2" t="inlineStr"/>
-      <c r="K328" s="2" t="inlineStr"/>
-      <c r="L328" s="2" t="inlineStr"/>
+      <c r="G328" s="4" t="inlineStr"/>
+      <c r="H328" s="4" t="inlineStr"/>
+      <c r="I328" s="4" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr"/>
@@ -11509,16 +10493,13 @@
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
-      <c r="G329" s="2" t="inlineStr"/>
-      <c r="H329" s="2" t="inlineStr"/>
-      <c r="I329" s="2" t="inlineStr"/>
-      <c r="J329" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K329" s="2" t="inlineStr"/>
-      <c r="L329" s="4" t="inlineStr">
+      <c r="G329" s="4" t="inlineStr"/>
+      <c r="H329" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I329" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11543,12 +10524,9 @@
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
-      <c r="G330" s="2" t="inlineStr"/>
-      <c r="H330" s="2" t="inlineStr"/>
-      <c r="I330" s="2" t="inlineStr"/>
-      <c r="J330" s="2" t="inlineStr"/>
-      <c r="K330" s="2" t="inlineStr"/>
-      <c r="L330" s="2" t="inlineStr"/>
+      <c r="G330" s="4" t="inlineStr"/>
+      <c r="H330" s="4" t="inlineStr"/>
+      <c r="I330" s="4" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr"/>
@@ -11569,12 +10547,9 @@
         </is>
       </c>
       <c r="F331" t="inlineStr"/>
-      <c r="G331" s="2" t="inlineStr"/>
-      <c r="H331" s="2" t="inlineStr"/>
-      <c r="I331" s="2" t="inlineStr"/>
-      <c r="J331" s="2" t="inlineStr"/>
-      <c r="K331" s="2" t="inlineStr"/>
-      <c r="L331" s="2" t="inlineStr"/>
+      <c r="G331" s="4" t="inlineStr"/>
+      <c r="H331" s="4" t="inlineStr"/>
+      <c r="I331" s="4" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr"/>
@@ -11595,12 +10570,9 @@
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
-      <c r="G332" s="2" t="inlineStr"/>
-      <c r="H332" s="2" t="inlineStr"/>
-      <c r="I332" s="2" t="inlineStr"/>
-      <c r="J332" s="2" t="inlineStr"/>
-      <c r="K332" s="2" t="inlineStr"/>
-      <c r="L332" s="2" t="inlineStr"/>
+      <c r="G332" s="4" t="inlineStr"/>
+      <c r="H332" s="4" t="inlineStr"/>
+      <c r="I332" s="4" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr"/>
@@ -11621,12 +10593,9 @@
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
-      <c r="G333" s="2" t="inlineStr"/>
-      <c r="H333" s="2" t="inlineStr"/>
-      <c r="I333" s="2" t="inlineStr"/>
-      <c r="J333" s="2" t="inlineStr"/>
-      <c r="K333" s="2" t="inlineStr"/>
-      <c r="L333" s="2" t="inlineStr"/>
+      <c r="G333" s="4" t="inlineStr"/>
+      <c r="H333" s="4" t="inlineStr"/>
+      <c r="I333" s="4" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr"/>
@@ -11647,12 +10616,9 @@
         </is>
       </c>
       <c r="F334" t="inlineStr"/>
-      <c r="G334" s="2" t="inlineStr"/>
-      <c r="H334" s="2" t="inlineStr"/>
-      <c r="I334" s="2" t="inlineStr"/>
-      <c r="J334" s="2" t="inlineStr"/>
-      <c r="K334" s="2" t="inlineStr"/>
-      <c r="L334" s="2" t="inlineStr"/>
+      <c r="G334" s="4" t="inlineStr"/>
+      <c r="H334" s="4" t="inlineStr"/>
+      <c r="I334" s="4" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr"/>
@@ -11673,12 +10639,9 @@
         </is>
       </c>
       <c r="F335" t="inlineStr"/>
-      <c r="G335" s="2" t="inlineStr"/>
-      <c r="H335" s="2" t="inlineStr"/>
-      <c r="I335" s="2" t="inlineStr"/>
-      <c r="J335" s="2" t="inlineStr"/>
-      <c r="K335" s="2" t="inlineStr"/>
-      <c r="L335" s="2" t="inlineStr"/>
+      <c r="G335" s="4" t="inlineStr"/>
+      <c r="H335" s="4" t="inlineStr"/>
+      <c r="I335" s="4" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr"/>
@@ -11699,12 +10662,9 @@
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
-      <c r="G336" s="2" t="inlineStr"/>
-      <c r="H336" s="2" t="inlineStr"/>
-      <c r="I336" s="2" t="inlineStr"/>
-      <c r="J336" s="2" t="inlineStr"/>
-      <c r="K336" s="2" t="inlineStr"/>
-      <c r="L336" s="2" t="inlineStr"/>
+      <c r="G336" s="4" t="inlineStr"/>
+      <c r="H336" s="4" t="inlineStr"/>
+      <c r="I336" s="4" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr"/>
@@ -11725,12 +10685,9 @@
         </is>
       </c>
       <c r="F337" t="inlineStr"/>
-      <c r="G337" s="2" t="inlineStr"/>
-      <c r="H337" s="2" t="inlineStr"/>
-      <c r="I337" s="2" t="inlineStr"/>
-      <c r="J337" s="2" t="inlineStr"/>
-      <c r="K337" s="2" t="inlineStr"/>
-      <c r="L337" s="2" t="inlineStr"/>
+      <c r="G337" s="4" t="inlineStr"/>
+      <c r="H337" s="4" t="inlineStr"/>
+      <c r="I337" s="4" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr"/>
@@ -11747,20 +10704,17 @@
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr"/>
-      <c r="G338" s="2" t="inlineStr"/>
-      <c r="H338" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I338" s="2" t="inlineStr"/>
-      <c r="J338" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K338" s="2" t="inlineStr"/>
-      <c r="L338" s="4" t="inlineStr">
+      <c r="G338" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H338" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I338" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11781,12 +10735,9 @@
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr"/>
-      <c r="G339" s="2" t="inlineStr"/>
-      <c r="H339" s="2" t="inlineStr"/>
-      <c r="I339" s="2" t="inlineStr"/>
-      <c r="J339" s="2" t="inlineStr"/>
-      <c r="K339" s="2" t="inlineStr"/>
-      <c r="L339" s="2" t="inlineStr"/>
+      <c r="G339" s="4" t="inlineStr"/>
+      <c r="H339" s="4" t="inlineStr"/>
+      <c r="I339" s="4" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr"/>
@@ -11803,16 +10754,13 @@
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr"/>
-      <c r="G340" s="2" t="inlineStr"/>
-      <c r="H340" s="2" t="inlineStr"/>
-      <c r="I340" s="2" t="inlineStr"/>
-      <c r="J340" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K340" s="2" t="inlineStr"/>
-      <c r="L340" s="4" t="inlineStr">
+      <c r="G340" s="4" t="inlineStr"/>
+      <c r="H340" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I340" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11833,16 +10781,13 @@
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr"/>
-      <c r="G341" s="2" t="inlineStr"/>
-      <c r="H341" s="2" t="inlineStr"/>
-      <c r="I341" s="2" t="inlineStr"/>
-      <c r="J341" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K341" s="2" t="inlineStr"/>
-      <c r="L341" s="4" t="inlineStr">
+      <c r="G341" s="4" t="inlineStr"/>
+      <c r="H341" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I341" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11863,16 +10808,13 @@
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr"/>
-      <c r="G342" s="2" t="inlineStr"/>
-      <c r="H342" s="2" t="inlineStr"/>
-      <c r="I342" s="2" t="inlineStr"/>
-      <c r="J342" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K342" s="2" t="inlineStr"/>
-      <c r="L342" s="4" t="inlineStr">
+      <c r="G342" s="4" t="inlineStr"/>
+      <c r="H342" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I342" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11893,12 +10835,9 @@
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr"/>
-      <c r="G343" s="2" t="inlineStr"/>
-      <c r="H343" s="2" t="inlineStr"/>
-      <c r="I343" s="2" t="inlineStr"/>
-      <c r="J343" s="2" t="inlineStr"/>
-      <c r="K343" s="2" t="inlineStr"/>
-      <c r="L343" s="2" t="inlineStr"/>
+      <c r="G343" s="4" t="inlineStr"/>
+      <c r="H343" s="4" t="inlineStr"/>
+      <c r="I343" s="4" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr"/>
@@ -11915,12 +10854,9 @@
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr"/>
-      <c r="G344" s="2" t="inlineStr"/>
-      <c r="H344" s="2" t="inlineStr"/>
-      <c r="I344" s="2" t="inlineStr"/>
-      <c r="J344" s="2" t="inlineStr"/>
-      <c r="K344" s="2" t="inlineStr"/>
-      <c r="L344" s="2" t="inlineStr"/>
+      <c r="G344" s="4" t="inlineStr"/>
+      <c r="H344" s="4" t="inlineStr"/>
+      <c r="I344" s="4" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr"/>
@@ -11937,12 +10873,9 @@
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr"/>
-      <c r="G345" s="2" t="inlineStr"/>
-      <c r="H345" s="2" t="inlineStr"/>
-      <c r="I345" s="2" t="inlineStr"/>
-      <c r="J345" s="2" t="inlineStr"/>
-      <c r="K345" s="2" t="inlineStr"/>
-      <c r="L345" s="2" t="inlineStr"/>
+      <c r="G345" s="4" t="inlineStr"/>
+      <c r="H345" s="4" t="inlineStr"/>
+      <c r="I345" s="4" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr"/>
@@ -11959,12 +10892,9 @@
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr"/>
-      <c r="G346" s="2" t="inlineStr"/>
-      <c r="H346" s="2" t="inlineStr"/>
-      <c r="I346" s="2" t="inlineStr"/>
-      <c r="J346" s="2" t="inlineStr"/>
-      <c r="K346" s="2" t="inlineStr"/>
-      <c r="L346" s="2" t="inlineStr"/>
+      <c r="G346" s="4" t="inlineStr"/>
+      <c r="H346" s="4" t="inlineStr"/>
+      <c r="I346" s="4" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr"/>
@@ -11981,12 +10911,9 @@
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr"/>
-      <c r="G347" s="2" t="inlineStr"/>
-      <c r="H347" s="2" t="inlineStr"/>
-      <c r="I347" s="2" t="inlineStr"/>
-      <c r="J347" s="2" t="inlineStr"/>
-      <c r="K347" s="2" t="inlineStr"/>
-      <c r="L347" s="2" t="inlineStr"/>
+      <c r="G347" s="4" t="inlineStr"/>
+      <c r="H347" s="4" t="inlineStr"/>
+      <c r="I347" s="4" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr"/>
@@ -12003,12 +10930,9 @@
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr"/>
-      <c r="G348" s="2" t="inlineStr"/>
-      <c r="H348" s="2" t="inlineStr"/>
-      <c r="I348" s="2" t="inlineStr"/>
-      <c r="J348" s="2" t="inlineStr"/>
-      <c r="K348" s="2" t="inlineStr"/>
-      <c r="L348" s="4" t="inlineStr">
+      <c r="G348" s="4" t="inlineStr"/>
+      <c r="H348" s="4" t="inlineStr"/>
+      <c r="I348" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12029,12 +10953,9 @@
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr"/>
-      <c r="G349" s="2" t="inlineStr"/>
-      <c r="H349" s="2" t="inlineStr"/>
-      <c r="I349" s="2" t="inlineStr"/>
-      <c r="J349" s="2" t="inlineStr"/>
-      <c r="K349" s="2" t="inlineStr"/>
-      <c r="L349" s="2" t="inlineStr"/>
+      <c r="G349" s="4" t="inlineStr"/>
+      <c r="H349" s="4" t="inlineStr"/>
+      <c r="I349" s="4" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr"/>
@@ -12051,12 +10972,9 @@
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr"/>
-      <c r="G350" s="2" t="inlineStr"/>
-      <c r="H350" s="2" t="inlineStr"/>
-      <c r="I350" s="2" t="inlineStr"/>
-      <c r="J350" s="2" t="inlineStr"/>
-      <c r="K350" s="2" t="inlineStr"/>
-      <c r="L350" s="2" t="inlineStr"/>
+      <c r="G350" s="4" t="inlineStr"/>
+      <c r="H350" s="4" t="inlineStr"/>
+      <c r="I350" s="4" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr"/>
@@ -12073,12 +10991,9 @@
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr"/>
-      <c r="G351" s="2" t="inlineStr"/>
-      <c r="H351" s="2" t="inlineStr"/>
-      <c r="I351" s="2" t="inlineStr"/>
-      <c r="J351" s="2" t="inlineStr"/>
-      <c r="K351" s="2" t="inlineStr"/>
-      <c r="L351" s="4" t="inlineStr">
+      <c r="G351" s="4" t="inlineStr"/>
+      <c r="H351" s="4" t="inlineStr"/>
+      <c r="I351" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12099,12 +11014,9 @@
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr"/>
-      <c r="G352" s="2" t="inlineStr"/>
-      <c r="H352" s="2" t="inlineStr"/>
-      <c r="I352" s="2" t="inlineStr"/>
-      <c r="J352" s="2" t="inlineStr"/>
-      <c r="K352" s="2" t="inlineStr"/>
-      <c r="L352" s="4" t="inlineStr">
+      <c r="G352" s="4" t="inlineStr"/>
+      <c r="H352" s="4" t="inlineStr"/>
+      <c r="I352" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12125,12 +11037,9 @@
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr"/>
-      <c r="G353" s="2" t="inlineStr"/>
-      <c r="H353" s="2" t="inlineStr"/>
-      <c r="I353" s="2" t="inlineStr"/>
-      <c r="J353" s="2" t="inlineStr"/>
-      <c r="K353" s="2" t="inlineStr"/>
-      <c r="L353" s="2" t="inlineStr"/>
+      <c r="G353" s="4" t="inlineStr"/>
+      <c r="H353" s="4" t="inlineStr"/>
+      <c r="I353" s="4" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr"/>
@@ -12147,12 +11056,9 @@
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr"/>
-      <c r="G354" s="2" t="inlineStr"/>
-      <c r="H354" s="2" t="inlineStr"/>
-      <c r="I354" s="2" t="inlineStr"/>
-      <c r="J354" s="2" t="inlineStr"/>
-      <c r="K354" s="2" t="inlineStr"/>
-      <c r="L354" s="2" t="inlineStr"/>
+      <c r="G354" s="4" t="inlineStr"/>
+      <c r="H354" s="4" t="inlineStr"/>
+      <c r="I354" s="4" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr"/>
@@ -12169,12 +11075,9 @@
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr"/>
-      <c r="G355" s="2" t="inlineStr"/>
-      <c r="H355" s="2" t="inlineStr"/>
-      <c r="I355" s="2" t="inlineStr"/>
-      <c r="J355" s="2" t="inlineStr"/>
-      <c r="K355" s="2" t="inlineStr"/>
-      <c r="L355" s="2" t="inlineStr"/>
+      <c r="G355" s="4" t="inlineStr"/>
+      <c r="H355" s="4" t="inlineStr"/>
+      <c r="I355" s="4" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr"/>
@@ -12191,12 +11094,9 @@
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr"/>
-      <c r="G356" s="2" t="inlineStr"/>
-      <c r="H356" s="2" t="inlineStr"/>
-      <c r="I356" s="2" t="inlineStr"/>
-      <c r="J356" s="2" t="inlineStr"/>
-      <c r="K356" s="2" t="inlineStr"/>
-      <c r="L356" s="2" t="inlineStr"/>
+      <c r="G356" s="4" t="inlineStr"/>
+      <c r="H356" s="4" t="inlineStr"/>
+      <c r="I356" s="4" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr"/>
@@ -12213,12 +11113,9 @@
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr"/>
-      <c r="G357" s="2" t="inlineStr"/>
-      <c r="H357" s="2" t="inlineStr"/>
-      <c r="I357" s="2" t="inlineStr"/>
-      <c r="J357" s="2" t="inlineStr"/>
-      <c r="K357" s="2" t="inlineStr"/>
-      <c r="L357" s="2" t="inlineStr"/>
+      <c r="G357" s="4" t="inlineStr"/>
+      <c r="H357" s="4" t="inlineStr"/>
+      <c r="I357" s="4" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr"/>
@@ -12235,16 +11132,13 @@
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr"/>
-      <c r="G358" s="2" t="inlineStr"/>
-      <c r="H358" s="2" t="inlineStr"/>
-      <c r="I358" s="2" t="inlineStr"/>
-      <c r="J358" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K358" s="2" t="inlineStr"/>
-      <c r="L358" s="4" t="inlineStr">
+      <c r="G358" s="4" t="inlineStr"/>
+      <c r="H358" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I358" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12265,16 +11159,13 @@
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr"/>
-      <c r="G359" s="2" t="inlineStr"/>
-      <c r="H359" s="2" t="inlineStr"/>
-      <c r="I359" s="2" t="inlineStr"/>
-      <c r="J359" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K359" s="2" t="inlineStr"/>
-      <c r="L359" s="4" t="inlineStr">
+      <c r="G359" s="4" t="inlineStr"/>
+      <c r="H359" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I359" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12295,16 +11186,13 @@
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr"/>
-      <c r="G360" s="2" t="inlineStr"/>
-      <c r="H360" s="2" t="inlineStr"/>
-      <c r="I360" s="2" t="inlineStr"/>
-      <c r="J360" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K360" s="2" t="inlineStr"/>
-      <c r="L360" s="4" t="inlineStr">
+      <c r="G360" s="4" t="inlineStr"/>
+      <c r="H360" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I360" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12325,16 +11213,13 @@
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr"/>
-      <c r="G361" s="2" t="inlineStr"/>
-      <c r="H361" s="2" t="inlineStr"/>
-      <c r="I361" s="2" t="inlineStr"/>
-      <c r="J361" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K361" s="2" t="inlineStr"/>
-      <c r="L361" s="4" t="inlineStr">
+      <c r="G361" s="4" t="inlineStr"/>
+      <c r="H361" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I361" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12355,16 +11240,13 @@
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
-      <c r="G362" s="2" t="inlineStr"/>
-      <c r="H362" s="2" t="inlineStr"/>
-      <c r="I362" s="2" t="inlineStr"/>
-      <c r="J362" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K362" s="2" t="inlineStr"/>
-      <c r="L362" s="4" t="inlineStr">
+      <c r="G362" s="4" t="inlineStr"/>
+      <c r="H362" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I362" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12385,16 +11267,13 @@
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr"/>
-      <c r="G363" s="2" t="inlineStr"/>
-      <c r="H363" s="2" t="inlineStr"/>
-      <c r="I363" s="2" t="inlineStr"/>
-      <c r="J363" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K363" s="2" t="inlineStr"/>
-      <c r="L363" s="4" t="inlineStr">
+      <c r="G363" s="4" t="inlineStr"/>
+      <c r="H363" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I363" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12415,16 +11294,13 @@
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr"/>
-      <c r="G364" s="2" t="inlineStr"/>
-      <c r="H364" s="2" t="inlineStr"/>
-      <c r="I364" s="2" t="inlineStr"/>
-      <c r="J364" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K364" s="2" t="inlineStr"/>
-      <c r="L364" s="4" t="inlineStr">
+      <c r="G364" s="4" t="inlineStr"/>
+      <c r="H364" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I364" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12445,16 +11321,13 @@
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
-      <c r="G365" s="2" t="inlineStr"/>
-      <c r="H365" s="2" t="inlineStr"/>
-      <c r="I365" s="2" t="inlineStr"/>
-      <c r="J365" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K365" s="2" t="inlineStr"/>
-      <c r="L365" s="4" t="inlineStr">
+      <c r="G365" s="4" t="inlineStr"/>
+      <c r="H365" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I365" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12475,16 +11348,13 @@
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
-      <c r="G366" s="2" t="inlineStr"/>
-      <c r="H366" s="2" t="inlineStr"/>
-      <c r="I366" s="2" t="inlineStr"/>
-      <c r="J366" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K366" s="2" t="inlineStr"/>
-      <c r="L366" s="4" t="inlineStr">
+      <c r="G366" s="4" t="inlineStr"/>
+      <c r="H366" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I366" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12505,16 +11375,13 @@
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
-      <c r="G367" s="2" t="inlineStr"/>
-      <c r="H367" s="2" t="inlineStr"/>
-      <c r="I367" s="2" t="inlineStr"/>
-      <c r="J367" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K367" s="2" t="inlineStr"/>
-      <c r="L367" s="4" t="inlineStr">
+      <c r="G367" s="4" t="inlineStr"/>
+      <c r="H367" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I367" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12535,16 +11402,13 @@
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr"/>
-      <c r="G368" s="2" t="inlineStr"/>
-      <c r="H368" s="2" t="inlineStr"/>
-      <c r="I368" s="2" t="inlineStr"/>
-      <c r="J368" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K368" s="2" t="inlineStr"/>
-      <c r="L368" s="4" t="inlineStr">
+      <c r="G368" s="4" t="inlineStr"/>
+      <c r="H368" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I368" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12565,16 +11429,13 @@
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr"/>
-      <c r="G369" s="2" t="inlineStr"/>
-      <c r="H369" s="2" t="inlineStr"/>
-      <c r="I369" s="2" t="inlineStr"/>
-      <c r="J369" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K369" s="2" t="inlineStr"/>
-      <c r="L369" s="4" t="inlineStr">
+      <c r="G369" s="4" t="inlineStr"/>
+      <c r="H369" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I369" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12595,16 +11456,13 @@
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr"/>
-      <c r="G370" s="2" t="inlineStr"/>
-      <c r="H370" s="2" t="inlineStr"/>
-      <c r="I370" s="2" t="inlineStr"/>
-      <c r="J370" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="K370" s="2" t="inlineStr"/>
-      <c r="L370" s="4" t="inlineStr">
+      <c r="G370" s="4" t="inlineStr"/>
+      <c r="H370" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I370" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12625,12 +11483,9 @@
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr"/>
-      <c r="G371" s="2" t="inlineStr"/>
-      <c r="H371" s="2" t="inlineStr"/>
-      <c r="I371" s="2" t="inlineStr"/>
-      <c r="J371" s="2" t="inlineStr"/>
-      <c r="K371" s="2" t="inlineStr"/>
-      <c r="L371" s="2" t="inlineStr"/>
+      <c r="G371" s="4" t="inlineStr"/>
+      <c r="H371" s="4" t="inlineStr"/>
+      <c r="I371" s="4" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr"/>
@@ -12647,12 +11502,9 @@
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr"/>
-      <c r="G372" s="2" t="inlineStr"/>
-      <c r="H372" s="2" t="inlineStr"/>
-      <c r="I372" s="2" t="inlineStr"/>
-      <c r="J372" s="2" t="inlineStr"/>
-      <c r="K372" s="2" t="inlineStr"/>
-      <c r="L372" s="2" t="inlineStr"/>
+      <c r="G372" s="4" t="inlineStr"/>
+      <c r="H372" s="4" t="inlineStr"/>
+      <c r="I372" s="4" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr"/>
@@ -12669,12 +11521,9 @@
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr"/>
-      <c r="G373" s="2" t="inlineStr"/>
-      <c r="H373" s="2" t="inlineStr"/>
-      <c r="I373" s="2" t="inlineStr"/>
-      <c r="J373" s="2" t="inlineStr"/>
-      <c r="K373" s="2" t="inlineStr"/>
-      <c r="L373" s="2" t="inlineStr"/>
+      <c r="G373" s="4" t="inlineStr"/>
+      <c r="H373" s="4" t="inlineStr"/>
+      <c r="I373" s="4" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr"/>
@@ -12691,12 +11540,9 @@
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr"/>
-      <c r="G374" s="2" t="inlineStr"/>
-      <c r="H374" s="2" t="inlineStr"/>
-      <c r="I374" s="2" t="inlineStr"/>
-      <c r="J374" s="2" t="inlineStr"/>
-      <c r="K374" s="2" t="inlineStr"/>
-      <c r="L374" s="2" t="inlineStr"/>
+      <c r="G374" s="4" t="inlineStr"/>
+      <c r="H374" s="4" t="inlineStr"/>
+      <c r="I374" s="4" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr"/>
@@ -12713,12 +11559,9 @@
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr"/>
-      <c r="G375" s="2" t="inlineStr"/>
-      <c r="H375" s="2" t="inlineStr"/>
-      <c r="I375" s="2" t="inlineStr"/>
-      <c r="J375" s="2" t="inlineStr"/>
-      <c r="K375" s="2" t="inlineStr"/>
-      <c r="L375" s="2" t="inlineStr"/>
+      <c r="G375" s="4" t="inlineStr"/>
+      <c r="H375" s="4" t="inlineStr"/>
+      <c r="I375" s="4" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr"/>
@@ -12735,12 +11578,9 @@
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
-      <c r="G376" s="2" t="inlineStr"/>
-      <c r="H376" s="2" t="inlineStr"/>
-      <c r="I376" s="2" t="inlineStr"/>
-      <c r="J376" s="2" t="inlineStr"/>
-      <c r="K376" s="2" t="inlineStr"/>
-      <c r="L376" s="2" t="inlineStr"/>
+      <c r="G376" s="4" t="inlineStr"/>
+      <c r="H376" s="4" t="inlineStr"/>
+      <c r="I376" s="4" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr"/>
@@ -12757,12 +11597,9 @@
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
-      <c r="G377" s="2" t="inlineStr"/>
-      <c r="H377" s="2" t="inlineStr"/>
-      <c r="I377" s="2" t="inlineStr"/>
-      <c r="J377" s="2" t="inlineStr"/>
-      <c r="K377" s="2" t="inlineStr"/>
-      <c r="L377" s="2" t="inlineStr"/>
+      <c r="G377" s="4" t="inlineStr"/>
+      <c r="H377" s="4" t="inlineStr"/>
+      <c r="I377" s="4" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr"/>
@@ -12779,12 +11616,9 @@
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr"/>
-      <c r="G378" s="2" t="inlineStr"/>
-      <c r="H378" s="2" t="inlineStr"/>
-      <c r="I378" s="2" t="inlineStr"/>
-      <c r="J378" s="2" t="inlineStr"/>
-      <c r="K378" s="2" t="inlineStr"/>
-      <c r="L378" s="2" t="inlineStr"/>
+      <c r="G378" s="4" t="inlineStr"/>
+      <c r="H378" s="4" t="inlineStr"/>
+      <c r="I378" s="4" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr"/>
@@ -12801,12 +11635,9 @@
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr"/>
-      <c r="G379" s="2" t="inlineStr"/>
-      <c r="H379" s="2" t="inlineStr"/>
-      <c r="I379" s="2" t="inlineStr"/>
-      <c r="J379" s="2" t="inlineStr"/>
-      <c r="K379" s="2" t="inlineStr"/>
-      <c r="L379" s="2" t="inlineStr"/>
+      <c r="G379" s="4" t="inlineStr"/>
+      <c r="H379" s="4" t="inlineStr"/>
+      <c r="I379" s="4" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr"/>
@@ -12823,12 +11654,9 @@
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr"/>
-      <c r="G380" s="2" t="inlineStr"/>
-      <c r="H380" s="2" t="inlineStr"/>
-      <c r="I380" s="2" t="inlineStr"/>
-      <c r="J380" s="2" t="inlineStr"/>
-      <c r="K380" s="2" t="inlineStr"/>
-      <c r="L380" s="2" t="inlineStr"/>
+      <c r="G380" s="4" t="inlineStr"/>
+      <c r="H380" s="4" t="inlineStr"/>
+      <c r="I380" s="4" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr"/>
@@ -12845,12 +11673,9 @@
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr"/>
-      <c r="G381" s="2" t="inlineStr"/>
-      <c r="H381" s="2" t="inlineStr"/>
-      <c r="I381" s="2" t="inlineStr"/>
-      <c r="J381" s="2" t="inlineStr"/>
-      <c r="K381" s="2" t="inlineStr"/>
-      <c r="L381" s="2" t="inlineStr"/>
+      <c r="G381" s="4" t="inlineStr"/>
+      <c r="H381" s="4" t="inlineStr"/>
+      <c r="I381" s="4" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr"/>
@@ -12867,12 +11692,9 @@
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr"/>
-      <c r="G382" s="2" t="inlineStr"/>
-      <c r="H382" s="2" t="inlineStr"/>
-      <c r="I382" s="2" t="inlineStr"/>
-      <c r="J382" s="2" t="inlineStr"/>
-      <c r="K382" s="2" t="inlineStr"/>
-      <c r="L382" s="2" t="inlineStr"/>
+      <c r="G382" s="4" t="inlineStr"/>
+      <c r="H382" s="4" t="inlineStr"/>
+      <c r="I382" s="4" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr"/>
@@ -12889,12 +11711,9 @@
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr"/>
-      <c r="G383" s="2" t="inlineStr"/>
-      <c r="H383" s="2" t="inlineStr"/>
-      <c r="I383" s="2" t="inlineStr"/>
-      <c r="J383" s="2" t="inlineStr"/>
-      <c r="K383" s="2" t="inlineStr"/>
-      <c r="L383" s="2" t="inlineStr"/>
+      <c r="G383" s="4" t="inlineStr"/>
+      <c r="H383" s="4" t="inlineStr"/>
+      <c r="I383" s="4" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr"/>
@@ -12911,12 +11730,9 @@
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr"/>
-      <c r="G384" s="2" t="inlineStr"/>
-      <c r="H384" s="2" t="inlineStr"/>
-      <c r="I384" s="2" t="inlineStr"/>
-      <c r="J384" s="2" t="inlineStr"/>
-      <c r="K384" s="2" t="inlineStr"/>
-      <c r="L384" s="2" t="inlineStr"/>
+      <c r="G384" s="4" t="inlineStr"/>
+      <c r="H384" s="4" t="inlineStr"/>
+      <c r="I384" s="4" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr"/>
@@ -12933,12 +11749,9 @@
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr"/>
-      <c r="G385" s="2" t="inlineStr"/>
-      <c r="H385" s="2" t="inlineStr"/>
-      <c r="I385" s="2" t="inlineStr"/>
-      <c r="J385" s="2" t="inlineStr"/>
-      <c r="K385" s="2" t="inlineStr"/>
-      <c r="L385" s="2" t="inlineStr"/>
+      <c r="G385" s="4" t="inlineStr"/>
+      <c r="H385" s="4" t="inlineStr"/>
+      <c r="I385" s="4" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr"/>
@@ -12955,12 +11768,9 @@
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr"/>
-      <c r="G386" s="2" t="inlineStr"/>
-      <c r="H386" s="2" t="inlineStr"/>
-      <c r="I386" s="2" t="inlineStr"/>
-      <c r="J386" s="2" t="inlineStr"/>
-      <c r="K386" s="2" t="inlineStr"/>
-      <c r="L386" s="2" t="inlineStr"/>
+      <c r="G386" s="4" t="inlineStr"/>
+      <c r="H386" s="4" t="inlineStr"/>
+      <c r="I386" s="4" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr"/>
@@ -12977,12 +11787,9 @@
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr"/>
-      <c r="G387" s="2" t="inlineStr"/>
-      <c r="H387" s="2" t="inlineStr"/>
-      <c r="I387" s="2" t="inlineStr"/>
-      <c r="J387" s="2" t="inlineStr"/>
-      <c r="K387" s="2" t="inlineStr"/>
-      <c r="L387" s="2" t="inlineStr"/>
+      <c r="G387" s="4" t="inlineStr"/>
+      <c r="H387" s="4" t="inlineStr"/>
+      <c r="I387" s="4" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr"/>
@@ -12999,12 +11806,9 @@
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr"/>
-      <c r="G388" s="2" t="inlineStr"/>
-      <c r="H388" s="2" t="inlineStr"/>
-      <c r="I388" s="2" t="inlineStr"/>
-      <c r="J388" s="2" t="inlineStr"/>
-      <c r="K388" s="2" t="inlineStr"/>
-      <c r="L388" s="2" t="inlineStr"/>
+      <c r="G388" s="4" t="inlineStr"/>
+      <c r="H388" s="4" t="inlineStr"/>
+      <c r="I388" s="4" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr"/>
@@ -13021,12 +11825,9 @@
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr"/>
-      <c r="G389" s="2" t="inlineStr"/>
-      <c r="H389" s="2" t="inlineStr"/>
-      <c r="I389" s="2" t="inlineStr"/>
-      <c r="J389" s="2" t="inlineStr"/>
-      <c r="K389" s="2" t="inlineStr"/>
-      <c r="L389" s="2" t="inlineStr"/>
+      <c r="G389" s="4" t="inlineStr"/>
+      <c r="H389" s="4" t="inlineStr"/>
+      <c r="I389" s="4" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr"/>
@@ -13043,12 +11844,9 @@
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr"/>
-      <c r="G390" s="2" t="inlineStr"/>
-      <c r="H390" s="2" t="inlineStr"/>
-      <c r="I390" s="2" t="inlineStr"/>
-      <c r="J390" s="2" t="inlineStr"/>
-      <c r="K390" s="2" t="inlineStr"/>
-      <c r="L390" s="2" t="inlineStr"/>
+      <c r="G390" s="4" t="inlineStr"/>
+      <c r="H390" s="4" t="inlineStr"/>
+      <c r="I390" s="4" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -13069,16 +11867,13 @@
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr"/>
-      <c r="G391" s="2" t="inlineStr"/>
-      <c r="H391" s="2" t="inlineStr"/>
-      <c r="I391" s="2" t="inlineStr"/>
-      <c r="J391" s="2" t="inlineStr"/>
-      <c r="K391" s="2" t="inlineStr">
+      <c r="G391" s="4" t="inlineStr"/>
+      <c r="H391" s="4" t="inlineStr"/>
+      <c r="I391" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L391" s="2" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr"/>
@@ -13095,24 +11890,21 @@
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr"/>
-      <c r="G392" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H392" s="2" t="inlineStr"/>
-      <c r="I392" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J392" s="2" t="inlineStr"/>
-      <c r="K392" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L392" s="2" t="inlineStr"/>
+      <c r="G392" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H392" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I392" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr"/>
@@ -13129,24 +11921,21 @@
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>
-      <c r="G393" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H393" s="2" t="inlineStr"/>
-      <c r="I393" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J393" s="2" t="inlineStr"/>
-      <c r="K393" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L393" s="2" t="inlineStr"/>
+      <c r="G393" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H393" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I393" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr"/>
@@ -13163,24 +11952,21 @@
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr"/>
-      <c r="G394" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H394" s="2" t="inlineStr"/>
-      <c r="I394" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J394" s="2" t="inlineStr"/>
-      <c r="K394" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L394" s="2" t="inlineStr"/>
+      <c r="G394" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H394" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I394" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr"/>
@@ -13197,24 +11983,21 @@
       <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr"/>
-      <c r="G395" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H395" s="2" t="inlineStr"/>
-      <c r="I395" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J395" s="2" t="inlineStr"/>
-      <c r="K395" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L395" s="2" t="inlineStr"/>
+      <c r="G395" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H395" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I395" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr"/>
@@ -13231,16 +12014,13 @@
       <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr"/>
-      <c r="G396" s="2" t="inlineStr"/>
-      <c r="H396" s="2" t="inlineStr"/>
-      <c r="I396" s="2" t="inlineStr"/>
-      <c r="J396" s="2" t="inlineStr"/>
-      <c r="K396" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L396" s="2" t="inlineStr"/>
+      <c r="G396" s="4" t="inlineStr"/>
+      <c r="H396" s="4" t="inlineStr"/>
+      <c r="I396" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr"/>
@@ -13257,24 +12037,21 @@
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr"/>
-      <c r="G397" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H397" s="2" t="inlineStr"/>
-      <c r="I397" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J397" s="2" t="inlineStr"/>
-      <c r="K397" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L397" s="2" t="inlineStr"/>
+      <c r="G397" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H397" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I397" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr"/>
@@ -13291,16 +12068,13 @@
       <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
-      <c r="G398" s="2" t="inlineStr"/>
-      <c r="H398" s="2" t="inlineStr"/>
-      <c r="I398" s="2" t="inlineStr"/>
-      <c r="J398" s="2" t="inlineStr"/>
-      <c r="K398" s="2" t="inlineStr">
+      <c r="G398" s="4" t="inlineStr"/>
+      <c r="H398" s="4" t="inlineStr"/>
+      <c r="I398" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L398" s="2" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr"/>
@@ -13317,12 +12091,9 @@
       <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
-      <c r="G399" s="2" t="inlineStr"/>
-      <c r="H399" s="2" t="inlineStr"/>
-      <c r="I399" s="2" t="inlineStr"/>
-      <c r="J399" s="2" t="inlineStr"/>
-      <c r="K399" s="2" t="inlineStr"/>
-      <c r="L399" s="2" t="inlineStr"/>
+      <c r="G399" s="4" t="inlineStr"/>
+      <c r="H399" s="4" t="inlineStr"/>
+      <c r="I399" s="4" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr"/>
@@ -13339,12 +12110,9 @@
       <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr"/>
-      <c r="G400" s="2" t="inlineStr"/>
-      <c r="H400" s="2" t="inlineStr"/>
-      <c r="I400" s="2" t="inlineStr"/>
-      <c r="J400" s="2" t="inlineStr"/>
-      <c r="K400" s="2" t="inlineStr"/>
-      <c r="L400" s="2" t="inlineStr"/>
+      <c r="G400" s="4" t="inlineStr"/>
+      <c r="H400" s="4" t="inlineStr"/>
+      <c r="I400" s="4" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr"/>
@@ -13361,12 +12129,9 @@
       <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr"/>
-      <c r="G401" s="2" t="inlineStr"/>
-      <c r="H401" s="2" t="inlineStr"/>
-      <c r="I401" s="2" t="inlineStr"/>
-      <c r="J401" s="2" t="inlineStr"/>
-      <c r="K401" s="2" t="inlineStr"/>
-      <c r="L401" s="2" t="inlineStr"/>
+      <c r="G401" s="4" t="inlineStr"/>
+      <c r="H401" s="4" t="inlineStr"/>
+      <c r="I401" s="4" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr"/>
@@ -13383,12 +12148,9 @@
       <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr"/>
-      <c r="G402" s="2" t="inlineStr"/>
-      <c r="H402" s="2" t="inlineStr"/>
-      <c r="I402" s="2" t="inlineStr"/>
-      <c r="J402" s="2" t="inlineStr"/>
-      <c r="K402" s="2" t="inlineStr"/>
-      <c r="L402" s="2" t="inlineStr"/>
+      <c r="G402" s="4" t="inlineStr"/>
+      <c r="H402" s="4" t="inlineStr"/>
+      <c r="I402" s="4" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr"/>
@@ -13405,12 +12167,9 @@
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr"/>
-      <c r="G403" s="2" t="inlineStr"/>
-      <c r="H403" s="2" t="inlineStr"/>
-      <c r="I403" s="2" t="inlineStr"/>
-      <c r="J403" s="2" t="inlineStr"/>
-      <c r="K403" s="2" t="inlineStr"/>
-      <c r="L403" s="2" t="inlineStr"/>
+      <c r="G403" s="4" t="inlineStr"/>
+      <c r="H403" s="4" t="inlineStr"/>
+      <c r="I403" s="4" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr"/>
@@ -13427,12 +12186,9 @@
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
-      <c r="G404" s="2" t="inlineStr"/>
-      <c r="H404" s="2" t="inlineStr"/>
-      <c r="I404" s="2" t="inlineStr"/>
-      <c r="J404" s="2" t="inlineStr"/>
-      <c r="K404" s="2" t="inlineStr"/>
-      <c r="L404" s="2" t="inlineStr"/>
+      <c r="G404" s="4" t="inlineStr"/>
+      <c r="H404" s="4" t="inlineStr"/>
+      <c r="I404" s="4" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr"/>
@@ -13449,16 +12205,13 @@
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
-      <c r="G405" s="2" t="inlineStr"/>
-      <c r="H405" s="2" t="inlineStr"/>
-      <c r="I405" s="2" t="inlineStr"/>
-      <c r="J405" s="2" t="inlineStr"/>
-      <c r="K405" s="2" t="inlineStr">
+      <c r="G405" s="4" t="inlineStr"/>
+      <c r="H405" s="4" t="inlineStr"/>
+      <c r="I405" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L405" s="2" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr"/>
@@ -13475,16 +12228,13 @@
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr"/>
-      <c r="G406" s="2" t="inlineStr"/>
-      <c r="H406" s="2" t="inlineStr"/>
-      <c r="I406" s="2" t="inlineStr"/>
-      <c r="J406" s="2" t="inlineStr"/>
-      <c r="K406" s="2" t="inlineStr">
+      <c r="G406" s="4" t="inlineStr"/>
+      <c r="H406" s="4" t="inlineStr"/>
+      <c r="I406" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L406" s="2" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr"/>
@@ -13501,16 +12251,13 @@
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr"/>
-      <c r="G407" s="2" t="inlineStr"/>
-      <c r="H407" s="2" t="inlineStr"/>
-      <c r="I407" s="2" t="inlineStr"/>
-      <c r="J407" s="2" t="inlineStr"/>
-      <c r="K407" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L407" s="2" t="inlineStr"/>
+      <c r="G407" s="4" t="inlineStr"/>
+      <c r="H407" s="4" t="inlineStr"/>
+      <c r="I407" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr"/>
@@ -13527,16 +12274,13 @@
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr"/>
-      <c r="G408" s="2" t="inlineStr"/>
-      <c r="H408" s="2" t="inlineStr"/>
-      <c r="I408" s="2" t="inlineStr"/>
-      <c r="J408" s="2" t="inlineStr"/>
-      <c r="K408" s="2" t="inlineStr">
+      <c r="G408" s="4" t="inlineStr"/>
+      <c r="H408" s="4" t="inlineStr"/>
+      <c r="I408" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L408" s="2" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr"/>
@@ -13553,12 +12297,9 @@
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr"/>
-      <c r="G409" s="2" t="inlineStr"/>
-      <c r="H409" s="2" t="inlineStr"/>
-      <c r="I409" s="2" t="inlineStr"/>
-      <c r="J409" s="2" t="inlineStr"/>
-      <c r="K409" s="2" t="inlineStr"/>
-      <c r="L409" s="2" t="inlineStr"/>
+      <c r="G409" s="4" t="inlineStr"/>
+      <c r="H409" s="4" t="inlineStr"/>
+      <c r="I409" s="4" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr"/>
@@ -13575,12 +12316,9 @@
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr"/>
-      <c r="G410" s="2" t="inlineStr"/>
-      <c r="H410" s="2" t="inlineStr"/>
-      <c r="I410" s="2" t="inlineStr"/>
-      <c r="J410" s="2" t="inlineStr"/>
-      <c r="K410" s="2" t="inlineStr"/>
-      <c r="L410" s="2" t="inlineStr"/>
+      <c r="G410" s="4" t="inlineStr"/>
+      <c r="H410" s="4" t="inlineStr"/>
+      <c r="I410" s="4" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr"/>
@@ -13597,12 +12335,9 @@
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr"/>
-      <c r="G411" s="2" t="inlineStr"/>
-      <c r="H411" s="2" t="inlineStr"/>
-      <c r="I411" s="2" t="inlineStr"/>
-      <c r="J411" s="2" t="inlineStr"/>
-      <c r="K411" s="2" t="inlineStr"/>
-      <c r="L411" s="2" t="inlineStr"/>
+      <c r="G411" s="4" t="inlineStr"/>
+      <c r="H411" s="4" t="inlineStr"/>
+      <c r="I411" s="4" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr"/>
@@ -13619,12 +12354,9 @@
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr"/>
-      <c r="G412" s="2" t="inlineStr"/>
-      <c r="H412" s="2" t="inlineStr"/>
-      <c r="I412" s="2" t="inlineStr"/>
-      <c r="J412" s="2" t="inlineStr"/>
-      <c r="K412" s="2" t="inlineStr"/>
-      <c r="L412" s="2" t="inlineStr"/>
+      <c r="G412" s="4" t="inlineStr"/>
+      <c r="H412" s="4" t="inlineStr"/>
+      <c r="I412" s="4" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr"/>
@@ -13641,16 +12373,13 @@
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr"/>
-      <c r="G413" s="2" t="inlineStr"/>
-      <c r="H413" s="2" t="inlineStr"/>
-      <c r="I413" s="2" t="inlineStr"/>
-      <c r="J413" s="2" t="inlineStr"/>
-      <c r="K413" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L413" s="2" t="inlineStr"/>
+      <c r="G413" s="4" t="inlineStr"/>
+      <c r="H413" s="4" t="inlineStr"/>
+      <c r="I413" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -13671,16 +12400,13 @@
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr"/>
-      <c r="G414" s="2" t="inlineStr"/>
-      <c r="H414" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I414" s="2" t="inlineStr"/>
-      <c r="J414" s="2" t="inlineStr"/>
-      <c r="K414" s="2" t="inlineStr"/>
-      <c r="L414" s="2" t="inlineStr"/>
+      <c r="G414" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H414" s="4" t="inlineStr"/>
+      <c r="I414" s="4" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr"/>
@@ -13697,12 +12423,9 @@
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr"/>
-      <c r="G415" s="2" t="inlineStr"/>
-      <c r="H415" s="2" t="inlineStr"/>
-      <c r="I415" s="2" t="inlineStr"/>
-      <c r="J415" s="2" t="inlineStr"/>
-      <c r="K415" s="2" t="inlineStr"/>
-      <c r="L415" s="2" t="inlineStr"/>
+      <c r="G415" s="4" t="inlineStr"/>
+      <c r="H415" s="4" t="inlineStr"/>
+      <c r="I415" s="4" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr"/>
@@ -13719,16 +12442,13 @@
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr"/>
-      <c r="G416" s="2" t="inlineStr"/>
-      <c r="H416" s="2" t="inlineStr"/>
-      <c r="I416" s="2" t="inlineStr"/>
-      <c r="J416" s="2" t="inlineStr"/>
-      <c r="K416" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L416" s="2" t="inlineStr"/>
+      <c r="G416" s="4" t="inlineStr"/>
+      <c r="H416" s="4" t="inlineStr"/>
+      <c r="I416" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr"/>
@@ -13745,24 +12465,21 @@
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr"/>
-      <c r="G417" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H417" s="2" t="inlineStr"/>
-      <c r="I417" s="2" t="inlineStr">
+      <c r="G417" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H417" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="J417" s="2" t="inlineStr"/>
-      <c r="K417" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L417" s="2" t="inlineStr"/>
+      <c r="I417" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr"/>
@@ -13779,24 +12496,21 @@
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr"/>
-      <c r="G418" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H418" s="2" t="inlineStr"/>
-      <c r="I418" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J418" s="2" t="inlineStr"/>
-      <c r="K418" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L418" s="2" t="inlineStr"/>
+      <c r="G418" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H418" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I418" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr"/>
@@ -13813,12 +12527,9 @@
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr"/>
-      <c r="G419" s="2" t="inlineStr"/>
-      <c r="H419" s="2" t="inlineStr"/>
-      <c r="I419" s="2" t="inlineStr"/>
-      <c r="J419" s="2" t="inlineStr"/>
-      <c r="K419" s="2" t="inlineStr"/>
-      <c r="L419" s="2" t="inlineStr"/>
+      <c r="G419" s="4" t="inlineStr"/>
+      <c r="H419" s="4" t="inlineStr"/>
+      <c r="I419" s="4" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr"/>
@@ -13835,16 +12546,13 @@
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr"/>
-      <c r="G420" s="2" t="inlineStr"/>
-      <c r="H420" s="2" t="inlineStr"/>
-      <c r="I420" s="2" t="inlineStr"/>
-      <c r="J420" s="2" t="inlineStr"/>
-      <c r="K420" s="2" t="inlineStr">
+      <c r="G420" s="4" t="inlineStr"/>
+      <c r="H420" s="4" t="inlineStr"/>
+      <c r="I420" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr"/>
@@ -13861,24 +12569,21 @@
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr"/>
-      <c r="G421" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H421" s="2" t="inlineStr"/>
-      <c r="I421" s="2" t="inlineStr">
+      <c r="G421" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H421" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="J421" s="2" t="inlineStr"/>
-      <c r="K421" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L421" s="2" t="inlineStr"/>
+      <c r="I421" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr"/>
@@ -13895,16 +12600,13 @@
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr"/>
-      <c r="G422" s="2" t="inlineStr"/>
-      <c r="H422" s="2" t="inlineStr"/>
-      <c r="I422" s="2" t="inlineStr"/>
-      <c r="J422" s="2" t="inlineStr"/>
-      <c r="K422" s="2" t="inlineStr">
+      <c r="G422" s="4" t="inlineStr"/>
+      <c r="H422" s="4" t="inlineStr"/>
+      <c r="I422" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L422" s="2" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr"/>
@@ -13921,16 +12623,13 @@
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr"/>
-      <c r="G423" s="2" t="inlineStr"/>
-      <c r="H423" s="2" t="inlineStr"/>
-      <c r="I423" s="2" t="inlineStr"/>
-      <c r="J423" s="2" t="inlineStr"/>
-      <c r="K423" s="2" t="inlineStr">
+      <c r="G423" s="4" t="inlineStr"/>
+      <c r="H423" s="4" t="inlineStr"/>
+      <c r="I423" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L423" s="2" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr"/>
@@ -13947,20 +12646,17 @@
       <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr"/>
-      <c r="G424" s="2" t="inlineStr"/>
-      <c r="H424" s="2" t="inlineStr"/>
-      <c r="I424" s="2" t="inlineStr">
+      <c r="G424" s="4" t="inlineStr"/>
+      <c r="H424" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="J424" s="2" t="inlineStr"/>
-      <c r="K424" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L424" s="2" t="inlineStr"/>
+      <c r="I424" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr"/>
@@ -13977,16 +12673,13 @@
       <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr"/>
       <c r="F425" t="inlineStr"/>
-      <c r="G425" s="2" t="inlineStr"/>
-      <c r="H425" s="2" t="inlineStr"/>
-      <c r="I425" s="2" t="inlineStr"/>
-      <c r="J425" s="2" t="inlineStr"/>
-      <c r="K425" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L425" s="2" t="inlineStr"/>
+      <c r="G425" s="4" t="inlineStr"/>
+      <c r="H425" s="4" t="inlineStr"/>
+      <c r="I425" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr"/>
@@ -14003,16 +12696,13 @@
       <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr"/>
-      <c r="G426" s="2" t="inlineStr"/>
-      <c r="H426" s="2" t="inlineStr"/>
-      <c r="I426" s="2" t="inlineStr"/>
-      <c r="J426" s="2" t="inlineStr"/>
-      <c r="K426" s="2" t="inlineStr">
+      <c r="G426" s="4" t="inlineStr"/>
+      <c r="H426" s="4" t="inlineStr"/>
+      <c r="I426" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L426" s="2" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr"/>
@@ -14029,16 +12719,13 @@
       <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr"/>
-      <c r="G427" s="2" t="inlineStr"/>
-      <c r="H427" s="2" t="inlineStr"/>
-      <c r="I427" s="2" t="inlineStr"/>
-      <c r="J427" s="2" t="inlineStr"/>
-      <c r="K427" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L427" s="2" t="inlineStr"/>
+      <c r="G427" s="4" t="inlineStr"/>
+      <c r="H427" s="4" t="inlineStr"/>
+      <c r="I427" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr"/>
@@ -14055,12 +12742,9 @@
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
-      <c r="G428" s="2" t="inlineStr"/>
-      <c r="H428" s="2" t="inlineStr"/>
-      <c r="I428" s="2" t="inlineStr"/>
-      <c r="J428" s="2" t="inlineStr"/>
-      <c r="K428" s="2" t="inlineStr"/>
-      <c r="L428" s="2" t="inlineStr"/>
+      <c r="G428" s="4" t="inlineStr"/>
+      <c r="H428" s="4" t="inlineStr"/>
+      <c r="I428" s="4" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr"/>
@@ -14077,16 +12761,13 @@
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
-      <c r="G429" s="2" t="inlineStr"/>
-      <c r="H429" s="2" t="inlineStr"/>
-      <c r="I429" s="2" t="inlineStr"/>
-      <c r="J429" s="2" t="inlineStr"/>
-      <c r="K429" s="2" t="inlineStr">
+      <c r="G429" s="4" t="inlineStr"/>
+      <c r="H429" s="4" t="inlineStr"/>
+      <c r="I429" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="L429" s="2" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr"/>
@@ -14103,16 +12784,13 @@
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
-      <c r="G430" s="2" t="inlineStr"/>
-      <c r="H430" s="2" t="inlineStr"/>
-      <c r="I430" s="2" t="inlineStr"/>
-      <c r="J430" s="2" t="inlineStr"/>
-      <c r="K430" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L430" s="2" t="inlineStr"/>
+      <c r="G430" s="4" t="inlineStr"/>
+      <c r="H430" s="4" t="inlineStr"/>
+      <c r="I430" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr"/>
@@ -14129,16 +12807,13 @@
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr"/>
-      <c r="G431" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H431" s="2" t="inlineStr"/>
-      <c r="I431" s="2" t="inlineStr"/>
-      <c r="J431" s="2" t="inlineStr"/>
-      <c r="K431" s="2" t="inlineStr"/>
-      <c r="L431" s="2" t="inlineStr"/>
+      <c r="G431" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H431" s="4" t="inlineStr"/>
+      <c r="I431" s="4" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr"/>
@@ -14155,12 +12830,9 @@
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr"/>
-      <c r="G432" s="2" t="inlineStr"/>
-      <c r="H432" s="2" t="inlineStr"/>
-      <c r="I432" s="2" t="inlineStr"/>
-      <c r="J432" s="2" t="inlineStr"/>
-      <c r="K432" s="2" t="inlineStr"/>
-      <c r="L432" s="2" t="inlineStr"/>
+      <c r="G432" s="4" t="inlineStr"/>
+      <c r="H432" s="4" t="inlineStr"/>
+      <c r="I432" s="4" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr"/>
@@ -14177,12 +12849,9 @@
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr"/>
       <c r="F433" t="inlineStr"/>
-      <c r="G433" s="2" t="inlineStr"/>
-      <c r="H433" s="2" t="inlineStr"/>
-      <c r="I433" s="2" t="inlineStr"/>
-      <c r="J433" s="2" t="inlineStr"/>
-      <c r="K433" s="2" t="inlineStr"/>
-      <c r="L433" s="2" t="inlineStr"/>
+      <c r="G433" s="4" t="inlineStr"/>
+      <c r="H433" s="4" t="inlineStr"/>
+      <c r="I433" s="4" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr"/>
@@ -14199,12 +12868,9 @@
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr"/>
-      <c r="G434" s="2" t="inlineStr"/>
-      <c r="H434" s="2" t="inlineStr"/>
-      <c r="I434" s="2" t="inlineStr"/>
-      <c r="J434" s="2" t="inlineStr"/>
-      <c r="K434" s="2" t="inlineStr"/>
-      <c r="L434" s="2" t="inlineStr"/>
+      <c r="G434" s="4" t="inlineStr"/>
+      <c r="H434" s="4" t="inlineStr"/>
+      <c r="I434" s="4" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr"/>
@@ -14221,24 +12887,21 @@
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr"/>
       <c r="F435" t="inlineStr"/>
-      <c r="G435" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H435" s="2" t="inlineStr"/>
-      <c r="I435" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J435" s="2" t="inlineStr"/>
-      <c r="K435" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L435" s="2" t="inlineStr"/>
+      <c r="G435" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H435" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I435" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -14259,12 +12922,9 @@
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr"/>
       <c r="F436" t="inlineStr"/>
-      <c r="G436" s="2" t="inlineStr"/>
-      <c r="H436" s="2" t="inlineStr"/>
-      <c r="I436" s="2" t="inlineStr"/>
-      <c r="J436" s="2" t="inlineStr"/>
-      <c r="K436" s="2" t="inlineStr"/>
-      <c r="L436" s="2" t="inlineStr"/>
+      <c r="G436" s="4" t="inlineStr"/>
+      <c r="H436" s="4" t="inlineStr"/>
+      <c r="I436" s="4" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr"/>
@@ -14281,20 +12941,17 @@
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
-      <c r="G437" s="2" t="inlineStr"/>
-      <c r="H437" s="2" t="inlineStr"/>
-      <c r="I437" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J437" s="2" t="inlineStr"/>
-      <c r="K437" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L437" s="2" t="inlineStr"/>
+      <c r="G437" s="4" t="inlineStr"/>
+      <c r="H437" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I437" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr"/>
@@ -14311,12 +12968,9 @@
       <c r="D438" t="inlineStr"/>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
-      <c r="G438" s="2" t="inlineStr"/>
-      <c r="H438" s="2" t="inlineStr"/>
-      <c r="I438" s="2" t="inlineStr"/>
-      <c r="J438" s="2" t="inlineStr"/>
-      <c r="K438" s="2" t="inlineStr"/>
-      <c r="L438" s="2" t="inlineStr"/>
+      <c r="G438" s="4" t="inlineStr"/>
+      <c r="H438" s="4" t="inlineStr"/>
+      <c r="I438" s="4" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr"/>
@@ -14333,12 +12987,9 @@
       <c r="D439" t="inlineStr"/>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
-      <c r="G439" s="2" t="inlineStr"/>
-      <c r="H439" s="2" t="inlineStr"/>
-      <c r="I439" s="2" t="inlineStr"/>
-      <c r="J439" s="2" t="inlineStr"/>
-      <c r="K439" s="2" t="inlineStr"/>
-      <c r="L439" s="2" t="inlineStr"/>
+      <c r="G439" s="4" t="inlineStr"/>
+      <c r="H439" s="4" t="inlineStr"/>
+      <c r="I439" s="4" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr"/>
@@ -14355,12 +13006,9 @@
       <c r="D440" t="inlineStr"/>
       <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr"/>
-      <c r="G440" s="2" t="inlineStr"/>
-      <c r="H440" s="2" t="inlineStr"/>
-      <c r="I440" s="2" t="inlineStr"/>
-      <c r="J440" s="2" t="inlineStr"/>
-      <c r="K440" s="2" t="inlineStr"/>
-      <c r="L440" s="2" t="inlineStr"/>
+      <c r="G440" s="4" t="inlineStr"/>
+      <c r="H440" s="4" t="inlineStr"/>
+      <c r="I440" s="4" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr"/>
@@ -14377,12 +13025,9 @@
       <c r="D441" t="inlineStr"/>
       <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr"/>
-      <c r="G441" s="2" t="inlineStr"/>
-      <c r="H441" s="2" t="inlineStr"/>
-      <c r="I441" s="2" t="inlineStr"/>
-      <c r="J441" s="2" t="inlineStr"/>
-      <c r="K441" s="2" t="inlineStr"/>
-      <c r="L441" s="2" t="inlineStr"/>
+      <c r="G441" s="4" t="inlineStr"/>
+      <c r="H441" s="4" t="inlineStr"/>
+      <c r="I441" s="4" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr"/>
@@ -14399,12 +13044,9 @@
       <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr"/>
-      <c r="G442" s="2" t="inlineStr"/>
-      <c r="H442" s="2" t="inlineStr"/>
-      <c r="I442" s="2" t="inlineStr"/>
-      <c r="J442" s="2" t="inlineStr"/>
-      <c r="K442" s="2" t="inlineStr"/>
-      <c r="L442" s="2" t="inlineStr"/>
+      <c r="G442" s="4" t="inlineStr"/>
+      <c r="H442" s="4" t="inlineStr"/>
+      <c r="I442" s="4" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr"/>
@@ -14421,12 +13063,9 @@
       <c r="D443" t="inlineStr"/>
       <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr"/>
-      <c r="G443" s="2" t="inlineStr"/>
-      <c r="H443" s="2" t="inlineStr"/>
-      <c r="I443" s="2" t="inlineStr"/>
-      <c r="J443" s="2" t="inlineStr"/>
-      <c r="K443" s="2" t="inlineStr"/>
-      <c r="L443" s="2" t="inlineStr"/>
+      <c r="G443" s="4" t="inlineStr"/>
+      <c r="H443" s="4" t="inlineStr"/>
+      <c r="I443" s="4" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr"/>
@@ -14443,12 +13082,9 @@
       <c r="D444" t="inlineStr"/>
       <c r="E444" t="inlineStr"/>
       <c r="F444" t="inlineStr"/>
-      <c r="G444" s="2" t="inlineStr"/>
-      <c r="H444" s="2" t="inlineStr"/>
-      <c r="I444" s="2" t="inlineStr"/>
-      <c r="J444" s="2" t="inlineStr"/>
-      <c r="K444" s="2" t="inlineStr"/>
-      <c r="L444" s="2" t="inlineStr"/>
+      <c r="G444" s="4" t="inlineStr"/>
+      <c r="H444" s="4" t="inlineStr"/>
+      <c r="I444" s="4" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr"/>
@@ -14465,12 +13101,9 @@
       <c r="D445" t="inlineStr"/>
       <c r="E445" t="inlineStr"/>
       <c r="F445" t="inlineStr"/>
-      <c r="G445" s="2" t="inlineStr"/>
-      <c r="H445" s="2" t="inlineStr"/>
-      <c r="I445" s="2" t="inlineStr"/>
-      <c r="J445" s="2" t="inlineStr"/>
-      <c r="K445" s="2" t="inlineStr"/>
-      <c r="L445" s="2" t="inlineStr"/>
+      <c r="G445" s="4" t="inlineStr"/>
+      <c r="H445" s="4" t="inlineStr"/>
+      <c r="I445" s="4" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr"/>
@@ -14487,12 +13120,9 @@
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
-      <c r="G446" s="2" t="inlineStr"/>
-      <c r="H446" s="2" t="inlineStr"/>
-      <c r="I446" s="2" t="inlineStr"/>
-      <c r="J446" s="2" t="inlineStr"/>
-      <c r="K446" s="2" t="inlineStr"/>
-      <c r="L446" s="2" t="inlineStr"/>
+      <c r="G446" s="4" t="inlineStr"/>
+      <c r="H446" s="4" t="inlineStr"/>
+      <c r="I446" s="4" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr"/>
@@ -14509,12 +13139,9 @@
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr"/>
-      <c r="G447" s="2" t="inlineStr"/>
-      <c r="H447" s="2" t="inlineStr"/>
-      <c r="I447" s="2" t="inlineStr"/>
-      <c r="J447" s="2" t="inlineStr"/>
-      <c r="K447" s="2" t="inlineStr"/>
-      <c r="L447" s="2" t="inlineStr"/>
+      <c r="G447" s="4" t="inlineStr"/>
+      <c r="H447" s="4" t="inlineStr"/>
+      <c r="I447" s="4" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr"/>
@@ -14531,12 +13158,9 @@
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
-      <c r="G448" s="2" t="inlineStr"/>
-      <c r="H448" s="2" t="inlineStr"/>
-      <c r="I448" s="2" t="inlineStr"/>
-      <c r="J448" s="2" t="inlineStr"/>
-      <c r="K448" s="2" t="inlineStr"/>
-      <c r="L448" s="2" t="inlineStr"/>
+      <c r="G448" s="4" t="inlineStr"/>
+      <c r="H448" s="4" t="inlineStr"/>
+      <c r="I448" s="4" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr"/>
@@ -14553,12 +13177,9 @@
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr"/>
-      <c r="G449" s="2" t="inlineStr"/>
-      <c r="H449" s="2" t="inlineStr"/>
-      <c r="I449" s="2" t="inlineStr"/>
-      <c r="J449" s="2" t="inlineStr"/>
-      <c r="K449" s="2" t="inlineStr"/>
-      <c r="L449" s="2" t="inlineStr"/>
+      <c r="G449" s="4" t="inlineStr"/>
+      <c r="H449" s="4" t="inlineStr"/>
+      <c r="I449" s="4" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr"/>
@@ -14575,12 +13196,9 @@
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr"/>
       <c r="F450" t="inlineStr"/>
-      <c r="G450" s="2" t="inlineStr"/>
-      <c r="H450" s="2" t="inlineStr"/>
-      <c r="I450" s="2" t="inlineStr"/>
-      <c r="J450" s="2" t="inlineStr"/>
-      <c r="K450" s="2" t="inlineStr"/>
-      <c r="L450" s="2" t="inlineStr"/>
+      <c r="G450" s="4" t="inlineStr"/>
+      <c r="H450" s="4" t="inlineStr"/>
+      <c r="I450" s="4" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr"/>
@@ -14597,12 +13215,9 @@
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="inlineStr"/>
-      <c r="G451" s="2" t="inlineStr"/>
-      <c r="H451" s="2" t="inlineStr"/>
-      <c r="I451" s="2" t="inlineStr"/>
-      <c r="J451" s="2" t="inlineStr"/>
-      <c r="K451" s="2" t="inlineStr"/>
-      <c r="L451" s="2" t="inlineStr"/>
+      <c r="G451" s="4" t="inlineStr"/>
+      <c r="H451" s="4" t="inlineStr"/>
+      <c r="I451" s="4" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr"/>
@@ -14619,12 +13234,9 @@
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr"/>
-      <c r="G452" s="2" t="inlineStr"/>
-      <c r="H452" s="2" t="inlineStr"/>
-      <c r="I452" s="2" t="inlineStr"/>
-      <c r="J452" s="2" t="inlineStr"/>
-      <c r="K452" s="2" t="inlineStr"/>
-      <c r="L452" s="2" t="inlineStr"/>
+      <c r="G452" s="4" t="inlineStr"/>
+      <c r="H452" s="4" t="inlineStr"/>
+      <c r="I452" s="4" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr"/>
@@ -14641,12 +13253,9 @@
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
-      <c r="G453" s="2" t="inlineStr"/>
-      <c r="H453" s="2" t="inlineStr"/>
-      <c r="I453" s="2" t="inlineStr"/>
-      <c r="J453" s="2" t="inlineStr"/>
-      <c r="K453" s="2" t="inlineStr"/>
-      <c r="L453" s="2" t="inlineStr"/>
+      <c r="G453" s="4" t="inlineStr"/>
+      <c r="H453" s="4" t="inlineStr"/>
+      <c r="I453" s="4" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr"/>
@@ -14663,12 +13272,9 @@
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
-      <c r="G454" s="2" t="inlineStr"/>
-      <c r="H454" s="2" t="inlineStr"/>
-      <c r="I454" s="2" t="inlineStr"/>
-      <c r="J454" s="2" t="inlineStr"/>
-      <c r="K454" s="2" t="inlineStr"/>
-      <c r="L454" s="2" t="inlineStr"/>
+      <c r="G454" s="4" t="inlineStr"/>
+      <c r="H454" s="4" t="inlineStr"/>
+      <c r="I454" s="4" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr"/>
@@ -14685,12 +13291,9 @@
       <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr"/>
-      <c r="G455" s="2" t="inlineStr"/>
-      <c r="H455" s="2" t="inlineStr"/>
-      <c r="I455" s="2" t="inlineStr"/>
-      <c r="J455" s="2" t="inlineStr"/>
-      <c r="K455" s="2" t="inlineStr"/>
-      <c r="L455" s="2" t="inlineStr"/>
+      <c r="G455" s="4" t="inlineStr"/>
+      <c r="H455" s="4" t="inlineStr"/>
+      <c r="I455" s="4" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr"/>
@@ -14707,12 +13310,9 @@
       <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr"/>
       <c r="F456" t="inlineStr"/>
-      <c r="G456" s="2" t="inlineStr"/>
-      <c r="H456" s="2" t="inlineStr"/>
-      <c r="I456" s="2" t="inlineStr"/>
-      <c r="J456" s="2" t="inlineStr"/>
-      <c r="K456" s="2" t="inlineStr"/>
-      <c r="L456" s="2" t="inlineStr"/>
+      <c r="G456" s="4" t="inlineStr"/>
+      <c r="H456" s="4" t="inlineStr"/>
+      <c r="I456" s="4" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr"/>
@@ -14729,12 +13329,9 @@
       <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr"/>
-      <c r="G457" s="2" t="inlineStr"/>
-      <c r="H457" s="2" t="inlineStr"/>
-      <c r="I457" s="2" t="inlineStr"/>
-      <c r="J457" s="2" t="inlineStr"/>
-      <c r="K457" s="2" t="inlineStr"/>
-      <c r="L457" s="2" t="inlineStr"/>
+      <c r="G457" s="4" t="inlineStr"/>
+      <c r="H457" s="4" t="inlineStr"/>
+      <c r="I457" s="4" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr"/>
@@ -14751,12 +13348,9 @@
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr"/>
-      <c r="G458" s="2" t="inlineStr"/>
-      <c r="H458" s="2" t="inlineStr"/>
-      <c r="I458" s="2" t="inlineStr"/>
-      <c r="J458" s="2" t="inlineStr"/>
-      <c r="K458" s="2" t="inlineStr"/>
-      <c r="L458" s="2" t="inlineStr"/>
+      <c r="G458" s="4" t="inlineStr"/>
+      <c r="H458" s="4" t="inlineStr"/>
+      <c r="I458" s="4" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr"/>
@@ -14773,12 +13367,9 @@
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr"/>
-      <c r="G459" s="2" t="inlineStr"/>
-      <c r="H459" s="2" t="inlineStr"/>
-      <c r="I459" s="2" t="inlineStr"/>
-      <c r="J459" s="2" t="inlineStr"/>
-      <c r="K459" s="2" t="inlineStr"/>
-      <c r="L459" s="2" t="inlineStr"/>
+      <c r="G459" s="4" t="inlineStr"/>
+      <c r="H459" s="4" t="inlineStr"/>
+      <c r="I459" s="4" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr"/>
@@ -14795,12 +13386,9 @@
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr"/>
-      <c r="G460" s="2" t="inlineStr"/>
-      <c r="H460" s="2" t="inlineStr"/>
-      <c r="I460" s="2" t="inlineStr"/>
-      <c r="J460" s="2" t="inlineStr"/>
-      <c r="K460" s="2" t="inlineStr"/>
-      <c r="L460" s="2" t="inlineStr"/>
+      <c r="G460" s="4" t="inlineStr"/>
+      <c r="H460" s="4" t="inlineStr"/>
+      <c r="I460" s="4" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr"/>
@@ -14817,12 +13405,9 @@
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
-      <c r="G461" s="2" t="inlineStr"/>
-      <c r="H461" s="2" t="inlineStr"/>
-      <c r="I461" s="2" t="inlineStr"/>
-      <c r="J461" s="2" t="inlineStr"/>
-      <c r="K461" s="2" t="inlineStr"/>
-      <c r="L461" s="2" t="inlineStr"/>
+      <c r="G461" s="4" t="inlineStr"/>
+      <c r="H461" s="4" t="inlineStr"/>
+      <c r="I461" s="4" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr"/>
@@ -14839,12 +13424,9 @@
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
-      <c r="G462" s="2" t="inlineStr"/>
-      <c r="H462" s="2" t="inlineStr"/>
-      <c r="I462" s="2" t="inlineStr"/>
-      <c r="J462" s="2" t="inlineStr"/>
-      <c r="K462" s="2" t="inlineStr"/>
-      <c r="L462" s="2" t="inlineStr"/>
+      <c r="G462" s="4" t="inlineStr"/>
+      <c r="H462" s="4" t="inlineStr"/>
+      <c r="I462" s="4" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr"/>
@@ -14861,12 +13443,9 @@
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
-      <c r="G463" s="2" t="inlineStr"/>
-      <c r="H463" s="2" t="inlineStr"/>
-      <c r="I463" s="2" t="inlineStr"/>
-      <c r="J463" s="2" t="inlineStr"/>
-      <c r="K463" s="2" t="inlineStr"/>
-      <c r="L463" s="2" t="inlineStr"/>
+      <c r="G463" s="4" t="inlineStr"/>
+      <c r="H463" s="4" t="inlineStr"/>
+      <c r="I463" s="4" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr"/>
@@ -14883,12 +13462,9 @@
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
-      <c r="G464" s="2" t="inlineStr"/>
-      <c r="H464" s="2" t="inlineStr"/>
-      <c r="I464" s="2" t="inlineStr"/>
-      <c r="J464" s="2" t="inlineStr"/>
-      <c r="K464" s="2" t="inlineStr"/>
-      <c r="L464" s="2" t="inlineStr"/>
+      <c r="G464" s="4" t="inlineStr"/>
+      <c r="H464" s="4" t="inlineStr"/>
+      <c r="I464" s="4" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr"/>
@@ -14905,12 +13481,9 @@
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr"/>
-      <c r="G465" s="2" t="inlineStr"/>
-      <c r="H465" s="2" t="inlineStr"/>
-      <c r="I465" s="2" t="inlineStr"/>
-      <c r="J465" s="2" t="inlineStr"/>
-      <c r="K465" s="2" t="inlineStr"/>
-      <c r="L465" s="2" t="inlineStr"/>
+      <c r="G465" s="4" t="inlineStr"/>
+      <c r="H465" s="4" t="inlineStr"/>
+      <c r="I465" s="4" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr"/>
@@ -14927,12 +13500,9 @@
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="inlineStr"/>
-      <c r="G466" s="2" t="inlineStr"/>
-      <c r="H466" s="2" t="inlineStr"/>
-      <c r="I466" s="2" t="inlineStr"/>
-      <c r="J466" s="2" t="inlineStr"/>
-      <c r="K466" s="2" t="inlineStr"/>
-      <c r="L466" s="2" t="inlineStr"/>
+      <c r="G466" s="4" t="inlineStr"/>
+      <c r="H466" s="4" t="inlineStr"/>
+      <c r="I466" s="4" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr"/>
@@ -14949,12 +13519,9 @@
       <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr"/>
       <c r="F467" t="inlineStr"/>
-      <c r="G467" s="2" t="inlineStr"/>
-      <c r="H467" s="2" t="inlineStr"/>
-      <c r="I467" s="2" t="inlineStr"/>
-      <c r="J467" s="2" t="inlineStr"/>
-      <c r="K467" s="2" t="inlineStr"/>
-      <c r="L467" s="2" t="inlineStr"/>
+      <c r="G467" s="4" t="inlineStr"/>
+      <c r="H467" s="4" t="inlineStr"/>
+      <c r="I467" s="4" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr"/>
@@ -14971,12 +13538,9 @@
       <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr"/>
       <c r="F468" t="inlineStr"/>
-      <c r="G468" s="2" t="inlineStr"/>
-      <c r="H468" s="2" t="inlineStr"/>
-      <c r="I468" s="2" t="inlineStr"/>
-      <c r="J468" s="2" t="inlineStr"/>
-      <c r="K468" s="2" t="inlineStr"/>
-      <c r="L468" s="2" t="inlineStr"/>
+      <c r="G468" s="4" t="inlineStr"/>
+      <c r="H468" s="4" t="inlineStr"/>
+      <c r="I468" s="4" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr"/>
@@ -14993,12 +13557,9 @@
       <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr"/>
       <c r="F469" t="inlineStr"/>
-      <c r="G469" s="2" t="inlineStr"/>
-      <c r="H469" s="2" t="inlineStr"/>
-      <c r="I469" s="2" t="inlineStr"/>
-      <c r="J469" s="2" t="inlineStr"/>
-      <c r="K469" s="2" t="inlineStr"/>
-      <c r="L469" s="2" t="inlineStr"/>
+      <c r="G469" s="4" t="inlineStr"/>
+      <c r="H469" s="4" t="inlineStr"/>
+      <c r="I469" s="4" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr"/>
@@ -15015,12 +13576,9 @@
       <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr"/>
       <c r="F470" t="inlineStr"/>
-      <c r="G470" s="2" t="inlineStr"/>
-      <c r="H470" s="2" t="inlineStr"/>
-      <c r="I470" s="2" t="inlineStr"/>
-      <c r="J470" s="2" t="inlineStr"/>
-      <c r="K470" s="2" t="inlineStr"/>
-      <c r="L470" s="2" t="inlineStr"/>
+      <c r="G470" s="4" t="inlineStr"/>
+      <c r="H470" s="4" t="inlineStr"/>
+      <c r="I470" s="4" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr"/>
@@ -15037,12 +13595,9 @@
       <c r="D471" t="inlineStr"/>
       <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr"/>
-      <c r="G471" s="2" t="inlineStr"/>
-      <c r="H471" s="2" t="inlineStr"/>
-      <c r="I471" s="2" t="inlineStr"/>
-      <c r="J471" s="2" t="inlineStr"/>
-      <c r="K471" s="2" t="inlineStr"/>
-      <c r="L471" s="2" t="inlineStr"/>
+      <c r="G471" s="4" t="inlineStr"/>
+      <c r="H471" s="4" t="inlineStr"/>
+      <c r="I471" s="4" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr"/>
@@ -15059,12 +13614,9 @@
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr"/>
-      <c r="G472" s="2" t="inlineStr"/>
-      <c r="H472" s="2" t="inlineStr"/>
-      <c r="I472" s="2" t="inlineStr"/>
-      <c r="J472" s="2" t="inlineStr"/>
-      <c r="K472" s="2" t="inlineStr"/>
-      <c r="L472" s="2" t="inlineStr"/>
+      <c r="G472" s="4" t="inlineStr"/>
+      <c r="H472" s="4" t="inlineStr"/>
+      <c r="I472" s="4" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr"/>
@@ -15081,12 +13633,9 @@
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr"/>
-      <c r="G473" s="2" t="inlineStr"/>
-      <c r="H473" s="2" t="inlineStr"/>
-      <c r="I473" s="2" t="inlineStr"/>
-      <c r="J473" s="2" t="inlineStr"/>
-      <c r="K473" s="2" t="inlineStr"/>
-      <c r="L473" s="2" t="inlineStr"/>
+      <c r="G473" s="4" t="inlineStr"/>
+      <c r="H473" s="4" t="inlineStr"/>
+      <c r="I473" s="4" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr"/>
@@ -15103,12 +13652,9 @@
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr"/>
-      <c r="G474" s="2" t="inlineStr"/>
-      <c r="H474" s="2" t="inlineStr"/>
-      <c r="I474" s="2" t="inlineStr"/>
-      <c r="J474" s="2" t="inlineStr"/>
-      <c r="K474" s="2" t="inlineStr"/>
-      <c r="L474" s="2" t="inlineStr"/>
+      <c r="G474" s="4" t="inlineStr"/>
+      <c r="H474" s="4" t="inlineStr"/>
+      <c r="I474" s="4" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr"/>
@@ -15125,12 +13671,9 @@
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr"/>
       <c r="F475" t="inlineStr"/>
-      <c r="G475" s="2" t="inlineStr"/>
-      <c r="H475" s="2" t="inlineStr"/>
-      <c r="I475" s="2" t="inlineStr"/>
-      <c r="J475" s="2" t="inlineStr"/>
-      <c r="K475" s="2" t="inlineStr"/>
-      <c r="L475" s="2" t="inlineStr"/>
+      <c r="G475" s="4" t="inlineStr"/>
+      <c r="H475" s="4" t="inlineStr"/>
+      <c r="I475" s="4" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr"/>
@@ -15147,12 +13690,9 @@
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr"/>
       <c r="F476" t="inlineStr"/>
-      <c r="G476" s="2" t="inlineStr"/>
-      <c r="H476" s="2" t="inlineStr"/>
-      <c r="I476" s="2" t="inlineStr"/>
-      <c r="J476" s="2" t="inlineStr"/>
-      <c r="K476" s="2" t="inlineStr"/>
-      <c r="L476" s="2" t="inlineStr"/>
+      <c r="G476" s="4" t="inlineStr"/>
+      <c r="H476" s="4" t="inlineStr"/>
+      <c r="I476" s="4" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr"/>
@@ -15169,12 +13709,9 @@
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr"/>
       <c r="F477" t="inlineStr"/>
-      <c r="G477" s="2" t="inlineStr"/>
-      <c r="H477" s="2" t="inlineStr"/>
-      <c r="I477" s="2" t="inlineStr"/>
-      <c r="J477" s="2" t="inlineStr"/>
-      <c r="K477" s="2" t="inlineStr"/>
-      <c r="L477" s="2" t="inlineStr"/>
+      <c r="G477" s="4" t="inlineStr"/>
+      <c r="H477" s="4" t="inlineStr"/>
+      <c r="I477" s="4" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr"/>
@@ -15191,12 +13728,9 @@
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr"/>
-      <c r="G478" s="2" t="inlineStr"/>
-      <c r="H478" s="2" t="inlineStr"/>
-      <c r="I478" s="2" t="inlineStr"/>
-      <c r="J478" s="2" t="inlineStr"/>
-      <c r="K478" s="2" t="inlineStr"/>
-      <c r="L478" s="2" t="inlineStr"/>
+      <c r="G478" s="4" t="inlineStr"/>
+      <c r="H478" s="4" t="inlineStr"/>
+      <c r="I478" s="4" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr"/>
@@ -15213,12 +13747,9 @@
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr"/>
-      <c r="G479" s="2" t="inlineStr"/>
-      <c r="H479" s="2" t="inlineStr"/>
-      <c r="I479" s="2" t="inlineStr"/>
-      <c r="J479" s="2" t="inlineStr"/>
-      <c r="K479" s="2" t="inlineStr"/>
-      <c r="L479" s="2" t="inlineStr"/>
+      <c r="G479" s="4" t="inlineStr"/>
+      <c r="H479" s="4" t="inlineStr"/>
+      <c r="I479" s="4" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr"/>
@@ -15235,12 +13766,9 @@
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr"/>
-      <c r="G480" s="2" t="inlineStr"/>
-      <c r="H480" s="2" t="inlineStr"/>
-      <c r="I480" s="2" t="inlineStr"/>
-      <c r="J480" s="2" t="inlineStr"/>
-      <c r="K480" s="2" t="inlineStr"/>
-      <c r="L480" s="2" t="inlineStr"/>
+      <c r="G480" s="4" t="inlineStr"/>
+      <c r="H480" s="4" t="inlineStr"/>
+      <c r="I480" s="4" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr"/>
@@ -15257,16 +13785,13 @@
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
       <c r="F481" t="inlineStr"/>
-      <c r="G481" s="2" t="inlineStr"/>
-      <c r="H481" s="2" t="inlineStr"/>
-      <c r="I481" s="2" t="inlineStr"/>
-      <c r="J481" s="2" t="inlineStr"/>
-      <c r="K481" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L481" s="2" t="inlineStr"/>
+      <c r="G481" s="4" t="inlineStr"/>
+      <c r="H481" s="4" t="inlineStr"/>
+      <c r="I481" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr"/>
@@ -15283,12 +13808,9 @@
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr"/>
       <c r="F482" t="inlineStr"/>
-      <c r="G482" s="2" t="inlineStr"/>
-      <c r="H482" s="2" t="inlineStr"/>
-      <c r="I482" s="2" t="inlineStr"/>
-      <c r="J482" s="2" t="inlineStr"/>
-      <c r="K482" s="2" t="inlineStr"/>
-      <c r="L482" s="2" t="inlineStr"/>
+      <c r="G482" s="4" t="inlineStr"/>
+      <c r="H482" s="4" t="inlineStr"/>
+      <c r="I482" s="4" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr"/>
@@ -15305,12 +13827,9 @@
       <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr"/>
       <c r="F483" t="inlineStr"/>
-      <c r="G483" s="2" t="inlineStr"/>
-      <c r="H483" s="2" t="inlineStr"/>
-      <c r="I483" s="2" t="inlineStr"/>
-      <c r="J483" s="2" t="inlineStr"/>
-      <c r="K483" s="2" t="inlineStr"/>
-      <c r="L483" s="2" t="inlineStr"/>
+      <c r="G483" s="4" t="inlineStr"/>
+      <c r="H483" s="4" t="inlineStr"/>
+      <c r="I483" s="4" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr"/>
@@ -15327,12 +13846,9 @@
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr"/>
       <c r="F484" t="inlineStr"/>
-      <c r="G484" s="2" t="inlineStr"/>
-      <c r="H484" s="2" t="inlineStr"/>
-      <c r="I484" s="2" t="inlineStr"/>
-      <c r="J484" s="2" t="inlineStr"/>
-      <c r="K484" s="2" t="inlineStr"/>
-      <c r="L484" s="2" t="inlineStr"/>
+      <c r="G484" s="4" t="inlineStr"/>
+      <c r="H484" s="4" t="inlineStr"/>
+      <c r="I484" s="4" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr"/>
@@ -15349,12 +13865,9 @@
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="inlineStr"/>
-      <c r="G485" s="2" t="inlineStr"/>
-      <c r="H485" s="2" t="inlineStr"/>
-      <c r="I485" s="2" t="inlineStr"/>
-      <c r="J485" s="2" t="inlineStr"/>
-      <c r="K485" s="2" t="inlineStr"/>
-      <c r="L485" s="2" t="inlineStr"/>
+      <c r="G485" s="4" t="inlineStr"/>
+      <c r="H485" s="4" t="inlineStr"/>
+      <c r="I485" s="4" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr"/>
@@ -15371,12 +13884,9 @@
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr"/>
       <c r="F486" t="inlineStr"/>
-      <c r="G486" s="2" t="inlineStr"/>
-      <c r="H486" s="2" t="inlineStr"/>
-      <c r="I486" s="2" t="inlineStr"/>
-      <c r="J486" s="2" t="inlineStr"/>
-      <c r="K486" s="2" t="inlineStr"/>
-      <c r="L486" s="2" t="inlineStr"/>
+      <c r="G486" s="4" t="inlineStr"/>
+      <c r="H486" s="4" t="inlineStr"/>
+      <c r="I486" s="4" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr"/>
@@ -15393,12 +13903,9 @@
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="inlineStr"/>
-      <c r="G487" s="2" t="inlineStr"/>
-      <c r="H487" s="2" t="inlineStr"/>
-      <c r="I487" s="2" t="inlineStr"/>
-      <c r="J487" s="2" t="inlineStr"/>
-      <c r="K487" s="2" t="inlineStr"/>
-      <c r="L487" s="2" t="inlineStr"/>
+      <c r="G487" s="4" t="inlineStr"/>
+      <c r="H487" s="4" t="inlineStr"/>
+      <c r="I487" s="4" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr"/>
@@ -15415,12 +13922,9 @@
       <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr"/>
-      <c r="G488" s="2" t="inlineStr"/>
-      <c r="H488" s="2" t="inlineStr"/>
-      <c r="I488" s="2" t="inlineStr"/>
-      <c r="J488" s="2" t="inlineStr"/>
-      <c r="K488" s="2" t="inlineStr"/>
-      <c r="L488" s="2" t="inlineStr"/>
+      <c r="G488" s="4" t="inlineStr"/>
+      <c r="H488" s="4" t="inlineStr"/>
+      <c r="I488" s="4" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr"/>
@@ -15437,12 +13941,9 @@
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr"/>
-      <c r="G489" s="2" t="inlineStr"/>
-      <c r="H489" s="2" t="inlineStr"/>
-      <c r="I489" s="2" t="inlineStr"/>
-      <c r="J489" s="2" t="inlineStr"/>
-      <c r="K489" s="2" t="inlineStr"/>
-      <c r="L489" s="2" t="inlineStr"/>
+      <c r="G489" s="4" t="inlineStr"/>
+      <c r="H489" s="4" t="inlineStr"/>
+      <c r="I489" s="4" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr"/>
@@ -15459,12 +13960,9 @@
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr"/>
-      <c r="G490" s="2" t="inlineStr"/>
-      <c r="H490" s="2" t="inlineStr"/>
-      <c r="I490" s="2" t="inlineStr"/>
-      <c r="J490" s="2" t="inlineStr"/>
-      <c r="K490" s="2" t="inlineStr"/>
-      <c r="L490" s="2" t="inlineStr"/>
+      <c r="G490" s="4" t="inlineStr"/>
+      <c r="H490" s="4" t="inlineStr"/>
+      <c r="I490" s="4" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr"/>
@@ -15481,12 +13979,9 @@
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr"/>
-      <c r="G491" s="2" t="inlineStr"/>
-      <c r="H491" s="2" t="inlineStr"/>
-      <c r="I491" s="2" t="inlineStr"/>
-      <c r="J491" s="2" t="inlineStr"/>
-      <c r="K491" s="2" t="inlineStr"/>
-      <c r="L491" s="2" t="inlineStr"/>
+      <c r="G491" s="4" t="inlineStr"/>
+      <c r="H491" s="4" t="inlineStr"/>
+      <c r="I491" s="4" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr"/>
@@ -15503,12 +13998,9 @@
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr"/>
-      <c r="G492" s="2" t="inlineStr"/>
-      <c r="H492" s="2" t="inlineStr"/>
-      <c r="I492" s="2" t="inlineStr"/>
-      <c r="J492" s="2" t="inlineStr"/>
-      <c r="K492" s="2" t="inlineStr"/>
-      <c r="L492" s="2" t="inlineStr"/>
+      <c r="G492" s="4" t="inlineStr"/>
+      <c r="H492" s="4" t="inlineStr"/>
+      <c r="I492" s="4" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr"/>
@@ -15525,12 +14017,9 @@
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr"/>
-      <c r="G493" s="2" t="inlineStr"/>
-      <c r="H493" s="2" t="inlineStr"/>
-      <c r="I493" s="2" t="inlineStr"/>
-      <c r="J493" s="2" t="inlineStr"/>
-      <c r="K493" s="2" t="inlineStr"/>
-      <c r="L493" s="2" t="inlineStr"/>
+      <c r="G493" s="4" t="inlineStr"/>
+      <c r="H493" s="4" t="inlineStr"/>
+      <c r="I493" s="4" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr"/>
@@ -15547,20 +14036,17 @@
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr"/>
-      <c r="G494" s="2" t="inlineStr"/>
-      <c r="H494" s="2" t="inlineStr"/>
-      <c r="I494" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J494" s="2" t="inlineStr"/>
-      <c r="K494" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L494" s="2" t="inlineStr"/>
+      <c r="G494" s="4" t="inlineStr"/>
+      <c r="H494" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I494" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr"/>
@@ -15577,12 +14063,9 @@
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr"/>
-      <c r="G495" s="2" t="inlineStr"/>
-      <c r="H495" s="2" t="inlineStr"/>
-      <c r="I495" s="2" t="inlineStr"/>
-      <c r="J495" s="2" t="inlineStr"/>
-      <c r="K495" s="2" t="inlineStr"/>
-      <c r="L495" s="2" t="inlineStr"/>
+      <c r="G495" s="4" t="inlineStr"/>
+      <c r="H495" s="4" t="inlineStr"/>
+      <c r="I495" s="4" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr"/>
@@ -15599,12 +14082,9 @@
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr"/>
-      <c r="G496" s="2" t="inlineStr"/>
-      <c r="H496" s="2" t="inlineStr"/>
-      <c r="I496" s="2" t="inlineStr"/>
-      <c r="J496" s="2" t="inlineStr"/>
-      <c r="K496" s="2" t="inlineStr"/>
-      <c r="L496" s="2" t="inlineStr"/>
+      <c r="G496" s="4" t="inlineStr"/>
+      <c r="H496" s="4" t="inlineStr"/>
+      <c r="I496" s="4" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr"/>
@@ -15621,12 +14101,9 @@
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr"/>
-      <c r="G497" s="2" t="inlineStr"/>
-      <c r="H497" s="2" t="inlineStr"/>
-      <c r="I497" s="2" t="inlineStr"/>
-      <c r="J497" s="2" t="inlineStr"/>
-      <c r="K497" s="2" t="inlineStr"/>
-      <c r="L497" s="2" t="inlineStr"/>
+      <c r="G497" s="4" t="inlineStr"/>
+      <c r="H497" s="4" t="inlineStr"/>
+      <c r="I497" s="4" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr"/>
@@ -15643,12 +14120,9 @@
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr"/>
-      <c r="G498" s="2" t="inlineStr"/>
-      <c r="H498" s="2" t="inlineStr"/>
-      <c r="I498" s="2" t="inlineStr"/>
-      <c r="J498" s="2" t="inlineStr"/>
-      <c r="K498" s="2" t="inlineStr"/>
-      <c r="L498" s="2" t="inlineStr"/>
+      <c r="G498" s="4" t="inlineStr"/>
+      <c r="H498" s="4" t="inlineStr"/>
+      <c r="I498" s="4" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -15669,20 +14143,17 @@
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr"/>
       <c r="F499" t="inlineStr"/>
-      <c r="G499" s="2" t="inlineStr"/>
-      <c r="H499" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I499" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="J499" s="2" t="inlineStr"/>
-      <c r="K499" s="2" t="inlineStr"/>
-      <c r="L499" s="2" t="inlineStr"/>
+      <c r="G499" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H499" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="I499" s="4" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr"/>
@@ -15699,12 +14170,9 @@
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr"/>
       <c r="F500" t="inlineStr"/>
-      <c r="G500" s="2" t="inlineStr"/>
-      <c r="H500" s="2" t="inlineStr"/>
-      <c r="I500" s="2" t="inlineStr"/>
-      <c r="J500" s="2" t="inlineStr"/>
-      <c r="K500" s="2" t="inlineStr"/>
-      <c r="L500" s="2" t="inlineStr"/>
+      <c r="G500" s="4" t="inlineStr"/>
+      <c r="H500" s="4" t="inlineStr"/>
+      <c r="I500" s="4" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr"/>
@@ -15721,12 +14189,9 @@
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
-      <c r="G501" s="2" t="inlineStr"/>
-      <c r="H501" s="2" t="inlineStr"/>
-      <c r="I501" s="2" t="inlineStr"/>
-      <c r="J501" s="2" t="inlineStr"/>
-      <c r="K501" s="2" t="inlineStr"/>
-      <c r="L501" s="2" t="inlineStr"/>
+      <c r="G501" s="4" t="inlineStr"/>
+      <c r="H501" s="4" t="inlineStr"/>
+      <c r="I501" s="4" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr"/>
@@ -15743,12 +14208,9 @@
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="inlineStr"/>
-      <c r="G502" s="2" t="inlineStr"/>
-      <c r="H502" s="2" t="inlineStr"/>
-      <c r="I502" s="2" t="inlineStr"/>
-      <c r="J502" s="2" t="inlineStr"/>
-      <c r="K502" s="2" t="inlineStr"/>
-      <c r="L502" s="2" t="inlineStr"/>
+      <c r="G502" s="4" t="inlineStr"/>
+      <c r="H502" s="4" t="inlineStr"/>
+      <c r="I502" s="4" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr"/>
@@ -15765,12 +14227,9 @@
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr"/>
       <c r="F503" t="inlineStr"/>
-      <c r="G503" s="2" t="inlineStr"/>
-      <c r="H503" s="2" t="inlineStr"/>
-      <c r="I503" s="2" t="inlineStr"/>
-      <c r="J503" s="2" t="inlineStr"/>
-      <c r="K503" s="2" t="inlineStr"/>
-      <c r="L503" s="2" t="inlineStr"/>
+      <c r="G503" s="4" t="inlineStr"/>
+      <c r="H503" s="4" t="inlineStr"/>
+      <c r="I503" s="4" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr"/>
@@ -15787,12 +14246,9 @@
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr"/>
       <c r="F504" t="inlineStr"/>
-      <c r="G504" s="2" t="inlineStr"/>
-      <c r="H504" s="2" t="inlineStr"/>
-      <c r="I504" s="2" t="inlineStr"/>
-      <c r="J504" s="2" t="inlineStr"/>
-      <c r="K504" s="2" t="inlineStr"/>
-      <c r="L504" s="2" t="inlineStr"/>
+      <c r="G504" s="4" t="inlineStr"/>
+      <c r="H504" s="4" t="inlineStr"/>
+      <c r="I504" s="4" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr"/>
@@ -15809,12 +14265,9 @@
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr"/>
       <c r="F505" t="inlineStr"/>
-      <c r="G505" s="2" t="inlineStr"/>
-      <c r="H505" s="2" t="inlineStr"/>
-      <c r="I505" s="2" t="inlineStr"/>
-      <c r="J505" s="2" t="inlineStr"/>
-      <c r="K505" s="2" t="inlineStr"/>
-      <c r="L505" s="2" t="inlineStr"/>
+      <c r="G505" s="4" t="inlineStr"/>
+      <c r="H505" s="4" t="inlineStr"/>
+      <c r="I505" s="4" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr"/>
@@ -15831,12 +14284,9 @@
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr"/>
       <c r="F506" t="inlineStr"/>
-      <c r="G506" s="2" t="inlineStr"/>
-      <c r="H506" s="2" t="inlineStr"/>
-      <c r="I506" s="2" t="inlineStr"/>
-      <c r="J506" s="2" t="inlineStr"/>
-      <c r="K506" s="2" t="inlineStr"/>
-      <c r="L506" s="2" t="inlineStr"/>
+      <c r="G506" s="4" t="inlineStr"/>
+      <c r="H506" s="4" t="inlineStr"/>
+      <c r="I506" s="4" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr"/>
@@ -15853,24 +14303,21 @@
       <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr"/>
       <c r="F507" t="inlineStr"/>
-      <c r="G507" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H507" s="2" t="inlineStr"/>
-      <c r="I507" s="2" t="inlineStr">
+      <c r="G507" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="H507" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="J507" s="2" t="inlineStr"/>
-      <c r="K507" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L507" s="2" t="inlineStr"/>
+      <c r="I507" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr"/>
@@ -15887,12 +14334,9 @@
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr"/>
       <c r="F508" t="inlineStr"/>
-      <c r="G508" s="2" t="inlineStr"/>
-      <c r="H508" s="2" t="inlineStr"/>
-      <c r="I508" s="2" t="inlineStr"/>
-      <c r="J508" s="2" t="inlineStr"/>
-      <c r="K508" s="2" t="inlineStr"/>
-      <c r="L508" s="2" t="inlineStr"/>
+      <c r="G508" s="4" t="inlineStr"/>
+      <c r="H508" s="4" t="inlineStr"/>
+      <c r="I508" s="4" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr"/>
@@ -15909,12 +14353,9 @@
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr"/>
       <c r="F509" t="inlineStr"/>
-      <c r="G509" s="2" t="inlineStr"/>
-      <c r="H509" s="2" t="inlineStr"/>
-      <c r="I509" s="2" t="inlineStr"/>
-      <c r="J509" s="2" t="inlineStr"/>
-      <c r="K509" s="2" t="inlineStr"/>
-      <c r="L509" s="2" t="inlineStr"/>
+      <c r="G509" s="4" t="inlineStr"/>
+      <c r="H509" s="4" t="inlineStr"/>
+      <c r="I509" s="4" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr"/>
@@ -15931,12 +14372,9 @@
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr"/>
       <c r="F510" t="inlineStr"/>
-      <c r="G510" s="2" t="inlineStr"/>
-      <c r="H510" s="2" t="inlineStr"/>
-      <c r="I510" s="2" t="inlineStr"/>
-      <c r="J510" s="2" t="inlineStr"/>
-      <c r="K510" s="2" t="inlineStr"/>
-      <c r="L510" s="2" t="inlineStr"/>
+      <c r="G510" s="4" t="inlineStr"/>
+      <c r="H510" s="4" t="inlineStr"/>
+      <c r="I510" s="4" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr"/>
@@ -15953,12 +14391,9 @@
       <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr"/>
       <c r="F511" t="inlineStr"/>
-      <c r="G511" s="2" t="inlineStr"/>
-      <c r="H511" s="2" t="inlineStr"/>
-      <c r="I511" s="2" t="inlineStr"/>
-      <c r="J511" s="2" t="inlineStr"/>
-      <c r="K511" s="2" t="inlineStr"/>
-      <c r="L511" s="2" t="inlineStr"/>
+      <c r="G511" s="4" t="inlineStr"/>
+      <c r="H511" s="4" t="inlineStr"/>
+      <c r="I511" s="4" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr"/>
@@ -15975,12 +14410,9 @@
       <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr"/>
       <c r="F512" t="inlineStr"/>
-      <c r="G512" s="2" t="inlineStr"/>
-      <c r="H512" s="2" t="inlineStr"/>
-      <c r="I512" s="2" t="inlineStr"/>
-      <c r="J512" s="2" t="inlineStr"/>
-      <c r="K512" s="2" t="inlineStr"/>
-      <c r="L512" s="2" t="inlineStr"/>
+      <c r="G512" s="4" t="inlineStr"/>
+      <c r="H512" s="4" t="inlineStr"/>
+      <c r="I512" s="4" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr"/>
@@ -15997,12 +14429,9 @@
       <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr"/>
       <c r="F513" t="inlineStr"/>
-      <c r="G513" s="2" t="inlineStr"/>
-      <c r="H513" s="2" t="inlineStr"/>
-      <c r="I513" s="2" t="inlineStr"/>
-      <c r="J513" s="2" t="inlineStr"/>
-      <c r="K513" s="2" t="inlineStr"/>
-      <c r="L513" s="2" t="inlineStr"/>
+      <c r="G513" s="4" t="inlineStr"/>
+      <c r="H513" s="4" t="inlineStr"/>
+      <c r="I513" s="4" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr"/>
@@ -16019,12 +14448,9 @@
       <c r="D514" t="inlineStr"/>
       <c r="E514" t="inlineStr"/>
       <c r="F514" t="inlineStr"/>
-      <c r="G514" s="2" t="inlineStr"/>
-      <c r="H514" s="2" t="inlineStr"/>
-      <c r="I514" s="2" t="inlineStr"/>
-      <c r="J514" s="2" t="inlineStr"/>
-      <c r="K514" s="2" t="inlineStr"/>
-      <c r="L514" s="2" t="inlineStr"/>
+      <c r="G514" s="4" t="inlineStr"/>
+      <c r="H514" s="4" t="inlineStr"/>
+      <c r="I514" s="4" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr"/>
@@ -16041,12 +14467,9 @@
       <c r="D515" t="inlineStr"/>
       <c r="E515" t="inlineStr"/>
       <c r="F515" t="inlineStr"/>
-      <c r="G515" s="2" t="inlineStr"/>
-      <c r="H515" s="2" t="inlineStr"/>
-      <c r="I515" s="2" t="inlineStr"/>
-      <c r="J515" s="2" t="inlineStr"/>
-      <c r="K515" s="2" t="inlineStr"/>
-      <c r="L515" s="2" t="inlineStr"/>
+      <c r="G515" s="4" t="inlineStr"/>
+      <c r="H515" s="4" t="inlineStr"/>
+      <c r="I515" s="4" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr"/>
@@ -16063,12 +14486,9 @@
       <c r="D516" t="inlineStr"/>
       <c r="E516" t="inlineStr"/>
       <c r="F516" t="inlineStr"/>
-      <c r="G516" s="2" t="inlineStr"/>
-      <c r="H516" s="2" t="inlineStr"/>
-      <c r="I516" s="2" t="inlineStr"/>
-      <c r="J516" s="2" t="inlineStr"/>
-      <c r="K516" s="2" t="inlineStr"/>
-      <c r="L516" s="2" t="inlineStr"/>
+      <c r="G516" s="4" t="inlineStr"/>
+      <c r="H516" s="4" t="inlineStr"/>
+      <c r="I516" s="4" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr"/>
@@ -16085,12 +14505,9 @@
       <c r="D517" t="inlineStr"/>
       <c r="E517" t="inlineStr"/>
       <c r="F517" t="inlineStr"/>
-      <c r="G517" s="2" t="inlineStr"/>
-      <c r="H517" s="2" t="inlineStr"/>
-      <c r="I517" s="2" t="inlineStr"/>
-      <c r="J517" s="2" t="inlineStr"/>
-      <c r="K517" s="2" t="inlineStr"/>
-      <c r="L517" s="2" t="inlineStr"/>
+      <c r="G517" s="4" t="inlineStr"/>
+      <c r="H517" s="4" t="inlineStr"/>
+      <c r="I517" s="4" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr"/>
@@ -16107,12 +14524,9 @@
       <c r="D518" t="inlineStr"/>
       <c r="E518" t="inlineStr"/>
       <c r="F518" t="inlineStr"/>
-      <c r="G518" s="2" t="inlineStr"/>
-      <c r="H518" s="2" t="inlineStr"/>
-      <c r="I518" s="2" t="inlineStr"/>
-      <c r="J518" s="2" t="inlineStr"/>
-      <c r="K518" s="2" t="inlineStr"/>
-      <c r="L518" s="2" t="inlineStr"/>
+      <c r="G518" s="4" t="inlineStr"/>
+      <c r="H518" s="4" t="inlineStr"/>
+      <c r="I518" s="4" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr"/>
@@ -16129,12 +14543,9 @@
       <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr"/>
       <c r="F519" t="inlineStr"/>
-      <c r="G519" s="2" t="inlineStr"/>
-      <c r="H519" s="2" t="inlineStr"/>
-      <c r="I519" s="2" t="inlineStr"/>
-      <c r="J519" s="2" t="inlineStr"/>
-      <c r="K519" s="2" t="inlineStr"/>
-      <c r="L519" s="2" t="inlineStr"/>
+      <c r="G519" s="4" t="inlineStr"/>
+      <c r="H519" s="4" t="inlineStr"/>
+      <c r="I519" s="4" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr"/>
@@ -16151,12 +14562,9 @@
       <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr"/>
       <c r="F520" t="inlineStr"/>
-      <c r="G520" s="2" t="inlineStr"/>
-      <c r="H520" s="2" t="inlineStr"/>
-      <c r="I520" s="2" t="inlineStr"/>
-      <c r="J520" s="2" t="inlineStr"/>
-      <c r="K520" s="2" t="inlineStr"/>
-      <c r="L520" s="2" t="inlineStr"/>
+      <c r="G520" s="4" t="inlineStr"/>
+      <c r="H520" s="4" t="inlineStr"/>
+      <c r="I520" s="4" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr"/>
@@ -16173,16 +14581,13 @@
       <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr"/>
-      <c r="G521" s="2" t="inlineStr"/>
-      <c r="H521" s="2" t="inlineStr"/>
-      <c r="I521" s="2" t="inlineStr"/>
-      <c r="J521" s="2" t="inlineStr"/>
-      <c r="K521" s="4" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="L521" s="2" t="inlineStr"/>
+      <c r="G521" s="4" t="inlineStr"/>
+      <c r="H521" s="4" t="inlineStr"/>
+      <c r="I521" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr"/>
@@ -16199,12 +14604,9 @@
       <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr"/>
       <c r="F522" t="inlineStr"/>
-      <c r="G522" s="2" t="inlineStr"/>
-      <c r="H522" s="2" t="inlineStr"/>
-      <c r="I522" s="2" t="inlineStr"/>
-      <c r="J522" s="2" t="inlineStr"/>
-      <c r="K522" s="2" t="inlineStr"/>
-      <c r="L522" s="2" t="inlineStr"/>
+      <c r="G522" s="4" t="inlineStr"/>
+      <c r="H522" s="4" t="inlineStr"/>
+      <c r="I522" s="4" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr"/>
@@ -16221,12 +14623,9 @@
       <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr"/>
       <c r="F523" t="inlineStr"/>
-      <c r="G523" s="2" t="inlineStr"/>
-      <c r="H523" s="2" t="inlineStr"/>
-      <c r="I523" s="2" t="inlineStr"/>
-      <c r="J523" s="2" t="inlineStr"/>
-      <c r="K523" s="2" t="inlineStr"/>
-      <c r="L523" s="2" t="inlineStr"/>
+      <c r="G523" s="4" t="inlineStr"/>
+      <c r="H523" s="4" t="inlineStr"/>
+      <c r="I523" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backlinks.xlsx
+++ b/backlinks.xlsx
@@ -491,17 +491,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>extractkeywords</t>
+          <t>extractkeywords.com</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>heicpdf</t>
+          <t>heicpdf.to</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>tryschedule</t>
+          <t>tryschedule.com</t>
         </is>
       </c>
     </row>

--- a/backlinks.xlsx
+++ b/backlinks.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I523"/>
+  <dimension ref="A1:H523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -486,20 +486,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>extractkeywords.com</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>extractkeywords.com</t>
+          <t>heicpdf.to</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>heicpdf.to</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tryschedule.com</t>
         </is>
@@ -531,22 +526,17 @@
           <t>77</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -578,22 +568,17 @@
           <t>54</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>multi</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -621,22 +606,17 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -660,14 +640,9 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -691,9 +666,9 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>zh</t>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -702,11 +677,6 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -734,18 +704,13 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -773,18 +738,13 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -808,9 +768,9 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>zh</t>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -819,11 +779,6 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -851,18 +806,13 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -886,18 +836,13 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -925,18 +870,13 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -960,18 +900,13 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -995,18 +930,13 @@
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1030,18 +960,13 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1065,9 +990,9 @@
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1076,11 +1001,6 @@
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1108,18 +1028,13 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
+      <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1143,9 +1058,9 @@
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1154,11 +1069,6 @@
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1186,9 +1096,9 @@
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1197,11 +1107,6 @@
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1229,14 +1134,9 @@
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1260,18 +1160,13 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
+      <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1295,18 +1190,13 @@
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1330,18 +1220,13 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1365,18 +1250,13 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1400,18 +1280,13 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1435,18 +1310,13 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
+      <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1470,14 +1340,9 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1501,14 +1366,9 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1532,14 +1392,9 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1563,9 +1418,9 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1574,11 +1429,6 @@
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -1606,14 +1456,9 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1637,9 +1482,9 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -1648,11 +1493,6 @@
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -1680,14 +1520,9 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1711,14 +1546,9 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1742,14 +1572,9 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1773,14 +1598,9 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1804,14 +1624,9 @@
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1835,14 +1650,9 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1866,14 +1676,9 @@
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1897,14 +1702,9 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1928,14 +1728,9 @@
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1959,14 +1754,9 @@
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1990,9 +1780,9 @@
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>zh</t>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2001,11 +1791,6 @@
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2033,9 +1818,9 @@
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2044,11 +1829,6 @@
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2076,9 +1856,9 @@
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -2087,11 +1867,6 @@
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -2119,9 +1894,9 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2130,11 +1905,6 @@
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2162,9 +1932,9 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -2173,11 +1943,6 @@
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2205,18 +1970,13 @@
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2240,18 +2000,13 @@
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr"/>
-      <c r="I49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2275,9 +2030,9 @@
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>multi</t>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -2286,11 +2041,6 @@
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2318,9 +2068,9 @@
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -2329,11 +2079,6 @@
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2361,9 +2106,9 @@
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -2372,11 +2117,6 @@
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -2404,18 +2144,13 @@
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr"/>
-      <c r="I53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2439,18 +2174,13 @@
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2474,14 +2204,9 @@
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr"/>
-      <c r="I55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2505,14 +2230,9 @@
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr"/>
-      <c r="I56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2536,14 +2256,9 @@
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2567,14 +2282,9 @@
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2598,14 +2308,9 @@
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr"/>
-      <c r="I59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2629,14 +2334,9 @@
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr"/>
-      <c r="I60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2660,14 +2360,9 @@
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr"/>
-      <c r="I61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2691,14 +2386,9 @@
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="inlineStr"/>
       <c r="H62" s="4" t="inlineStr"/>
-      <c r="I62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2722,14 +2412,9 @@
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr"/>
-      <c r="I63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2753,14 +2438,9 @@
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="inlineStr"/>
       <c r="H64" s="4" t="inlineStr"/>
-      <c r="I64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2784,14 +2464,9 @@
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr"/>
-      <c r="I65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2815,14 +2490,9 @@
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="inlineStr"/>
       <c r="H66" s="4" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2846,14 +2516,9 @@
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="inlineStr"/>
-      <c r="I67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2877,14 +2542,9 @@
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="4" t="inlineStr"/>
-      <c r="I68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2908,14 +2568,9 @@
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr"/>
-      <c r="I69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2939,14 +2594,9 @@
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="inlineStr"/>
       <c r="H70" s="4" t="inlineStr"/>
-      <c r="I70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2970,14 +2620,9 @@
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="4" t="inlineStr"/>
-      <c r="I71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3001,14 +2646,9 @@
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr"/>
-      <c r="I72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3032,14 +2672,9 @@
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="4" t="inlineStr"/>
-      <c r="I73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3063,14 +2698,9 @@
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3094,14 +2724,9 @@
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="4" t="inlineStr"/>
-      <c r="I75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3125,14 +2750,9 @@
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="inlineStr"/>
       <c r="H76" s="4" t="inlineStr"/>
-      <c r="I76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3156,14 +2776,9 @@
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr"/>
-      <c r="I77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3187,14 +2802,9 @@
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="4" t="inlineStr"/>
-      <c r="I78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3218,14 +2828,9 @@
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr"/>
-      <c r="I79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3249,14 +2854,9 @@
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="inlineStr"/>
       <c r="H80" s="4" t="inlineStr"/>
-      <c r="I80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3280,14 +2880,9 @@
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="inlineStr"/>
       <c r="H81" s="4" t="inlineStr"/>
-      <c r="I81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3311,14 +2906,9 @@
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="inlineStr"/>
       <c r="H82" s="4" t="inlineStr"/>
-      <c r="I82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3342,14 +2932,9 @@
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="4" t="inlineStr"/>
-      <c r="I83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3373,14 +2958,9 @@
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="inlineStr"/>
       <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3404,14 +2984,9 @@
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr"/>
-      <c r="I85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3435,14 +3010,9 @@
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="inlineStr"/>
       <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3466,14 +3036,9 @@
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="inlineStr"/>
       <c r="H87" s="4" t="inlineStr"/>
-      <c r="I87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3497,14 +3062,9 @@
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="inlineStr"/>
       <c r="H88" s="4" t="inlineStr"/>
-      <c r="I88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3528,14 +3088,9 @@
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="inlineStr"/>
       <c r="H89" s="4" t="inlineStr"/>
-      <c r="I89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3559,14 +3114,9 @@
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="inlineStr"/>
       <c r="H90" s="4" t="inlineStr"/>
-      <c r="I90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3590,14 +3140,9 @@
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr"/>
-      <c r="I91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3621,14 +3166,9 @@
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="inlineStr"/>
       <c r="H92" s="4" t="inlineStr"/>
-      <c r="I92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3652,14 +3192,9 @@
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>multi</t>
-        </is>
-      </c>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="inlineStr"/>
       <c r="H93" s="4" t="inlineStr"/>
-      <c r="I93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3683,14 +3218,9 @@
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="inlineStr"/>
       <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3714,14 +3244,9 @@
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="inlineStr"/>
       <c r="H95" s="4" t="inlineStr"/>
-      <c r="I95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3745,14 +3270,9 @@
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="inlineStr"/>
       <c r="H96" s="4" t="inlineStr"/>
-      <c r="I96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3776,14 +3296,9 @@
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr"/>
-      <c r="I97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3807,14 +3322,9 @@
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="inlineStr"/>
       <c r="H98" s="4" t="inlineStr"/>
-      <c r="I98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3838,14 +3348,9 @@
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="inlineStr"/>
       <c r="H99" s="4" t="inlineStr"/>
-      <c r="I99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3869,14 +3374,9 @@
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="inlineStr"/>
       <c r="H100" s="4" t="inlineStr"/>
-      <c r="I100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3900,14 +3400,9 @@
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3931,14 +3426,9 @@
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="inlineStr"/>
       <c r="H102" s="4" t="inlineStr"/>
-      <c r="I102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3962,14 +3452,9 @@
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="inlineStr"/>
       <c r="H103" s="4" t="inlineStr"/>
-      <c r="I103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3993,14 +3478,9 @@
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F104" s="4" t="inlineStr"/>
       <c r="G104" s="4" t="inlineStr"/>
       <c r="H104" s="4" t="inlineStr"/>
-      <c r="I104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4024,14 +3504,9 @@
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F105" s="4" t="inlineStr"/>
       <c r="G105" s="4" t="inlineStr"/>
       <c r="H105" s="4" t="inlineStr"/>
-      <c r="I105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4055,14 +3530,9 @@
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F106" s="4" t="inlineStr"/>
       <c r="G106" s="4" t="inlineStr"/>
       <c r="H106" s="4" t="inlineStr"/>
-      <c r="I106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4086,14 +3556,9 @@
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="4" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr"/>
-      <c r="I107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4117,14 +3582,9 @@
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="4" t="inlineStr"/>
       <c r="H108" s="4" t="inlineStr"/>
-      <c r="I108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4148,14 +3608,9 @@
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="inlineStr"/>
       <c r="H109" s="4" t="inlineStr"/>
-      <c r="I109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4179,14 +3634,9 @@
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="inlineStr"/>
       <c r="H110" s="4" t="inlineStr"/>
-      <c r="I110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4210,14 +3660,9 @@
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="inlineStr"/>
       <c r="H111" s="4" t="inlineStr"/>
-      <c r="I111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4241,14 +3686,9 @@
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="inlineStr"/>
       <c r="H112" s="4" t="inlineStr"/>
-      <c r="I112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4272,14 +3712,9 @@
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr"/>
-      <c r="I113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4303,14 +3738,9 @@
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="inlineStr"/>
       <c r="H114" s="4" t="inlineStr"/>
-      <c r="I114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4334,14 +3764,9 @@
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="inlineStr"/>
       <c r="H115" s="4" t="inlineStr"/>
-      <c r="I115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4365,14 +3790,9 @@
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="inlineStr"/>
       <c r="H116" s="4" t="inlineStr"/>
-      <c r="I116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4396,14 +3816,9 @@
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="inlineStr"/>
       <c r="H117" s="4" t="inlineStr"/>
-      <c r="I117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4427,14 +3842,9 @@
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="inlineStr"/>
       <c r="H118" s="4" t="inlineStr"/>
-      <c r="I118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4458,14 +3868,9 @@
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="inlineStr"/>
       <c r="H119" s="4" t="inlineStr"/>
-      <c r="I119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4489,14 +3894,9 @@
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="inlineStr"/>
       <c r="H120" s="4" t="inlineStr"/>
-      <c r="I120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4520,14 +3920,9 @@
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="inlineStr"/>
       <c r="H121" s="4" t="inlineStr"/>
-      <c r="I121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4551,14 +3946,9 @@
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="inlineStr"/>
       <c r="H122" s="4" t="inlineStr"/>
-      <c r="I122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4582,14 +3972,9 @@
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="inlineStr"/>
       <c r="H123" s="4" t="inlineStr"/>
-      <c r="I123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4613,14 +3998,9 @@
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>multi</t>
-        </is>
-      </c>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="inlineStr"/>
       <c r="H124" s="4" t="inlineStr"/>
-      <c r="I124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4644,14 +4024,9 @@
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="inlineStr"/>
       <c r="H125" s="4" t="inlineStr"/>
-      <c r="I125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4675,14 +4050,9 @@
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="inlineStr"/>
       <c r="H126" s="4" t="inlineStr"/>
-      <c r="I126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4706,14 +4076,9 @@
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="inlineStr"/>
       <c r="H127" s="4" t="inlineStr"/>
-      <c r="I127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4737,14 +4102,9 @@
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="inlineStr"/>
       <c r="H128" s="4" t="inlineStr"/>
-      <c r="I128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4768,14 +4128,9 @@
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="inlineStr"/>
       <c r="H129" s="4" t="inlineStr"/>
-      <c r="I129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4799,14 +4154,9 @@
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="inlineStr"/>
       <c r="H130" s="4" t="inlineStr"/>
-      <c r="I130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4830,14 +4180,9 @@
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="inlineStr"/>
       <c r="H131" s="4" t="inlineStr"/>
-      <c r="I131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4861,14 +4206,9 @@
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="inlineStr"/>
       <c r="H132" s="4" t="inlineStr"/>
-      <c r="I132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4892,14 +4232,9 @@
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="inlineStr"/>
       <c r="H133" s="4" t="inlineStr"/>
-      <c r="I133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4923,14 +4258,9 @@
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="inlineStr"/>
       <c r="H134" s="4" t="inlineStr"/>
-      <c r="I134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4954,14 +4284,9 @@
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="inlineStr"/>
       <c r="H135" s="4" t="inlineStr"/>
-      <c r="I135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4985,14 +4310,9 @@
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="inlineStr"/>
       <c r="H136" s="4" t="inlineStr"/>
-      <c r="I136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5016,14 +4336,9 @@
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr"/>
-      <c r="I137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5047,14 +4362,9 @@
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="inlineStr"/>
       <c r="H138" s="4" t="inlineStr"/>
-      <c r="I138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5078,14 +4388,9 @@
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="inlineStr"/>
       <c r="H139" s="4" t="inlineStr"/>
-      <c r="I139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5109,14 +4414,9 @@
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="inlineStr"/>
       <c r="H140" s="4" t="inlineStr"/>
-      <c r="I140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5140,14 +4440,9 @@
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="inlineStr"/>
       <c r="H141" s="4" t="inlineStr"/>
-      <c r="I141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5171,14 +4466,9 @@
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="inlineStr"/>
       <c r="H142" s="4" t="inlineStr"/>
-      <c r="I142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5202,14 +4492,9 @@
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="inlineStr"/>
       <c r="H143" s="4" t="inlineStr"/>
-      <c r="I143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5233,14 +4518,9 @@
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="inlineStr"/>
       <c r="H144" s="4" t="inlineStr"/>
-      <c r="I144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5264,14 +4544,9 @@
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="inlineStr"/>
       <c r="H145" s="4" t="inlineStr"/>
-      <c r="I145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5295,14 +4570,9 @@
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="inlineStr"/>
       <c r="H146" s="4" t="inlineStr"/>
-      <c r="I146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5326,14 +4596,9 @@
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="inlineStr"/>
       <c r="H147" s="4" t="inlineStr"/>
-      <c r="I147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5357,14 +4622,9 @@
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="inlineStr"/>
       <c r="H148" s="4" t="inlineStr"/>
-      <c r="I148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5388,14 +4648,9 @@
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="inlineStr"/>
       <c r="H149" s="4" t="inlineStr"/>
-      <c r="I149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5419,14 +4674,9 @@
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="inlineStr"/>
       <c r="H150" s="4" t="inlineStr"/>
-      <c r="I150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5450,14 +4700,9 @@
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr"/>
-      <c r="I151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5481,14 +4726,9 @@
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr"/>
-      <c r="I152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5512,14 +4752,13 @@
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr"/>
-      <c r="I153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5543,14 +4782,9 @@
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="inlineStr"/>
       <c r="H154" s="4" t="inlineStr"/>
-      <c r="I154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5574,14 +4808,13 @@
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
       <c r="H155" s="4" t="inlineStr"/>
-      <c r="I155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5605,14 +4838,9 @@
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="inlineStr"/>
       <c r="H156" s="4" t="inlineStr"/>
-      <c r="I156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5636,14 +4864,17 @@
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>需付费</t>
+        </is>
+      </c>
       <c r="H157" s="4" t="inlineStr"/>
-      <c r="I157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5667,14 +4898,9 @@
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="inlineStr"/>
       <c r="H158" s="4" t="inlineStr"/>
-      <c r="I158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5698,14 +4924,13 @@
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>zh</t>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>失败</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
       <c r="H159" s="4" t="inlineStr"/>
-      <c r="I159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5729,14 +4954,9 @@
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F160" s="4" t="inlineStr"/>
       <c r="G160" s="4" t="inlineStr"/>
       <c r="H160" s="4" t="inlineStr"/>
-      <c r="I160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5760,14 +4980,9 @@
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F161" s="4" t="inlineStr"/>
       <c r="G161" s="4" t="inlineStr"/>
       <c r="H161" s="4" t="inlineStr"/>
-      <c r="I161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -5787,18 +5002,17 @@
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I162" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -5826,18 +5040,17 @@
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I163" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -5861,18 +5074,17 @@
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I164" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -5896,18 +5108,17 @@
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I165" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -5931,18 +5142,17 @@
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I166" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -5966,18 +5176,17 @@
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I167" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6001,18 +5210,17 @@
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I168" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6036,18 +5244,17 @@
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I169" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6071,18 +5278,17 @@
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6106,18 +5312,17 @@
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I171" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6141,18 +5346,17 @@
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6176,10 +5380,9 @@
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+      <c r="F173" s="4" t="inlineStr"/>
       <c r="G173" s="4" t="inlineStr"/>
-      <c r="H173" s="4" t="inlineStr"/>
-      <c r="I173" s="4" t="inlineStr">
+      <c r="H173" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -6203,10 +5406,9 @@
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" s="4" t="inlineStr"/>
       <c r="G174" s="4" t="inlineStr"/>
-      <c r="H174" s="4" t="inlineStr"/>
-      <c r="I174" s="4" t="inlineStr">
+      <c r="H174" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -6230,10 +5432,9 @@
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" s="4" t="inlineStr"/>
       <c r="G175" s="4" t="inlineStr"/>
-      <c r="H175" s="4" t="inlineStr"/>
-      <c r="I175" s="4" t="inlineStr">
+      <c r="H175" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -6257,10 +5458,9 @@
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" s="4" t="inlineStr"/>
       <c r="G176" s="4" t="inlineStr"/>
-      <c r="H176" s="4" t="inlineStr"/>
-      <c r="I176" s="4" t="inlineStr">
+      <c r="H176" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -6284,10 +5484,9 @@
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+      <c r="F177" s="4" t="inlineStr"/>
       <c r="G177" s="4" t="inlineStr"/>
-      <c r="H177" s="4" t="inlineStr"/>
-      <c r="I177" s="4" t="inlineStr">
+      <c r="H177" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -6311,10 +5510,9 @@
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" s="4" t="inlineStr"/>
       <c r="G178" s="4" t="inlineStr"/>
-      <c r="H178" s="4" t="inlineStr"/>
-      <c r="I178" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
@@ -6338,10 +5536,9 @@
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" s="4" t="inlineStr"/>
       <c r="G179" s="4" t="inlineStr"/>
-      <c r="H179" s="4" t="inlineStr"/>
-      <c r="I179" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
@@ -6365,10 +5562,9 @@
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" s="4" t="inlineStr"/>
       <c r="G180" s="4" t="inlineStr"/>
-      <c r="H180" s="4" t="inlineStr"/>
-      <c r="I180" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
@@ -6392,10 +5588,9 @@
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+      <c r="F181" s="4" t="inlineStr"/>
       <c r="G181" s="4" t="inlineStr"/>
-      <c r="H181" s="4" t="inlineStr"/>
-      <c r="I181" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
@@ -6419,10 +5614,9 @@
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" s="4" t="inlineStr"/>
       <c r="G182" s="4" t="inlineStr"/>
-      <c r="H182" s="4" t="inlineStr"/>
-      <c r="I182" s="4" t="inlineStr">
+      <c r="H182" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -6450,18 +5644,13 @@
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="G183" s="4" t="inlineStr">
+      <c r="F183" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G183" s="4" t="inlineStr"/>
       <c r="H183" s="4" t="inlineStr"/>
-      <c r="I183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6485,18 +5674,13 @@
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="G184" s="4" t="inlineStr">
+      <c r="F184" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G184" s="4" t="inlineStr"/>
       <c r="H184" s="4" t="inlineStr"/>
-      <c r="I184" s="4" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6520,18 +5704,13 @@
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="G185" s="4" t="inlineStr">
+      <c r="F185" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G185" s="4" t="inlineStr"/>
       <c r="H185" s="4" t="inlineStr"/>
-      <c r="I185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6555,18 +5734,13 @@
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="inlineStr">
+      <c r="F186" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G186" s="4" t="inlineStr"/>
       <c r="H186" s="4" t="inlineStr"/>
-      <c r="I186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6590,18 +5764,13 @@
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G187" s="4" t="inlineStr">
+      <c r="F187" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G187" s="4" t="inlineStr"/>
       <c r="H187" s="4" t="inlineStr"/>
-      <c r="I187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6625,18 +5794,13 @@
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G188" s="4" t="inlineStr">
+      <c r="F188" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G188" s="4" t="inlineStr"/>
       <c r="H188" s="4" t="inlineStr"/>
-      <c r="I188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6660,18 +5824,13 @@
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="G189" s="4" t="inlineStr">
+      <c r="F189" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G189" s="4" t="inlineStr"/>
       <c r="H189" s="4" t="inlineStr"/>
-      <c r="I189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6695,18 +5854,13 @@
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="G190" s="4" t="inlineStr">
+      <c r="F190" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G190" s="4" t="inlineStr"/>
       <c r="H190" s="4" t="inlineStr"/>
-      <c r="I190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6730,18 +5884,13 @@
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="G191" s="4" t="inlineStr">
+      <c r="F191" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G191" s="4" t="inlineStr"/>
       <c r="H191" s="4" t="inlineStr"/>
-      <c r="I191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6765,18 +5914,13 @@
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="G192" s="4" t="inlineStr">
+      <c r="F192" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G192" s="4" t="inlineStr"/>
       <c r="H192" s="4" t="inlineStr"/>
-      <c r="I192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6800,18 +5944,13 @@
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G193" s="4" t="inlineStr">
+      <c r="F193" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G193" s="4" t="inlineStr"/>
       <c r="H193" s="4" t="inlineStr"/>
-      <c r="I193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6835,18 +5974,13 @@
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G194" s="4" t="inlineStr">
+      <c r="F194" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G194" s="4" t="inlineStr"/>
       <c r="H194" s="4" t="inlineStr"/>
-      <c r="I194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6870,18 +6004,13 @@
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G195" s="4" t="inlineStr">
+      <c r="F195" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G195" s="4" t="inlineStr"/>
       <c r="H195" s="4" t="inlineStr"/>
-      <c r="I195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6905,18 +6034,13 @@
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G196" s="4" t="inlineStr">
+      <c r="F196" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G196" s="4" t="inlineStr"/>
       <c r="H196" s="4" t="inlineStr"/>
-      <c r="I196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6940,18 +6064,13 @@
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G197" s="4" t="inlineStr">
+      <c r="F197" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G197" s="4" t="inlineStr"/>
       <c r="H197" s="4" t="inlineStr"/>
-      <c r="I197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6975,18 +6094,13 @@
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G198" s="4" t="inlineStr">
+      <c r="F198" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G198" s="4" t="inlineStr"/>
       <c r="H198" s="4" t="inlineStr"/>
-      <c r="I198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7010,18 +6124,13 @@
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G199" s="4" t="inlineStr">
+      <c r="F199" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G199" s="4" t="inlineStr"/>
       <c r="H199" s="4" t="inlineStr"/>
-      <c r="I199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7045,18 +6154,13 @@
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G200" s="4" t="inlineStr">
+      <c r="F200" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G200" s="4" t="inlineStr"/>
       <c r="H200" s="4" t="inlineStr"/>
-      <c r="I200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7080,18 +6184,13 @@
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G201" s="4" t="inlineStr">
+      <c r="F201" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G201" s="4" t="inlineStr"/>
       <c r="H201" s="4" t="inlineStr"/>
-      <c r="I201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7115,18 +6214,13 @@
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="G202" s="4" t="inlineStr">
+      <c r="F202" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G202" s="4" t="inlineStr"/>
       <c r="H202" s="4" t="inlineStr"/>
-      <c r="I202" s="4" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7150,18 +6244,13 @@
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G203" s="4" t="inlineStr">
+      <c r="F203" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G203" s="4" t="inlineStr"/>
       <c r="H203" s="4" t="inlineStr"/>
-      <c r="I203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7185,18 +6274,13 @@
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G204" s="4" t="inlineStr">
+      <c r="F204" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G204" s="4" t="inlineStr"/>
       <c r="H204" s="4" t="inlineStr"/>
-      <c r="I204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7220,18 +6304,13 @@
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G205" s="4" t="inlineStr">
+      <c r="F205" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G205" s="4" t="inlineStr"/>
       <c r="H205" s="4" t="inlineStr"/>
-      <c r="I205" s="4" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7255,18 +6334,13 @@
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G206" s="4" t="inlineStr">
+      <c r="F206" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G206" s="4" t="inlineStr"/>
       <c r="H206" s="4" t="inlineStr"/>
-      <c r="I206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7290,18 +6364,13 @@
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="inlineStr">
+      <c r="F207" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G207" s="4" t="inlineStr"/>
       <c r="H207" s="4" t="inlineStr"/>
-      <c r="I207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7325,18 +6394,13 @@
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G208" s="4" t="inlineStr">
+      <c r="F208" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G208" s="4" t="inlineStr"/>
       <c r="H208" s="4" t="inlineStr"/>
-      <c r="I208" s="4" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7360,18 +6424,13 @@
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G209" s="4" t="inlineStr">
+      <c r="F209" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G209" s="4" t="inlineStr"/>
       <c r="H209" s="4" t="inlineStr"/>
-      <c r="I209" s="4" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7395,18 +6454,13 @@
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G210" s="4" t="inlineStr">
+      <c r="F210" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G210" s="4" t="inlineStr"/>
       <c r="H210" s="4" t="inlineStr"/>
-      <c r="I210" s="4" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7426,10 +6480,9 @@
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
+      <c r="F211" s="4" t="inlineStr"/>
       <c r="G211" s="4" t="inlineStr"/>
       <c r="H211" s="4" t="inlineStr"/>
-      <c r="I211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7449,10 +6502,9 @@
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
+      <c r="F212" s="4" t="inlineStr"/>
       <c r="G212" s="4" t="inlineStr"/>
       <c r="H212" s="4" t="inlineStr"/>
-      <c r="I212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7472,10 +6524,9 @@
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
+      <c r="F213" s="4" t="inlineStr"/>
       <c r="G213" s="4" t="inlineStr"/>
       <c r="H213" s="4" t="inlineStr"/>
-      <c r="I213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7495,10 +6546,9 @@
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
+      <c r="F214" s="4" t="inlineStr"/>
       <c r="G214" s="4" t="inlineStr"/>
       <c r="H214" s="4" t="inlineStr"/>
-      <c r="I214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7518,10 +6568,9 @@
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
+      <c r="F215" s="4" t="inlineStr"/>
       <c r="G215" s="4" t="inlineStr"/>
       <c r="H215" s="4" t="inlineStr"/>
-      <c r="I215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7541,10 +6590,9 @@
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
+      <c r="F216" s="4" t="inlineStr"/>
       <c r="G216" s="4" t="inlineStr"/>
       <c r="H216" s="4" t="inlineStr"/>
-      <c r="I216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7564,10 +6612,9 @@
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
+      <c r="F217" s="4" t="inlineStr"/>
       <c r="G217" s="4" t="inlineStr"/>
       <c r="H217" s="4" t="inlineStr"/>
-      <c r="I217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7587,10 +6634,9 @@
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
+      <c r="F218" s="4" t="inlineStr"/>
       <c r="G218" s="4" t="inlineStr"/>
       <c r="H218" s="4" t="inlineStr"/>
-      <c r="I218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7610,10 +6656,9 @@
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="F219" s="4" t="inlineStr"/>
       <c r="G219" s="4" t="inlineStr"/>
       <c r="H219" s="4" t="inlineStr"/>
-      <c r="I219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7633,10 +6678,9 @@
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" s="4" t="inlineStr"/>
       <c r="G220" s="4" t="inlineStr"/>
       <c r="H220" s="4" t="inlineStr"/>
-      <c r="I220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7656,10 +6700,9 @@
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
+      <c r="F221" s="4" t="inlineStr"/>
       <c r="G221" s="4" t="inlineStr"/>
       <c r="H221" s="4" t="inlineStr"/>
-      <c r="I221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7679,10 +6722,9 @@
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
+      <c r="F222" s="4" t="inlineStr"/>
       <c r="G222" s="4" t="inlineStr"/>
       <c r="H222" s="4" t="inlineStr"/>
-      <c r="I222" s="4" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7702,10 +6744,9 @@
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
+      <c r="F223" s="4" t="inlineStr"/>
       <c r="G223" s="4" t="inlineStr"/>
       <c r="H223" s="4" t="inlineStr"/>
-      <c r="I223" s="4" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7725,10 +6766,9 @@
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
+      <c r="F224" s="4" t="inlineStr"/>
       <c r="G224" s="4" t="inlineStr"/>
       <c r="H224" s="4" t="inlineStr"/>
-      <c r="I224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7748,10 +6788,9 @@
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
+      <c r="F225" s="4" t="inlineStr"/>
       <c r="G225" s="4" t="inlineStr"/>
       <c r="H225" s="4" t="inlineStr"/>
-      <c r="I225" s="4" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7771,10 +6810,9 @@
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
+      <c r="F226" s="4" t="inlineStr"/>
       <c r="G226" s="4" t="inlineStr"/>
       <c r="H226" s="4" t="inlineStr"/>
-      <c r="I226" s="4" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7794,10 +6832,9 @@
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
+      <c r="F227" s="4" t="inlineStr"/>
       <c r="G227" s="4" t="inlineStr"/>
       <c r="H227" s="4" t="inlineStr"/>
-      <c r="I227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7817,10 +6854,9 @@
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
+      <c r="F228" s="4" t="inlineStr"/>
       <c r="G228" s="4" t="inlineStr"/>
       <c r="H228" s="4" t="inlineStr"/>
-      <c r="I228" s="4" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7840,10 +6876,9 @@
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
+      <c r="F229" s="4" t="inlineStr"/>
       <c r="G229" s="4" t="inlineStr"/>
       <c r="H229" s="4" t="inlineStr"/>
-      <c r="I229" s="4" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7863,10 +6898,9 @@
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
+      <c r="F230" s="4" t="inlineStr"/>
       <c r="G230" s="4" t="inlineStr"/>
       <c r="H230" s="4" t="inlineStr"/>
-      <c r="I230" s="4" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7886,10 +6920,9 @@
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
+      <c r="F231" s="4" t="inlineStr"/>
       <c r="G231" s="4" t="inlineStr"/>
       <c r="H231" s="4" t="inlineStr"/>
-      <c r="I231" s="4" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7909,10 +6942,9 @@
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
+      <c r="F232" s="4" t="inlineStr"/>
       <c r="G232" s="4" t="inlineStr"/>
       <c r="H232" s="4" t="inlineStr"/>
-      <c r="I232" s="4" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7932,10 +6964,9 @@
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
+      <c r="F233" s="4" t="inlineStr"/>
       <c r="G233" s="4" t="inlineStr"/>
       <c r="H233" s="4" t="inlineStr"/>
-      <c r="I233" s="4" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7955,10 +6986,9 @@
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
+      <c r="F234" s="4" t="inlineStr"/>
       <c r="G234" s="4" t="inlineStr"/>
       <c r="H234" s="4" t="inlineStr"/>
-      <c r="I234" s="4" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7978,10 +7008,9 @@
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+      <c r="F235" s="4" t="inlineStr"/>
       <c r="G235" s="4" t="inlineStr"/>
       <c r="H235" s="4" t="inlineStr"/>
-      <c r="I235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8005,14 +7034,9 @@
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F236" s="4" t="inlineStr"/>
       <c r="G236" s="4" t="inlineStr"/>
       <c r="H236" s="4" t="inlineStr"/>
-      <c r="I236" s="4" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8032,10 +7056,9 @@
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
+      <c r="F237" s="4" t="inlineStr"/>
       <c r="G237" s="4" t="inlineStr"/>
       <c r="H237" s="4" t="inlineStr"/>
-      <c r="I237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8055,10 +7078,9 @@
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
+      <c r="F238" s="4" t="inlineStr"/>
       <c r="G238" s="4" t="inlineStr"/>
       <c r="H238" s="4" t="inlineStr"/>
-      <c r="I238" s="4" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8078,10 +7100,9 @@
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
+      <c r="F239" s="4" t="inlineStr"/>
       <c r="G239" s="4" t="inlineStr"/>
       <c r="H239" s="4" t="inlineStr"/>
-      <c r="I239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8101,10 +7122,9 @@
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
+      <c r="F240" s="4" t="inlineStr"/>
       <c r="G240" s="4" t="inlineStr"/>
       <c r="H240" s="4" t="inlineStr"/>
-      <c r="I240" s="4" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8124,10 +7144,9 @@
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
+      <c r="F241" s="4" t="inlineStr"/>
       <c r="G241" s="4" t="inlineStr"/>
       <c r="H241" s="4" t="inlineStr"/>
-      <c r="I241" s="4" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8147,10 +7166,9 @@
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
+      <c r="F242" s="4" t="inlineStr"/>
       <c r="G242" s="4" t="inlineStr"/>
       <c r="H242" s="4" t="inlineStr"/>
-      <c r="I242" s="4" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8170,10 +7188,9 @@
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
+      <c r="F243" s="4" t="inlineStr"/>
       <c r="G243" s="4" t="inlineStr"/>
       <c r="H243" s="4" t="inlineStr"/>
-      <c r="I243" s="4" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8193,10 +7210,9 @@
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" s="4" t="inlineStr"/>
       <c r="G244" s="4" t="inlineStr"/>
       <c r="H244" s="4" t="inlineStr"/>
-      <c r="I244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8216,10 +7232,9 @@
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
+      <c r="F245" s="4" t="inlineStr"/>
       <c r="G245" s="4" t="inlineStr"/>
       <c r="H245" s="4" t="inlineStr"/>
-      <c r="I245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8239,10 +7254,9 @@
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
+      <c r="F246" s="4" t="inlineStr"/>
       <c r="G246" s="4" t="inlineStr"/>
       <c r="H246" s="4" t="inlineStr"/>
-      <c r="I246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8262,10 +7276,9 @@
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
+      <c r="F247" s="4" t="inlineStr"/>
       <c r="G247" s="4" t="inlineStr"/>
       <c r="H247" s="4" t="inlineStr"/>
-      <c r="I247" s="4" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8285,10 +7298,9 @@
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" s="4" t="inlineStr"/>
       <c r="G248" s="4" t="inlineStr"/>
       <c r="H248" s="4" t="inlineStr"/>
-      <c r="I248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8308,10 +7320,9 @@
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
+      <c r="F249" s="4" t="inlineStr"/>
       <c r="G249" s="4" t="inlineStr"/>
       <c r="H249" s="4" t="inlineStr"/>
-      <c r="I249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8331,10 +7342,9 @@
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
+      <c r="F250" s="4" t="inlineStr"/>
       <c r="G250" s="4" t="inlineStr"/>
       <c r="H250" s="4" t="inlineStr"/>
-      <c r="I250" s="4" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8354,10 +7364,9 @@
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
+      <c r="F251" s="4" t="inlineStr"/>
       <c r="G251" s="4" t="inlineStr"/>
       <c r="H251" s="4" t="inlineStr"/>
-      <c r="I251" s="4" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8377,10 +7386,9 @@
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
+      <c r="F252" s="4" t="inlineStr"/>
       <c r="G252" s="4" t="inlineStr"/>
       <c r="H252" s="4" t="inlineStr"/>
-      <c r="I252" s="4" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8400,10 +7408,9 @@
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
+      <c r="F253" s="4" t="inlineStr"/>
       <c r="G253" s="4" t="inlineStr"/>
       <c r="H253" s="4" t="inlineStr"/>
-      <c r="I253" s="4" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8423,10 +7430,9 @@
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
+      <c r="F254" s="4" t="inlineStr"/>
       <c r="G254" s="4" t="inlineStr"/>
       <c r="H254" s="4" t="inlineStr"/>
-      <c r="I254" s="4" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8446,10 +7452,9 @@
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
+      <c r="F255" s="4" t="inlineStr"/>
       <c r="G255" s="4" t="inlineStr"/>
       <c r="H255" s="4" t="inlineStr"/>
-      <c r="I255" s="4" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr"/>
@@ -8469,10 +7474,9 @@
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
+      <c r="F256" s="4" t="inlineStr"/>
       <c r="G256" s="4" t="inlineStr"/>
-      <c r="H256" s="4" t="inlineStr"/>
-      <c r="I256" s="4" t="inlineStr">
+      <c r="H256" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -8496,18 +7500,17 @@
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H257" s="4" t="inlineStr">
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="G257" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I257" s="3" t="inlineStr">
+      <c r="H257" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8531,10 +7534,9 @@
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
+      <c r="F258" s="4" t="inlineStr"/>
       <c r="G258" s="4" t="inlineStr"/>
-      <c r="H258" s="4" t="inlineStr"/>
-      <c r="I258" s="4" t="inlineStr">
+      <c r="H258" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -8558,10 +7560,9 @@
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
+      <c r="F259" s="4" t="inlineStr"/>
       <c r="G259" s="4" t="inlineStr"/>
       <c r="H259" s="4" t="inlineStr"/>
-      <c r="I259" s="4" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr"/>
@@ -8581,10 +7582,9 @@
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
+      <c r="F260" s="4" t="inlineStr"/>
       <c r="G260" s="4" t="inlineStr"/>
       <c r="H260" s="4" t="inlineStr"/>
-      <c r="I260" s="4" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8608,14 +7608,9 @@
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F261" s="4" t="inlineStr"/>
       <c r="G261" s="4" t="inlineStr"/>
       <c r="H261" s="4" t="inlineStr"/>
-      <c r="I261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8635,10 +7630,9 @@
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
+      <c r="F262" s="4" t="inlineStr"/>
       <c r="G262" s="4" t="inlineStr"/>
       <c r="H262" s="4" t="inlineStr"/>
-      <c r="I262" s="4" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8666,14 +7660,13 @@
           <t>77</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" s="4" t="inlineStr"/>
+      <c r="F263" s="4" t="inlineStr"/>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>需付费</t>
+        </is>
+      </c>
       <c r="H263" s="2" t="inlineStr">
-        <is>
-          <t>需付费</t>
-        </is>
-      </c>
-      <c r="I263" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -8701,14 +7694,9 @@
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F264" s="4" t="inlineStr"/>
       <c r="G264" s="4" t="inlineStr"/>
       <c r="H264" s="4" t="inlineStr"/>
-      <c r="I264" s="4" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8732,10 +7720,9 @@
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
+      <c r="F265" s="4" t="inlineStr"/>
       <c r="G265" s="4" t="inlineStr"/>
       <c r="H265" s="4" t="inlineStr"/>
-      <c r="I265" s="4" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8759,10 +7746,9 @@
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
+      <c r="F266" s="4" t="inlineStr"/>
       <c r="G266" s="4" t="inlineStr"/>
       <c r="H266" s="4" t="inlineStr"/>
-      <c r="I266" s="4" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8786,14 +7772,9 @@
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F267" s="4" t="inlineStr"/>
       <c r="G267" s="4" t="inlineStr"/>
       <c r="H267" s="4" t="inlineStr"/>
-      <c r="I267" s="4" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8817,10 +7798,9 @@
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
+      <c r="F268" s="4" t="inlineStr"/>
       <c r="G268" s="4" t="inlineStr"/>
       <c r="H268" s="4" t="inlineStr"/>
-      <c r="I268" s="4" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -8844,10 +7824,9 @@
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
+      <c r="F269" s="4" t="inlineStr"/>
       <c r="G269" s="4" t="inlineStr"/>
       <c r="H269" s="4" t="inlineStr"/>
-      <c r="I269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8871,10 +7850,9 @@
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
+      <c r="F270" s="4" t="inlineStr"/>
       <c r="G270" s="4" t="inlineStr"/>
       <c r="H270" s="4" t="inlineStr"/>
-      <c r="I270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8898,10 +7876,9 @@
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
+      <c r="F271" s="4" t="inlineStr"/>
       <c r="G271" s="4" t="inlineStr"/>
       <c r="H271" s="4" t="inlineStr"/>
-      <c r="I271" s="4" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8925,10 +7902,9 @@
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
+      <c r="F272" s="4" t="inlineStr"/>
       <c r="G272" s="4" t="inlineStr"/>
       <c r="H272" s="4" t="inlineStr"/>
-      <c r="I272" s="4" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8952,10 +7928,9 @@
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
+      <c r="F273" s="4" t="inlineStr"/>
       <c r="G273" s="4" t="inlineStr"/>
       <c r="H273" s="4" t="inlineStr"/>
-      <c r="I273" s="4" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8979,10 +7954,9 @@
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
+      <c r="F274" s="4" t="inlineStr"/>
       <c r="G274" s="4" t="inlineStr"/>
       <c r="H274" s="4" t="inlineStr"/>
-      <c r="I274" s="4" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9006,10 +7980,9 @@
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
+      <c r="F275" s="4" t="inlineStr"/>
       <c r="G275" s="4" t="inlineStr"/>
       <c r="H275" s="4" t="inlineStr"/>
-      <c r="I275" s="4" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9033,10 +8006,9 @@
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
+      <c r="F276" s="4" t="inlineStr"/>
       <c r="G276" s="4" t="inlineStr"/>
       <c r="H276" s="4" t="inlineStr"/>
-      <c r="I276" s="4" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9060,10 +8032,9 @@
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
+      <c r="F277" s="4" t="inlineStr"/>
       <c r="G277" s="4" t="inlineStr"/>
       <c r="H277" s="4" t="inlineStr"/>
-      <c r="I277" s="4" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9087,10 +8058,9 @@
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
+      <c r="F278" s="4" t="inlineStr"/>
       <c r="G278" s="4" t="inlineStr"/>
       <c r="H278" s="4" t="inlineStr"/>
-      <c r="I278" s="4" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9114,10 +8084,9 @@
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
+      <c r="F279" s="4" t="inlineStr"/>
       <c r="G279" s="4" t="inlineStr"/>
       <c r="H279" s="4" t="inlineStr"/>
-      <c r="I279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9141,10 +8110,9 @@
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
+      <c r="F280" s="4" t="inlineStr"/>
       <c r="G280" s="4" t="inlineStr"/>
       <c r="H280" s="4" t="inlineStr"/>
-      <c r="I280" s="4" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9168,10 +8136,9 @@
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
+      <c r="F281" s="4" t="inlineStr"/>
       <c r="G281" s="4" t="inlineStr"/>
       <c r="H281" s="4" t="inlineStr"/>
-      <c r="I281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9195,10 +8162,9 @@
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
+      <c r="F282" s="4" t="inlineStr"/>
       <c r="G282" s="4" t="inlineStr"/>
       <c r="H282" s="4" t="inlineStr"/>
-      <c r="I282" s="4" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9222,14 +8188,9 @@
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F283" s="4" t="inlineStr"/>
       <c r="G283" s="4" t="inlineStr"/>
       <c r="H283" s="4" t="inlineStr"/>
-      <c r="I283" s="4" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9253,14 +8214,9 @@
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F284" s="4" t="inlineStr"/>
       <c r="G284" s="4" t="inlineStr"/>
       <c r="H284" s="4" t="inlineStr"/>
-      <c r="I284" s="4" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9284,10 +8240,9 @@
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
+      <c r="F285" s="4" t="inlineStr"/>
       <c r="G285" s="4" t="inlineStr"/>
       <c r="H285" s="4" t="inlineStr"/>
-      <c r="I285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9311,10 +8266,9 @@
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
+      <c r="F286" s="4" t="inlineStr"/>
       <c r="G286" s="4" t="inlineStr"/>
       <c r="H286" s="4" t="inlineStr"/>
-      <c r="I286" s="4" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9338,10 +8292,9 @@
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
+      <c r="F287" s="4" t="inlineStr"/>
       <c r="G287" s="4" t="inlineStr"/>
       <c r="H287" s="4" t="inlineStr"/>
-      <c r="I287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9365,10 +8318,9 @@
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
+      <c r="F288" s="4" t="inlineStr"/>
       <c r="G288" s="4" t="inlineStr"/>
       <c r="H288" s="4" t="inlineStr"/>
-      <c r="I288" s="4" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9392,10 +8344,9 @@
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
+      <c r="F289" s="4" t="inlineStr"/>
       <c r="G289" s="4" t="inlineStr"/>
       <c r="H289" s="4" t="inlineStr"/>
-      <c r="I289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9419,10 +8370,9 @@
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
+      <c r="F290" s="4" t="inlineStr"/>
       <c r="G290" s="4" t="inlineStr"/>
       <c r="H290" s="4" t="inlineStr"/>
-      <c r="I290" s="4" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9446,10 +8396,9 @@
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
+      <c r="F291" s="4" t="inlineStr"/>
       <c r="G291" s="4" t="inlineStr"/>
       <c r="H291" s="4" t="inlineStr"/>
-      <c r="I291" s="4" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9473,10 +8422,9 @@
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
+      <c r="F292" s="4" t="inlineStr"/>
       <c r="G292" s="4" t="inlineStr"/>
       <c r="H292" s="4" t="inlineStr"/>
-      <c r="I292" s="4" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9500,10 +8448,9 @@
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
-      <c r="F293" t="inlineStr"/>
+      <c r="F293" s="4" t="inlineStr"/>
       <c r="G293" s="4" t="inlineStr"/>
       <c r="H293" s="4" t="inlineStr"/>
-      <c r="I293" s="4" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -9527,10 +8474,9 @@
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
-      <c r="F294" t="inlineStr"/>
+      <c r="F294" s="4" t="inlineStr"/>
       <c r="G294" s="4" t="inlineStr"/>
       <c r="H294" s="4" t="inlineStr"/>
-      <c r="I294" s="4" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9554,10 +8500,9 @@
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
-      <c r="F295" t="inlineStr"/>
+      <c r="F295" s="4" t="inlineStr"/>
       <c r="G295" s="4" t="inlineStr"/>
       <c r="H295" s="4" t="inlineStr"/>
-      <c r="I295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9581,14 +8526,9 @@
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
+      <c r="F296" s="4" t="inlineStr"/>
       <c r="G296" s="4" t="inlineStr"/>
       <c r="H296" s="4" t="inlineStr"/>
-      <c r="I296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9612,14 +8552,9 @@
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F297" s="4" t="inlineStr"/>
       <c r="G297" s="4" t="inlineStr"/>
       <c r="H297" s="4" t="inlineStr"/>
-      <c r="I297" s="4" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9643,14 +8578,9 @@
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
+      <c r="F298" s="4" t="inlineStr"/>
       <c r="G298" s="4" t="inlineStr"/>
       <c r="H298" s="4" t="inlineStr"/>
-      <c r="I298" s="4" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr"/>
@@ -9670,14 +8600,13 @@
           <t>93</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" s="4" t="inlineStr"/>
+      <c r="F299" s="4" t="inlineStr"/>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H299" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I299" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -9701,14 +8630,13 @@
           <t>91</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" s="4" t="inlineStr"/>
+      <c r="F300" s="4" t="inlineStr"/>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>需付费</t>
+        </is>
+      </c>
       <c r="H300" s="2" t="inlineStr">
-        <is>
-          <t>需付费</t>
-        </is>
-      </c>
-      <c r="I300" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -9732,14 +8660,13 @@
           <t>90</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" s="4" t="inlineStr"/>
+      <c r="F301" s="4" t="inlineStr"/>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H301" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I301" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -9763,14 +8690,13 @@
           <t>87</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr"/>
-      <c r="G302" s="4" t="inlineStr"/>
+      <c r="F302" s="4" t="inlineStr"/>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H302" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I302" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -9794,18 +8720,17 @@
           <t>81</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" s="4" t="inlineStr">
+      <c r="F303" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H303" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I303" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -9829,14 +8754,13 @@
           <t>79</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" s="4" t="inlineStr"/>
+      <c r="F304" s="4" t="inlineStr"/>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H304" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I304" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -9860,14 +8784,13 @@
           <t>78</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr"/>
-      <c r="G305" s="4" t="inlineStr"/>
+      <c r="F305" s="4" t="inlineStr"/>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H305" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I305" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -9891,14 +8814,13 @@
           <t>75</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" s="4" t="inlineStr"/>
+      <c r="F306" s="4" t="inlineStr"/>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>需付费</t>
+        </is>
+      </c>
       <c r="H306" s="2" t="inlineStr">
-        <is>
-          <t>需付费</t>
-        </is>
-      </c>
-      <c r="I306" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -9922,14 +8844,13 @@
           <t>74</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" s="4" t="inlineStr"/>
+      <c r="F307" s="4" t="inlineStr"/>
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H307" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I307" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -9953,14 +8874,13 @@
           <t>74</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" s="4" t="inlineStr"/>
+      <c r="F308" s="4" t="inlineStr"/>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>需付费</t>
+        </is>
+      </c>
       <c r="H308" s="2" t="inlineStr">
-        <is>
-          <t>需付费</t>
-        </is>
-      </c>
-      <c r="I308" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -9984,14 +8904,13 @@
           <t>73</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" s="4" t="inlineStr"/>
+      <c r="F309" s="4" t="inlineStr"/>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>需付费</t>
+        </is>
+      </c>
       <c r="H309" s="2" t="inlineStr">
-        <is>
-          <t>需付费</t>
-        </is>
-      </c>
-      <c r="I309" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -10015,14 +8934,13 @@
           <t>72</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr"/>
-      <c r="G310" s="4" t="inlineStr"/>
+      <c r="F310" s="4" t="inlineStr"/>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H310" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I310" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10046,14 +8964,13 @@
           <t>71</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr"/>
-      <c r="G311" s="4" t="inlineStr"/>
+      <c r="F311" s="4" t="inlineStr"/>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>需付费</t>
+        </is>
+      </c>
       <c r="H311" s="2" t="inlineStr">
-        <is>
-          <t>需付费</t>
-        </is>
-      </c>
-      <c r="I311" s="2" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -10077,18 +8994,17 @@
           <t>69</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr"/>
-      <c r="G312" s="4" t="inlineStr">
+      <c r="F312" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H312" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I312" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10112,10 +9028,9 @@
           <t>68</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr"/>
+      <c r="F313" s="4" t="inlineStr"/>
       <c r="G313" s="4" t="inlineStr"/>
       <c r="H313" s="4" t="inlineStr"/>
-      <c r="I313" s="4" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr"/>
@@ -10135,14 +9050,13 @@
           <t>67</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr"/>
-      <c r="G314" s="4" t="inlineStr"/>
+      <c r="F314" s="4" t="inlineStr"/>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H314" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I314" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10166,10 +9080,9 @@
           <t>63</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr"/>
+      <c r="F315" s="4" t="inlineStr"/>
       <c r="G315" s="4" t="inlineStr"/>
       <c r="H315" s="4" t="inlineStr"/>
-      <c r="I315" s="4" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr"/>
@@ -10189,10 +9102,9 @@
           <t>62</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr"/>
+      <c r="F316" s="4" t="inlineStr"/>
       <c r="G316" s="4" t="inlineStr"/>
       <c r="H316" s="4" t="inlineStr"/>
-      <c r="I316" s="4" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr"/>
@@ -10212,10 +9124,9 @@
           <t>60</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr"/>
+      <c r="F317" s="4" t="inlineStr"/>
       <c r="G317" s="4" t="inlineStr"/>
       <c r="H317" s="4" t="inlineStr"/>
-      <c r="I317" s="4" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr"/>
@@ -10235,10 +9146,9 @@
           <t>60</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr"/>
+      <c r="F318" s="4" t="inlineStr"/>
       <c r="G318" s="4" t="inlineStr"/>
       <c r="H318" s="4" t="inlineStr"/>
-      <c r="I318" s="4" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr"/>
@@ -10258,10 +9168,9 @@
           <t>60</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr"/>
+      <c r="F319" s="4" t="inlineStr"/>
       <c r="G319" s="4" t="inlineStr"/>
       <c r="H319" s="4" t="inlineStr"/>
-      <c r="I319" s="4" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr"/>
@@ -10281,10 +9190,9 @@
           <t>55</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr"/>
+      <c r="F320" s="4" t="inlineStr"/>
       <c r="G320" s="4" t="inlineStr"/>
       <c r="H320" s="4" t="inlineStr"/>
-      <c r="I320" s="4" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr"/>
@@ -10304,10 +9212,9 @@
           <t>54</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr"/>
+      <c r="F321" s="4" t="inlineStr"/>
       <c r="G321" s="4" t="inlineStr"/>
       <c r="H321" s="4" t="inlineStr"/>
-      <c r="I321" s="4" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr"/>
@@ -10327,10 +9234,9 @@
           <t>54</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr"/>
+      <c r="F322" s="4" t="inlineStr"/>
       <c r="G322" s="4" t="inlineStr"/>
       <c r="H322" s="4" t="inlineStr"/>
-      <c r="I322" s="4" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr"/>
@@ -10350,10 +9256,9 @@
           <t>52</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr"/>
+      <c r="F323" s="4" t="inlineStr"/>
       <c r="G323" s="4" t="inlineStr"/>
       <c r="H323" s="4" t="inlineStr"/>
-      <c r="I323" s="4" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr"/>
@@ -10373,10 +9278,9 @@
           <t>48</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr"/>
+      <c r="F324" s="4" t="inlineStr"/>
       <c r="G324" s="4" t="inlineStr"/>
-      <c r="H324" s="4" t="inlineStr"/>
-      <c r="I324" s="2" t="inlineStr">
+      <c r="H324" s="2" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
@@ -10400,10 +9304,9 @@
           <t>42</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr"/>
+      <c r="F325" s="4" t="inlineStr"/>
       <c r="G325" s="4" t="inlineStr"/>
       <c r="H325" s="4" t="inlineStr"/>
-      <c r="I325" s="4" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr"/>
@@ -10423,10 +9326,9 @@
           <t>41</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr"/>
+      <c r="F326" s="4" t="inlineStr"/>
       <c r="G326" s="4" t="inlineStr"/>
       <c r="H326" s="4" t="inlineStr"/>
-      <c r="I326" s="4" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr"/>
@@ -10446,10 +9348,9 @@
           <t>40</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr"/>
+      <c r="F327" s="4" t="inlineStr"/>
       <c r="G327" s="4" t="inlineStr"/>
       <c r="H327" s="4" t="inlineStr"/>
-      <c r="I327" s="4" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr"/>
@@ -10469,10 +9370,9 @@
           <t>38</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr"/>
+      <c r="F328" s="4" t="inlineStr"/>
       <c r="G328" s="4" t="inlineStr"/>
       <c r="H328" s="4" t="inlineStr"/>
-      <c r="I328" s="4" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr"/>
@@ -10492,14 +9392,13 @@
           <t>35</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr"/>
-      <c r="G329" s="4" t="inlineStr"/>
+      <c r="F329" s="4" t="inlineStr"/>
+      <c r="G329" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H329" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I329" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10523,10 +9422,9 @@
           <t>35</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr"/>
+      <c r="F330" s="4" t="inlineStr"/>
       <c r="G330" s="4" t="inlineStr"/>
       <c r="H330" s="4" t="inlineStr"/>
-      <c r="I330" s="4" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr"/>
@@ -10546,10 +9444,9 @@
           <t>35</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr"/>
+      <c r="F331" s="4" t="inlineStr"/>
       <c r="G331" s="4" t="inlineStr"/>
       <c r="H331" s="4" t="inlineStr"/>
-      <c r="I331" s="4" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr"/>
@@ -10569,10 +9466,9 @@
           <t>32</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr"/>
+      <c r="F332" s="4" t="inlineStr"/>
       <c r="G332" s="4" t="inlineStr"/>
       <c r="H332" s="4" t="inlineStr"/>
-      <c r="I332" s="4" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr"/>
@@ -10592,10 +9488,9 @@
           <t>13</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr"/>
+      <c r="F333" s="4" t="inlineStr"/>
       <c r="G333" s="4" t="inlineStr"/>
       <c r="H333" s="4" t="inlineStr"/>
-      <c r="I333" s="4" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr"/>
@@ -10615,10 +9510,9 @@
           <t>13</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr"/>
+      <c r="F334" s="4" t="inlineStr"/>
       <c r="G334" s="4" t="inlineStr"/>
       <c r="H334" s="4" t="inlineStr"/>
-      <c r="I334" s="4" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr"/>
@@ -10638,10 +9532,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr"/>
+      <c r="F335" s="4" t="inlineStr"/>
       <c r="G335" s="4" t="inlineStr"/>
       <c r="H335" s="4" t="inlineStr"/>
-      <c r="I335" s="4" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr"/>
@@ -10661,10 +9554,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr"/>
+      <c r="F336" s="4" t="inlineStr"/>
       <c r="G336" s="4" t="inlineStr"/>
       <c r="H336" s="4" t="inlineStr"/>
-      <c r="I336" s="4" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr"/>
@@ -10684,10 +9576,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr"/>
+      <c r="F337" s="4" t="inlineStr"/>
       <c r="G337" s="4" t="inlineStr"/>
       <c r="H337" s="4" t="inlineStr"/>
-      <c r="I337" s="4" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr"/>
@@ -10703,18 +9594,17 @@
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
+      <c r="F338" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H338" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I338" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10734,10 +9624,9 @@
       </c>
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
+      <c r="F339" s="4" t="inlineStr"/>
       <c r="G339" s="4" t="inlineStr"/>
       <c r="H339" s="4" t="inlineStr"/>
-      <c r="I339" s="4" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr"/>
@@ -10753,14 +9642,13 @@
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" s="4" t="inlineStr"/>
+      <c r="F340" s="4" t="inlineStr"/>
+      <c r="G340" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H340" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I340" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10780,14 +9668,13 @@
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
-      <c r="G341" s="4" t="inlineStr"/>
+      <c r="F341" s="4" t="inlineStr"/>
+      <c r="G341" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H341" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I341" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10807,14 +9694,13 @@
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
-      <c r="G342" s="4" t="inlineStr"/>
+      <c r="F342" s="4" t="inlineStr"/>
+      <c r="G342" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H342" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I342" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10834,10 +9720,9 @@
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
+      <c r="F343" s="4" t="inlineStr"/>
       <c r="G343" s="4" t="inlineStr"/>
       <c r="H343" s="4" t="inlineStr"/>
-      <c r="I343" s="4" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr"/>
@@ -10853,10 +9738,9 @@
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
+      <c r="F344" s="4" t="inlineStr"/>
       <c r="G344" s="4" t="inlineStr"/>
       <c r="H344" s="4" t="inlineStr"/>
-      <c r="I344" s="4" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr"/>
@@ -10872,10 +9756,9 @@
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
+      <c r="F345" s="4" t="inlineStr"/>
       <c r="G345" s="4" t="inlineStr"/>
       <c r="H345" s="4" t="inlineStr"/>
-      <c r="I345" s="4" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr"/>
@@ -10891,10 +9774,9 @@
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
+      <c r="F346" s="4" t="inlineStr"/>
       <c r="G346" s="4" t="inlineStr"/>
       <c r="H346" s="4" t="inlineStr"/>
-      <c r="I346" s="4" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr"/>
@@ -10910,10 +9792,9 @@
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
+      <c r="F347" s="4" t="inlineStr"/>
       <c r="G347" s="4" t="inlineStr"/>
       <c r="H347" s="4" t="inlineStr"/>
-      <c r="I347" s="4" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr"/>
@@ -10929,10 +9810,9 @@
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
+      <c r="F348" s="4" t="inlineStr"/>
       <c r="G348" s="4" t="inlineStr"/>
-      <c r="H348" s="4" t="inlineStr"/>
-      <c r="I348" s="3" t="inlineStr">
+      <c r="H348" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10952,10 +9832,9 @@
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
+      <c r="F349" s="4" t="inlineStr"/>
       <c r="G349" s="4" t="inlineStr"/>
       <c r="H349" s="4" t="inlineStr"/>
-      <c r="I349" s="4" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr"/>
@@ -10971,10 +9850,9 @@
       </c>
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
+      <c r="F350" s="4" t="inlineStr"/>
       <c r="G350" s="4" t="inlineStr"/>
       <c r="H350" s="4" t="inlineStr"/>
-      <c r="I350" s="4" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr"/>
@@ -10990,10 +9868,9 @@
       </c>
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
+      <c r="F351" s="4" t="inlineStr"/>
       <c r="G351" s="4" t="inlineStr"/>
-      <c r="H351" s="4" t="inlineStr"/>
-      <c r="I351" s="3" t="inlineStr">
+      <c r="H351" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11013,10 +9890,9 @@
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
+      <c r="F352" s="4" t="inlineStr"/>
       <c r="G352" s="4" t="inlineStr"/>
-      <c r="H352" s="4" t="inlineStr"/>
-      <c r="I352" s="3" t="inlineStr">
+      <c r="H352" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11036,10 +9912,9 @@
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
+      <c r="F353" s="4" t="inlineStr"/>
       <c r="G353" s="4" t="inlineStr"/>
       <c r="H353" s="4" t="inlineStr"/>
-      <c r="I353" s="4" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr"/>
@@ -11055,10 +9930,9 @@
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
+      <c r="F354" s="4" t="inlineStr"/>
       <c r="G354" s="4" t="inlineStr"/>
       <c r="H354" s="4" t="inlineStr"/>
-      <c r="I354" s="4" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr"/>
@@ -11074,10 +9948,9 @@
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
+      <c r="F355" s="4" t="inlineStr"/>
       <c r="G355" s="4" t="inlineStr"/>
       <c r="H355" s="4" t="inlineStr"/>
-      <c r="I355" s="4" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr"/>
@@ -11093,10 +9966,9 @@
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
+      <c r="F356" s="4" t="inlineStr"/>
       <c r="G356" s="4" t="inlineStr"/>
       <c r="H356" s="4" t="inlineStr"/>
-      <c r="I356" s="4" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr"/>
@@ -11112,10 +9984,9 @@
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
+      <c r="F357" s="4" t="inlineStr"/>
       <c r="G357" s="4" t="inlineStr"/>
       <c r="H357" s="4" t="inlineStr"/>
-      <c r="I357" s="4" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr"/>
@@ -11131,14 +10002,13 @@
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
-      <c r="G358" s="4" t="inlineStr"/>
+      <c r="F358" s="4" t="inlineStr"/>
+      <c r="G358" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H358" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I358" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11158,14 +10028,13 @@
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
-      <c r="G359" s="4" t="inlineStr"/>
+      <c r="F359" s="4" t="inlineStr"/>
+      <c r="G359" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H359" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I359" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11185,14 +10054,13 @@
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
-      <c r="G360" s="4" t="inlineStr"/>
+      <c r="F360" s="4" t="inlineStr"/>
+      <c r="G360" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H360" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I360" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11212,14 +10080,13 @@
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
-      <c r="G361" s="4" t="inlineStr"/>
+      <c r="F361" s="4" t="inlineStr"/>
+      <c r="G361" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H361" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I361" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11239,14 +10106,13 @@
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
-      <c r="G362" s="4" t="inlineStr"/>
+      <c r="F362" s="4" t="inlineStr"/>
+      <c r="G362" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H362" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I362" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11266,14 +10132,13 @@
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
-      <c r="G363" s="4" t="inlineStr"/>
+      <c r="F363" s="4" t="inlineStr"/>
+      <c r="G363" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H363" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I363" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11293,14 +10158,13 @@
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
-      <c r="G364" s="4" t="inlineStr"/>
+      <c r="F364" s="4" t="inlineStr"/>
+      <c r="G364" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H364" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I364" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11320,14 +10184,13 @@
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
-      <c r="G365" s="4" t="inlineStr"/>
+      <c r="F365" s="4" t="inlineStr"/>
+      <c r="G365" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H365" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I365" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11347,14 +10210,13 @@
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
-      <c r="G366" s="4" t="inlineStr"/>
+      <c r="F366" s="4" t="inlineStr"/>
+      <c r="G366" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H366" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I366" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11374,14 +10236,13 @@
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
-      <c r="G367" s="4" t="inlineStr"/>
+      <c r="F367" s="4" t="inlineStr"/>
+      <c r="G367" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H367" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I367" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11401,14 +10262,13 @@
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
-      <c r="G368" s="4" t="inlineStr"/>
+      <c r="F368" s="4" t="inlineStr"/>
+      <c r="G368" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H368" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I368" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11428,14 +10288,13 @@
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
-      <c r="G369" s="4" t="inlineStr"/>
+      <c r="F369" s="4" t="inlineStr"/>
+      <c r="G369" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H369" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I369" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11455,14 +10314,13 @@
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
-      <c r="G370" s="4" t="inlineStr"/>
+      <c r="F370" s="4" t="inlineStr"/>
+      <c r="G370" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H370" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I370" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11482,10 +10340,9 @@
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
+      <c r="F371" s="4" t="inlineStr"/>
       <c r="G371" s="4" t="inlineStr"/>
       <c r="H371" s="4" t="inlineStr"/>
-      <c r="I371" s="4" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr"/>
@@ -11501,10 +10358,9 @@
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
+      <c r="F372" s="4" t="inlineStr"/>
       <c r="G372" s="4" t="inlineStr"/>
       <c r="H372" s="4" t="inlineStr"/>
-      <c r="I372" s="4" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr"/>
@@ -11520,10 +10376,9 @@
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
+      <c r="F373" s="4" t="inlineStr"/>
       <c r="G373" s="4" t="inlineStr"/>
       <c r="H373" s="4" t="inlineStr"/>
-      <c r="I373" s="4" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr"/>
@@ -11539,10 +10394,9 @@
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
+      <c r="F374" s="4" t="inlineStr"/>
       <c r="G374" s="4" t="inlineStr"/>
       <c r="H374" s="4" t="inlineStr"/>
-      <c r="I374" s="4" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr"/>
@@ -11558,10 +10412,9 @@
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
+      <c r="F375" s="4" t="inlineStr"/>
       <c r="G375" s="4" t="inlineStr"/>
       <c r="H375" s="4" t="inlineStr"/>
-      <c r="I375" s="4" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr"/>
@@ -11577,10 +10430,9 @@
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
+      <c r="F376" s="4" t="inlineStr"/>
       <c r="G376" s="4" t="inlineStr"/>
       <c r="H376" s="4" t="inlineStr"/>
-      <c r="I376" s="4" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr"/>
@@ -11596,10 +10448,9 @@
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
+      <c r="F377" s="4" t="inlineStr"/>
       <c r="G377" s="4" t="inlineStr"/>
       <c r="H377" s="4" t="inlineStr"/>
-      <c r="I377" s="4" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr"/>
@@ -11615,10 +10466,9 @@
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
+      <c r="F378" s="4" t="inlineStr"/>
       <c r="G378" s="4" t="inlineStr"/>
       <c r="H378" s="4" t="inlineStr"/>
-      <c r="I378" s="4" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr"/>
@@ -11634,10 +10484,9 @@
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
+      <c r="F379" s="4" t="inlineStr"/>
       <c r="G379" s="4" t="inlineStr"/>
       <c r="H379" s="4" t="inlineStr"/>
-      <c r="I379" s="4" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr"/>
@@ -11653,10 +10502,9 @@
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
+      <c r="F380" s="4" t="inlineStr"/>
       <c r="G380" s="4" t="inlineStr"/>
       <c r="H380" s="4" t="inlineStr"/>
-      <c r="I380" s="4" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr"/>
@@ -11672,10 +10520,9 @@
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
+      <c r="F381" s="4" t="inlineStr"/>
       <c r="G381" s="4" t="inlineStr"/>
       <c r="H381" s="4" t="inlineStr"/>
-      <c r="I381" s="4" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr"/>
@@ -11691,10 +10538,9 @@
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
+      <c r="F382" s="4" t="inlineStr"/>
       <c r="G382" s="4" t="inlineStr"/>
       <c r="H382" s="4" t="inlineStr"/>
-      <c r="I382" s="4" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr"/>
@@ -11710,10 +10556,9 @@
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
+      <c r="F383" s="4" t="inlineStr"/>
       <c r="G383" s="4" t="inlineStr"/>
       <c r="H383" s="4" t="inlineStr"/>
-      <c r="I383" s="4" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr"/>
@@ -11729,10 +10574,9 @@
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr"/>
+      <c r="F384" s="4" t="inlineStr"/>
       <c r="G384" s="4" t="inlineStr"/>
       <c r="H384" s="4" t="inlineStr"/>
-      <c r="I384" s="4" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr"/>
@@ -11748,10 +10592,9 @@
       </c>
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr"/>
+      <c r="F385" s="4" t="inlineStr"/>
       <c r="G385" s="4" t="inlineStr"/>
       <c r="H385" s="4" t="inlineStr"/>
-      <c r="I385" s="4" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr"/>
@@ -11767,10 +10610,9 @@
       </c>
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr"/>
+      <c r="F386" s="4" t="inlineStr"/>
       <c r="G386" s="4" t="inlineStr"/>
       <c r="H386" s="4" t="inlineStr"/>
-      <c r="I386" s="4" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr"/>
@@ -11786,10 +10628,9 @@
       </c>
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
+      <c r="F387" s="4" t="inlineStr"/>
       <c r="G387" s="4" t="inlineStr"/>
       <c r="H387" s="4" t="inlineStr"/>
-      <c r="I387" s="4" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr"/>
@@ -11805,10 +10646,9 @@
       </c>
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
+      <c r="F388" s="4" t="inlineStr"/>
       <c r="G388" s="4" t="inlineStr"/>
       <c r="H388" s="4" t="inlineStr"/>
-      <c r="I388" s="4" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr"/>
@@ -11824,10 +10664,9 @@
       </c>
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
+      <c r="F389" s="4" t="inlineStr"/>
       <c r="G389" s="4" t="inlineStr"/>
       <c r="H389" s="4" t="inlineStr"/>
-      <c r="I389" s="4" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr"/>
@@ -11843,10 +10682,9 @@
       </c>
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
+      <c r="F390" s="4" t="inlineStr"/>
       <c r="G390" s="4" t="inlineStr"/>
       <c r="H390" s="4" t="inlineStr"/>
-      <c r="I390" s="4" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -11866,10 +10704,9 @@
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr"/>
+      <c r="F391" s="4" t="inlineStr"/>
       <c r="G391" s="4" t="inlineStr"/>
-      <c r="H391" s="4" t="inlineStr"/>
-      <c r="I391" s="4" t="inlineStr">
+      <c r="H391" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -11889,18 +10726,17 @@
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
-      <c r="F392" t="inlineStr"/>
+      <c r="F392" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H392" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I392" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11920,18 +10756,17 @@
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
+      <c r="F393" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H393" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I393" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11951,18 +10786,17 @@
       </c>
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
+      <c r="F394" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H394" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I394" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -11982,18 +10816,17 @@
       </c>
       <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
+      <c r="F395" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H395" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I395" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12013,10 +10846,9 @@
       </c>
       <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
+      <c r="F396" s="4" t="inlineStr"/>
       <c r="G396" s="4" t="inlineStr"/>
-      <c r="H396" s="4" t="inlineStr"/>
-      <c r="I396" s="3" t="inlineStr">
+      <c r="H396" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12036,18 +10868,17 @@
       </c>
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
+      <c r="F397" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H397" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I397" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12067,10 +10898,9 @@
       </c>
       <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
+      <c r="F398" s="4" t="inlineStr"/>
       <c r="G398" s="4" t="inlineStr"/>
-      <c r="H398" s="4" t="inlineStr"/>
-      <c r="I398" s="4" t="inlineStr">
+      <c r="H398" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -12090,10 +10920,9 @@
       </c>
       <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
+      <c r="F399" s="4" t="inlineStr"/>
       <c r="G399" s="4" t="inlineStr"/>
       <c r="H399" s="4" t="inlineStr"/>
-      <c r="I399" s="4" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr"/>
@@ -12109,10 +10938,9 @@
       </c>
       <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
+      <c r="F400" s="4" t="inlineStr"/>
       <c r="G400" s="4" t="inlineStr"/>
       <c r="H400" s="4" t="inlineStr"/>
-      <c r="I400" s="4" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr"/>
@@ -12128,10 +10956,9 @@
       </c>
       <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr"/>
-      <c r="F401" t="inlineStr"/>
+      <c r="F401" s="4" t="inlineStr"/>
       <c r="G401" s="4" t="inlineStr"/>
       <c r="H401" s="4" t="inlineStr"/>
-      <c r="I401" s="4" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr"/>
@@ -12147,10 +10974,9 @@
       </c>
       <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
+      <c r="F402" s="4" t="inlineStr"/>
       <c r="G402" s="4" t="inlineStr"/>
       <c r="H402" s="4" t="inlineStr"/>
-      <c r="I402" s="4" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr"/>
@@ -12166,10 +10992,9 @@
       </c>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
+      <c r="F403" s="4" t="inlineStr"/>
       <c r="G403" s="4" t="inlineStr"/>
       <c r="H403" s="4" t="inlineStr"/>
-      <c r="I403" s="4" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr"/>
@@ -12185,10 +11010,9 @@
       </c>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
+      <c r="F404" s="4" t="inlineStr"/>
       <c r="G404" s="4" t="inlineStr"/>
       <c r="H404" s="4" t="inlineStr"/>
-      <c r="I404" s="4" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr"/>
@@ -12204,10 +11028,9 @@
       </c>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
+      <c r="F405" s="4" t="inlineStr"/>
       <c r="G405" s="4" t="inlineStr"/>
-      <c r="H405" s="4" t="inlineStr"/>
-      <c r="I405" s="4" t="inlineStr">
+      <c r="H405" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -12227,10 +11050,9 @@
       </c>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
+      <c r="F406" s="4" t="inlineStr"/>
       <c r="G406" s="4" t="inlineStr"/>
-      <c r="H406" s="4" t="inlineStr"/>
-      <c r="I406" s="4" t="inlineStr">
+      <c r="H406" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -12250,10 +11072,9 @@
       </c>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr"/>
+      <c r="F407" s="4" t="inlineStr"/>
       <c r="G407" s="4" t="inlineStr"/>
-      <c r="H407" s="4" t="inlineStr"/>
-      <c r="I407" s="3" t="inlineStr">
+      <c r="H407" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12273,10 +11094,9 @@
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
+      <c r="F408" s="4" t="inlineStr"/>
       <c r="G408" s="4" t="inlineStr"/>
-      <c r="H408" s="4" t="inlineStr"/>
-      <c r="I408" s="4" t="inlineStr">
+      <c r="H408" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -12296,10 +11116,9 @@
       </c>
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
+      <c r="F409" s="4" t="inlineStr"/>
       <c r="G409" s="4" t="inlineStr"/>
       <c r="H409" s="4" t="inlineStr"/>
-      <c r="I409" s="4" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr"/>
@@ -12315,10 +11134,9 @@
       </c>
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
+      <c r="F410" s="4" t="inlineStr"/>
       <c r="G410" s="4" t="inlineStr"/>
       <c r="H410" s="4" t="inlineStr"/>
-      <c r="I410" s="4" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr"/>
@@ -12334,10 +11152,9 @@
       </c>
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
+      <c r="F411" s="4" t="inlineStr"/>
       <c r="G411" s="4" t="inlineStr"/>
       <c r="H411" s="4" t="inlineStr"/>
-      <c r="I411" s="4" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr"/>
@@ -12353,10 +11170,9 @@
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="F412" s="4" t="inlineStr"/>
       <c r="G412" s="4" t="inlineStr"/>
       <c r="H412" s="4" t="inlineStr"/>
-      <c r="I412" s="4" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr"/>
@@ -12372,10 +11188,9 @@
       </c>
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="F413" s="4" t="inlineStr"/>
       <c r="G413" s="4" t="inlineStr"/>
-      <c r="H413" s="4" t="inlineStr"/>
-      <c r="I413" s="3" t="inlineStr">
+      <c r="H413" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12399,14 +11214,13 @@
       </c>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
-      <c r="G414" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
+      <c r="F414" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="G414" s="4" t="inlineStr"/>
       <c r="H414" s="4" t="inlineStr"/>
-      <c r="I414" s="4" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr"/>
@@ -12422,10 +11236,9 @@
       </c>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="F415" s="4" t="inlineStr"/>
       <c r="G415" s="4" t="inlineStr"/>
       <c r="H415" s="4" t="inlineStr"/>
-      <c r="I415" s="4" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr"/>
@@ -12441,10 +11254,9 @@
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
+      <c r="F416" s="4" t="inlineStr"/>
       <c r="G416" s="4" t="inlineStr"/>
-      <c r="H416" s="4" t="inlineStr"/>
-      <c r="I416" s="3" t="inlineStr">
+      <c r="H416" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12464,18 +11276,17 @@
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H417" s="4" t="inlineStr">
+      <c r="F417" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="G417" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I417" s="3" t="inlineStr">
+      <c r="H417" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12495,18 +11306,17 @@
       </c>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
+      <c r="F418" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H418" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I418" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12526,10 +11336,9 @@
       </c>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
+      <c r="F419" s="4" t="inlineStr"/>
       <c r="G419" s="4" t="inlineStr"/>
       <c r="H419" s="4" t="inlineStr"/>
-      <c r="I419" s="4" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr"/>
@@ -12545,10 +11354,9 @@
       </c>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
+      <c r="F420" s="4" t="inlineStr"/>
       <c r="G420" s="4" t="inlineStr"/>
-      <c r="H420" s="4" t="inlineStr"/>
-      <c r="I420" s="4" t="inlineStr">
+      <c r="H420" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -12568,18 +11376,17 @@
       </c>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H421" s="4" t="inlineStr">
+      <c r="F421" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="G421" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I421" s="3" t="inlineStr">
+      <c r="H421" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12599,10 +11406,9 @@
       </c>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
+      <c r="F422" s="4" t="inlineStr"/>
       <c r="G422" s="4" t="inlineStr"/>
-      <c r="H422" s="4" t="inlineStr"/>
-      <c r="I422" s="4" t="inlineStr">
+      <c r="H422" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -12622,10 +11428,9 @@
       </c>
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr"/>
+      <c r="F423" s="4" t="inlineStr"/>
       <c r="G423" s="4" t="inlineStr"/>
-      <c r="H423" s="4" t="inlineStr"/>
-      <c r="I423" s="4" t="inlineStr">
+      <c r="H423" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -12645,14 +11450,13 @@
       </c>
       <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" s="4" t="inlineStr"/>
-      <c r="H424" s="4" t="inlineStr">
+      <c r="F424" s="4" t="inlineStr"/>
+      <c r="G424" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I424" s="3" t="inlineStr">
+      <c r="H424" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12672,10 +11476,9 @@
       </c>
       <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr"/>
+      <c r="F425" s="4" t="inlineStr"/>
       <c r="G425" s="4" t="inlineStr"/>
-      <c r="H425" s="4" t="inlineStr"/>
-      <c r="I425" s="3" t="inlineStr">
+      <c r="H425" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12695,10 +11498,9 @@
       </c>
       <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
+      <c r="F426" s="4" t="inlineStr"/>
       <c r="G426" s="4" t="inlineStr"/>
-      <c r="H426" s="4" t="inlineStr"/>
-      <c r="I426" s="4" t="inlineStr">
+      <c r="H426" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -12718,10 +11520,9 @@
       </c>
       <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
+      <c r="F427" s="4" t="inlineStr"/>
       <c r="G427" s="4" t="inlineStr"/>
-      <c r="H427" s="4" t="inlineStr"/>
-      <c r="I427" s="3" t="inlineStr">
+      <c r="H427" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12741,10 +11542,9 @@
       </c>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
+      <c r="F428" s="4" t="inlineStr"/>
       <c r="G428" s="4" t="inlineStr"/>
       <c r="H428" s="4" t="inlineStr"/>
-      <c r="I428" s="4" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr"/>
@@ -12760,10 +11560,9 @@
       </c>
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr"/>
+      <c r="F429" s="4" t="inlineStr"/>
       <c r="G429" s="4" t="inlineStr"/>
-      <c r="H429" s="4" t="inlineStr"/>
-      <c r="I429" s="4" t="inlineStr">
+      <c r="H429" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -12783,10 +11582,9 @@
       </c>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
+      <c r="F430" s="4" t="inlineStr"/>
       <c r="G430" s="4" t="inlineStr"/>
-      <c r="H430" s="4" t="inlineStr"/>
-      <c r="I430" s="3" t="inlineStr">
+      <c r="H430" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12806,14 +11604,13 @@
       </c>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
+      <c r="F431" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="G431" s="4" t="inlineStr"/>
       <c r="H431" s="4" t="inlineStr"/>
-      <c r="I431" s="4" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr"/>
@@ -12829,10 +11626,9 @@
       </c>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr"/>
-      <c r="F432" t="inlineStr"/>
+      <c r="F432" s="4" t="inlineStr"/>
       <c r="G432" s="4" t="inlineStr"/>
       <c r="H432" s="4" t="inlineStr"/>
-      <c r="I432" s="4" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr"/>
@@ -12848,10 +11644,9 @@
       </c>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
+      <c r="F433" s="4" t="inlineStr"/>
       <c r="G433" s="4" t="inlineStr"/>
       <c r="H433" s="4" t="inlineStr"/>
-      <c r="I433" s="4" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr"/>
@@ -12867,10 +11662,9 @@
       </c>
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
+      <c r="F434" s="4" t="inlineStr"/>
       <c r="G434" s="4" t="inlineStr"/>
       <c r="H434" s="4" t="inlineStr"/>
-      <c r="I434" s="4" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr"/>
@@ -12886,18 +11680,17 @@
       </c>
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
+      <c r="F435" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
       <c r="H435" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I435" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12921,10 +11714,9 @@
       </c>
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
+      <c r="F436" s="4" t="inlineStr"/>
       <c r="G436" s="4" t="inlineStr"/>
       <c r="H436" s="4" t="inlineStr"/>
-      <c r="I436" s="4" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr"/>
@@ -12940,14 +11732,13 @@
       </c>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" s="4" t="inlineStr"/>
+      <c r="F437" s="4" t="inlineStr"/>
+      <c r="G437" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H437" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I437" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -12967,10 +11758,9 @@
       </c>
       <c r="D438" t="inlineStr"/>
       <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
+      <c r="F438" s="4" t="inlineStr"/>
       <c r="G438" s="4" t="inlineStr"/>
       <c r="H438" s="4" t="inlineStr"/>
-      <c r="I438" s="4" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr"/>
@@ -12986,10 +11776,9 @@
       </c>
       <c r="D439" t="inlineStr"/>
       <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
+      <c r="F439" s="4" t="inlineStr"/>
       <c r="G439" s="4" t="inlineStr"/>
       <c r="H439" s="4" t="inlineStr"/>
-      <c r="I439" s="4" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr"/>
@@ -13005,10 +11794,9 @@
       </c>
       <c r="D440" t="inlineStr"/>
       <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
+      <c r="F440" s="4" t="inlineStr"/>
       <c r="G440" s="4" t="inlineStr"/>
       <c r="H440" s="4" t="inlineStr"/>
-      <c r="I440" s="4" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr"/>
@@ -13024,10 +11812,9 @@
       </c>
       <c r="D441" t="inlineStr"/>
       <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
+      <c r="F441" s="4" t="inlineStr"/>
       <c r="G441" s="4" t="inlineStr"/>
       <c r="H441" s="4" t="inlineStr"/>
-      <c r="I441" s="4" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr"/>
@@ -13043,10 +11830,9 @@
       </c>
       <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
+      <c r="F442" s="4" t="inlineStr"/>
       <c r="G442" s="4" t="inlineStr"/>
       <c r="H442" s="4" t="inlineStr"/>
-      <c r="I442" s="4" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr"/>
@@ -13062,10 +11848,9 @@
       </c>
       <c r="D443" t="inlineStr"/>
       <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
+      <c r="F443" s="4" t="inlineStr"/>
       <c r="G443" s="4" t="inlineStr"/>
       <c r="H443" s="4" t="inlineStr"/>
-      <c r="I443" s="4" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr"/>
@@ -13081,10 +11866,9 @@
       </c>
       <c r="D444" t="inlineStr"/>
       <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
+      <c r="F444" s="4" t="inlineStr"/>
       <c r="G444" s="4" t="inlineStr"/>
       <c r="H444" s="4" t="inlineStr"/>
-      <c r="I444" s="4" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr"/>
@@ -13100,10 +11884,9 @@
       </c>
       <c r="D445" t="inlineStr"/>
       <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
+      <c r="F445" s="4" t="inlineStr"/>
       <c r="G445" s="4" t="inlineStr"/>
       <c r="H445" s="4" t="inlineStr"/>
-      <c r="I445" s="4" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr"/>
@@ -13119,10 +11902,9 @@
       </c>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr"/>
-      <c r="F446" t="inlineStr"/>
+      <c r="F446" s="4" t="inlineStr"/>
       <c r="G446" s="4" t="inlineStr"/>
       <c r="H446" s="4" t="inlineStr"/>
-      <c r="I446" s="4" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr"/>
@@ -13138,10 +11920,9 @@
       </c>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
+      <c r="F447" s="4" t="inlineStr"/>
       <c r="G447" s="4" t="inlineStr"/>
       <c r="H447" s="4" t="inlineStr"/>
-      <c r="I447" s="4" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr"/>
@@ -13157,10 +11938,9 @@
       </c>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
+      <c r="F448" s="4" t="inlineStr"/>
       <c r="G448" s="4" t="inlineStr"/>
       <c r="H448" s="4" t="inlineStr"/>
-      <c r="I448" s="4" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr"/>
@@ -13176,10 +11956,9 @@
       </c>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr"/>
+      <c r="F449" s="4" t="inlineStr"/>
       <c r="G449" s="4" t="inlineStr"/>
       <c r="H449" s="4" t="inlineStr"/>
-      <c r="I449" s="4" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr"/>
@@ -13195,10 +11974,9 @@
       </c>
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
+      <c r="F450" s="4" t="inlineStr"/>
       <c r="G450" s="4" t="inlineStr"/>
       <c r="H450" s="4" t="inlineStr"/>
-      <c r="I450" s="4" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr"/>
@@ -13214,10 +11992,9 @@
       </c>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr"/>
+      <c r="F451" s="4" t="inlineStr"/>
       <c r="G451" s="4" t="inlineStr"/>
       <c r="H451" s="4" t="inlineStr"/>
-      <c r="I451" s="4" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr"/>
@@ -13233,10 +12010,9 @@
       </c>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
+      <c r="F452" s="4" t="inlineStr"/>
       <c r="G452" s="4" t="inlineStr"/>
       <c r="H452" s="4" t="inlineStr"/>
-      <c r="I452" s="4" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr"/>
@@ -13252,10 +12028,9 @@
       </c>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr"/>
-      <c r="F453" t="inlineStr"/>
+      <c r="F453" s="4" t="inlineStr"/>
       <c r="G453" s="4" t="inlineStr"/>
       <c r="H453" s="4" t="inlineStr"/>
-      <c r="I453" s="4" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr"/>
@@ -13271,10 +12046,9 @@
       </c>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
+      <c r="F454" s="4" t="inlineStr"/>
       <c r="G454" s="4" t="inlineStr"/>
       <c r="H454" s="4" t="inlineStr"/>
-      <c r="I454" s="4" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr"/>
@@ -13290,10 +12064,9 @@
       </c>
       <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr"/>
-      <c r="F455" t="inlineStr"/>
+      <c r="F455" s="4" t="inlineStr"/>
       <c r="G455" s="4" t="inlineStr"/>
       <c r="H455" s="4" t="inlineStr"/>
-      <c r="I455" s="4" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr"/>
@@ -13309,10 +12082,9 @@
       </c>
       <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
+      <c r="F456" s="4" t="inlineStr"/>
       <c r="G456" s="4" t="inlineStr"/>
       <c r="H456" s="4" t="inlineStr"/>
-      <c r="I456" s="4" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr"/>
@@ -13328,10 +12100,9 @@
       </c>
       <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr"/>
-      <c r="F457" t="inlineStr"/>
+      <c r="F457" s="4" t="inlineStr"/>
       <c r="G457" s="4" t="inlineStr"/>
       <c r="H457" s="4" t="inlineStr"/>
-      <c r="I457" s="4" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr"/>
@@ -13347,10 +12118,9 @@
       </c>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
-      <c r="F458" t="inlineStr"/>
+      <c r="F458" s="4" t="inlineStr"/>
       <c r="G458" s="4" t="inlineStr"/>
       <c r="H458" s="4" t="inlineStr"/>
-      <c r="I458" s="4" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr"/>
@@ -13366,10 +12136,9 @@
       </c>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
-      <c r="F459" t="inlineStr"/>
+      <c r="F459" s="4" t="inlineStr"/>
       <c r="G459" s="4" t="inlineStr"/>
       <c r="H459" s="4" t="inlineStr"/>
-      <c r="I459" s="4" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr"/>
@@ -13385,10 +12154,9 @@
       </c>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
-      <c r="F460" t="inlineStr"/>
+      <c r="F460" s="4" t="inlineStr"/>
       <c r="G460" s="4" t="inlineStr"/>
       <c r="H460" s="4" t="inlineStr"/>
-      <c r="I460" s="4" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr"/>
@@ -13404,10 +12172,9 @@
       </c>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
-      <c r="F461" t="inlineStr"/>
+      <c r="F461" s="4" t="inlineStr"/>
       <c r="G461" s="4" t="inlineStr"/>
       <c r="H461" s="4" t="inlineStr"/>
-      <c r="I461" s="4" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr"/>
@@ -13423,10 +12190,9 @@
       </c>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
-      <c r="F462" t="inlineStr"/>
+      <c r="F462" s="4" t="inlineStr"/>
       <c r="G462" s="4" t="inlineStr"/>
       <c r="H462" s="4" t="inlineStr"/>
-      <c r="I462" s="4" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr"/>
@@ -13442,10 +12208,9 @@
       </c>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
-      <c r="F463" t="inlineStr"/>
+      <c r="F463" s="4" t="inlineStr"/>
       <c r="G463" s="4" t="inlineStr"/>
       <c r="H463" s="4" t="inlineStr"/>
-      <c r="I463" s="4" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr"/>
@@ -13461,10 +12226,9 @@
       </c>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
-      <c r="F464" t="inlineStr"/>
+      <c r="F464" s="4" t="inlineStr"/>
       <c r="G464" s="4" t="inlineStr"/>
       <c r="H464" s="4" t="inlineStr"/>
-      <c r="I464" s="4" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr"/>
@@ -13480,10 +12244,9 @@
       </c>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
-      <c r="F465" t="inlineStr"/>
+      <c r="F465" s="4" t="inlineStr"/>
       <c r="G465" s="4" t="inlineStr"/>
       <c r="H465" s="4" t="inlineStr"/>
-      <c r="I465" s="4" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr"/>
@@ -13499,10 +12262,9 @@
       </c>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
-      <c r="F466" t="inlineStr"/>
+      <c r="F466" s="4" t="inlineStr"/>
       <c r="G466" s="4" t="inlineStr"/>
       <c r="H466" s="4" t="inlineStr"/>
-      <c r="I466" s="4" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr"/>
@@ -13518,10 +12280,9 @@
       </c>
       <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr"/>
-      <c r="F467" t="inlineStr"/>
+      <c r="F467" s="4" t="inlineStr"/>
       <c r="G467" s="4" t="inlineStr"/>
       <c r="H467" s="4" t="inlineStr"/>
-      <c r="I467" s="4" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr"/>
@@ -13537,10 +12298,9 @@
       </c>
       <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr"/>
-      <c r="F468" t="inlineStr"/>
+      <c r="F468" s="4" t="inlineStr"/>
       <c r="G468" s="4" t="inlineStr"/>
       <c r="H468" s="4" t="inlineStr"/>
-      <c r="I468" s="4" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr"/>
@@ -13556,10 +12316,9 @@
       </c>
       <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr"/>
-      <c r="F469" t="inlineStr"/>
+      <c r="F469" s="4" t="inlineStr"/>
       <c r="G469" s="4" t="inlineStr"/>
       <c r="H469" s="4" t="inlineStr"/>
-      <c r="I469" s="4" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr"/>
@@ -13575,10 +12334,9 @@
       </c>
       <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr"/>
+      <c r="F470" s="4" t="inlineStr"/>
       <c r="G470" s="4" t="inlineStr"/>
       <c r="H470" s="4" t="inlineStr"/>
-      <c r="I470" s="4" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr"/>
@@ -13594,10 +12352,9 @@
       </c>
       <c r="D471" t="inlineStr"/>
       <c r="E471" t="inlineStr"/>
-      <c r="F471" t="inlineStr"/>
+      <c r="F471" s="4" t="inlineStr"/>
       <c r="G471" s="4" t="inlineStr"/>
       <c r="H471" s="4" t="inlineStr"/>
-      <c r="I471" s="4" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr"/>
@@ -13613,10 +12370,9 @@
       </c>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr"/>
-      <c r="F472" t="inlineStr"/>
+      <c r="F472" s="4" t="inlineStr"/>
       <c r="G472" s="4" t="inlineStr"/>
       <c r="H472" s="4" t="inlineStr"/>
-      <c r="I472" s="4" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr"/>
@@ -13632,10 +12388,9 @@
       </c>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr"/>
-      <c r="F473" t="inlineStr"/>
+      <c r="F473" s="4" t="inlineStr"/>
       <c r="G473" s="4" t="inlineStr"/>
       <c r="H473" s="4" t="inlineStr"/>
-      <c r="I473" s="4" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr"/>
@@ -13651,10 +12406,9 @@
       </c>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr"/>
-      <c r="F474" t="inlineStr"/>
+      <c r="F474" s="4" t="inlineStr"/>
       <c r="G474" s="4" t="inlineStr"/>
       <c r="H474" s="4" t="inlineStr"/>
-      <c r="I474" s="4" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr"/>
@@ -13670,10 +12424,9 @@
       </c>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr"/>
-      <c r="F475" t="inlineStr"/>
+      <c r="F475" s="4" t="inlineStr"/>
       <c r="G475" s="4" t="inlineStr"/>
       <c r="H475" s="4" t="inlineStr"/>
-      <c r="I475" s="4" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr"/>
@@ -13689,10 +12442,9 @@
       </c>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr"/>
-      <c r="F476" t="inlineStr"/>
+      <c r="F476" s="4" t="inlineStr"/>
       <c r="G476" s="4" t="inlineStr"/>
       <c r="H476" s="4" t="inlineStr"/>
-      <c r="I476" s="4" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr"/>
@@ -13708,10 +12460,9 @@
       </c>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr"/>
-      <c r="F477" t="inlineStr"/>
+      <c r="F477" s="4" t="inlineStr"/>
       <c r="G477" s="4" t="inlineStr"/>
       <c r="H477" s="4" t="inlineStr"/>
-      <c r="I477" s="4" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr"/>
@@ -13727,10 +12478,9 @@
       </c>
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr"/>
-      <c r="F478" t="inlineStr"/>
+      <c r="F478" s="4" t="inlineStr"/>
       <c r="G478" s="4" t="inlineStr"/>
       <c r="H478" s="4" t="inlineStr"/>
-      <c r="I478" s="4" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr"/>
@@ -13746,10 +12496,9 @@
       </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
+      <c r="F479" s="4" t="inlineStr"/>
       <c r="G479" s="4" t="inlineStr"/>
       <c r="H479" s="4" t="inlineStr"/>
-      <c r="I479" s="4" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr"/>
@@ -13765,10 +12514,9 @@
       </c>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
+      <c r="F480" s="4" t="inlineStr"/>
       <c r="G480" s="4" t="inlineStr"/>
       <c r="H480" s="4" t="inlineStr"/>
-      <c r="I480" s="4" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr"/>
@@ -13784,10 +12532,9 @@
       </c>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
-      <c r="F481" t="inlineStr"/>
+      <c r="F481" s="4" t="inlineStr"/>
       <c r="G481" s="4" t="inlineStr"/>
-      <c r="H481" s="4" t="inlineStr"/>
-      <c r="I481" s="3" t="inlineStr">
+      <c r="H481" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -13807,10 +12554,9 @@
       </c>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
+      <c r="F482" s="4" t="inlineStr"/>
       <c r="G482" s="4" t="inlineStr"/>
       <c r="H482" s="4" t="inlineStr"/>
-      <c r="I482" s="4" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr"/>
@@ -13826,10 +12572,9 @@
       </c>
       <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr"/>
-      <c r="F483" t="inlineStr"/>
+      <c r="F483" s="4" t="inlineStr"/>
       <c r="G483" s="4" t="inlineStr"/>
       <c r="H483" s="4" t="inlineStr"/>
-      <c r="I483" s="4" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr"/>
@@ -13845,10 +12590,9 @@
       </c>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
+      <c r="F484" s="4" t="inlineStr"/>
       <c r="G484" s="4" t="inlineStr"/>
       <c r="H484" s="4" t="inlineStr"/>
-      <c r="I484" s="4" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr"/>
@@ -13864,10 +12608,9 @@
       </c>
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
+      <c r="F485" s="4" t="inlineStr"/>
       <c r="G485" s="4" t="inlineStr"/>
       <c r="H485" s="4" t="inlineStr"/>
-      <c r="I485" s="4" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr"/>
@@ -13883,10 +12626,9 @@
       </c>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
+      <c r="F486" s="4" t="inlineStr"/>
       <c r="G486" s="4" t="inlineStr"/>
       <c r="H486" s="4" t="inlineStr"/>
-      <c r="I486" s="4" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr"/>
@@ -13902,10 +12644,9 @@
       </c>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
-      <c r="F487" t="inlineStr"/>
+      <c r="F487" s="4" t="inlineStr"/>
       <c r="G487" s="4" t="inlineStr"/>
       <c r="H487" s="4" t="inlineStr"/>
-      <c r="I487" s="4" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr"/>
@@ -13921,10 +12662,9 @@
       </c>
       <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr"/>
-      <c r="F488" t="inlineStr"/>
+      <c r="F488" s="4" t="inlineStr"/>
       <c r="G488" s="4" t="inlineStr"/>
       <c r="H488" s="4" t="inlineStr"/>
-      <c r="I488" s="4" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr"/>
@@ -13940,10 +12680,9 @@
       </c>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
-      <c r="F489" t="inlineStr"/>
+      <c r="F489" s="4" t="inlineStr"/>
       <c r="G489" s="4" t="inlineStr"/>
       <c r="H489" s="4" t="inlineStr"/>
-      <c r="I489" s="4" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr"/>
@@ -13959,10 +12698,9 @@
       </c>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
-      <c r="F490" t="inlineStr"/>
+      <c r="F490" s="4" t="inlineStr"/>
       <c r="G490" s="4" t="inlineStr"/>
       <c r="H490" s="4" t="inlineStr"/>
-      <c r="I490" s="4" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr"/>
@@ -13978,10 +12716,9 @@
       </c>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
-      <c r="F491" t="inlineStr"/>
+      <c r="F491" s="4" t="inlineStr"/>
       <c r="G491" s="4" t="inlineStr"/>
       <c r="H491" s="4" t="inlineStr"/>
-      <c r="I491" s="4" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr"/>
@@ -13997,10 +12734,9 @@
       </c>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
+      <c r="F492" s="4" t="inlineStr"/>
       <c r="G492" s="4" t="inlineStr"/>
       <c r="H492" s="4" t="inlineStr"/>
-      <c r="I492" s="4" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr"/>
@@ -14016,10 +12752,9 @@
       </c>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
-      <c r="F493" t="inlineStr"/>
+      <c r="F493" s="4" t="inlineStr"/>
       <c r="G493" s="4" t="inlineStr"/>
       <c r="H493" s="4" t="inlineStr"/>
-      <c r="I493" s="4" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr"/>
@@ -14035,14 +12770,13 @@
       </c>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
-      <c r="F494" t="inlineStr"/>
-      <c r="G494" s="4" t="inlineStr"/>
+      <c r="F494" s="4" t="inlineStr"/>
+      <c r="G494" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="H494" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I494" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -14062,10 +12796,9 @@
       </c>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
-      <c r="F495" t="inlineStr"/>
+      <c r="F495" s="4" t="inlineStr"/>
       <c r="G495" s="4" t="inlineStr"/>
       <c r="H495" s="4" t="inlineStr"/>
-      <c r="I495" s="4" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr"/>
@@ -14081,10 +12814,9 @@
       </c>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr"/>
+      <c r="F496" s="4" t="inlineStr"/>
       <c r="G496" s="4" t="inlineStr"/>
       <c r="H496" s="4" t="inlineStr"/>
-      <c r="I496" s="4" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr"/>
@@ -14100,10 +12832,9 @@
       </c>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
-      <c r="F497" t="inlineStr"/>
+      <c r="F497" s="4" t="inlineStr"/>
       <c r="G497" s="4" t="inlineStr"/>
       <c r="H497" s="4" t="inlineStr"/>
-      <c r="I497" s="4" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr"/>
@@ -14119,10 +12850,9 @@
       </c>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
-      <c r="F498" t="inlineStr"/>
+      <c r="F498" s="4" t="inlineStr"/>
       <c r="G498" s="4" t="inlineStr"/>
       <c r="H498" s="4" t="inlineStr"/>
-      <c r="I498" s="4" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -14142,18 +12872,17 @@
       </c>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr"/>
-      <c r="F499" t="inlineStr"/>
+      <c r="F499" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
       </c>
-      <c r="H499" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="I499" s="4" t="inlineStr"/>
+      <c r="H499" s="4" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr"/>
@@ -14169,10 +12898,9 @@
       </c>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr"/>
-      <c r="F500" t="inlineStr"/>
+      <c r="F500" s="4" t="inlineStr"/>
       <c r="G500" s="4" t="inlineStr"/>
       <c r="H500" s="4" t="inlineStr"/>
-      <c r="I500" s="4" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr"/>
@@ -14188,10 +12916,9 @@
       </c>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr"/>
-      <c r="F501" t="inlineStr"/>
+      <c r="F501" s="4" t="inlineStr"/>
       <c r="G501" s="4" t="inlineStr"/>
       <c r="H501" s="4" t="inlineStr"/>
-      <c r="I501" s="4" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr"/>
@@ -14207,10 +12934,9 @@
       </c>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
-      <c r="F502" t="inlineStr"/>
+      <c r="F502" s="4" t="inlineStr"/>
       <c r="G502" s="4" t="inlineStr"/>
       <c r="H502" s="4" t="inlineStr"/>
-      <c r="I502" s="4" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr"/>
@@ -14226,10 +12952,9 @@
       </c>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr"/>
-      <c r="F503" t="inlineStr"/>
+      <c r="F503" s="4" t="inlineStr"/>
       <c r="G503" s="4" t="inlineStr"/>
       <c r="H503" s="4" t="inlineStr"/>
-      <c r="I503" s="4" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr"/>
@@ -14245,10 +12970,9 @@
       </c>
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
+      <c r="F504" s="4" t="inlineStr"/>
       <c r="G504" s="4" t="inlineStr"/>
       <c r="H504" s="4" t="inlineStr"/>
-      <c r="I504" s="4" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr"/>
@@ -14264,10 +12988,9 @@
       </c>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr"/>
-      <c r="F505" t="inlineStr"/>
+      <c r="F505" s="4" t="inlineStr"/>
       <c r="G505" s="4" t="inlineStr"/>
       <c r="H505" s="4" t="inlineStr"/>
-      <c r="I505" s="4" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr"/>
@@ -14283,10 +13006,9 @@
       </c>
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr"/>
-      <c r="F506" t="inlineStr"/>
+      <c r="F506" s="4" t="inlineStr"/>
       <c r="G506" s="4" t="inlineStr"/>
       <c r="H506" s="4" t="inlineStr"/>
-      <c r="I506" s="4" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr"/>
@@ -14302,18 +13024,17 @@
       </c>
       <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr"/>
-      <c r="F507" t="inlineStr"/>
-      <c r="G507" s="3" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="H507" s="4" t="inlineStr">
+      <c r="F507" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="G507" s="4" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="I507" s="3" t="inlineStr">
+      <c r="H507" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -14333,10 +13054,9 @@
       </c>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr"/>
-      <c r="F508" t="inlineStr"/>
+      <c r="F508" s="4" t="inlineStr"/>
       <c r="G508" s="4" t="inlineStr"/>
       <c r="H508" s="4" t="inlineStr"/>
-      <c r="I508" s="4" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr"/>
@@ -14352,10 +13072,9 @@
       </c>
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr"/>
-      <c r="F509" t="inlineStr"/>
+      <c r="F509" s="4" t="inlineStr"/>
       <c r="G509" s="4" t="inlineStr"/>
       <c r="H509" s="4" t="inlineStr"/>
-      <c r="I509" s="4" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr"/>
@@ -14371,10 +13090,9 @@
       </c>
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr"/>
-      <c r="F510" t="inlineStr"/>
+      <c r="F510" s="4" t="inlineStr"/>
       <c r="G510" s="4" t="inlineStr"/>
       <c r="H510" s="4" t="inlineStr"/>
-      <c r="I510" s="4" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr"/>
@@ -14390,10 +13108,9 @@
       </c>
       <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr"/>
-      <c r="F511" t="inlineStr"/>
+      <c r="F511" s="4" t="inlineStr"/>
       <c r="G511" s="4" t="inlineStr"/>
       <c r="H511" s="4" t="inlineStr"/>
-      <c r="I511" s="4" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr"/>
@@ -14409,10 +13126,9 @@
       </c>
       <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr"/>
-      <c r="F512" t="inlineStr"/>
+      <c r="F512" s="4" t="inlineStr"/>
       <c r="G512" s="4" t="inlineStr"/>
       <c r="H512" s="4" t="inlineStr"/>
-      <c r="I512" s="4" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr"/>
@@ -14428,10 +13144,9 @@
       </c>
       <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr"/>
+      <c r="F513" s="4" t="inlineStr"/>
       <c r="G513" s="4" t="inlineStr"/>
       <c r="H513" s="4" t="inlineStr"/>
-      <c r="I513" s="4" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr"/>
@@ -14447,10 +13162,9 @@
       </c>
       <c r="D514" t="inlineStr"/>
       <c r="E514" t="inlineStr"/>
-      <c r="F514" t="inlineStr"/>
+      <c r="F514" s="4" t="inlineStr"/>
       <c r="G514" s="4" t="inlineStr"/>
       <c r="H514" s="4" t="inlineStr"/>
-      <c r="I514" s="4" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr"/>
@@ -14466,10 +13180,9 @@
       </c>
       <c r="D515" t="inlineStr"/>
       <c r="E515" t="inlineStr"/>
-      <c r="F515" t="inlineStr"/>
+      <c r="F515" s="4" t="inlineStr"/>
       <c r="G515" s="4" t="inlineStr"/>
       <c r="H515" s="4" t="inlineStr"/>
-      <c r="I515" s="4" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr"/>
@@ -14485,10 +13198,9 @@
       </c>
       <c r="D516" t="inlineStr"/>
       <c r="E516" t="inlineStr"/>
-      <c r="F516" t="inlineStr"/>
+      <c r="F516" s="4" t="inlineStr"/>
       <c r="G516" s="4" t="inlineStr"/>
       <c r="H516" s="4" t="inlineStr"/>
-      <c r="I516" s="4" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr"/>
@@ -14504,10 +13216,9 @@
       </c>
       <c r="D517" t="inlineStr"/>
       <c r="E517" t="inlineStr"/>
-      <c r="F517" t="inlineStr"/>
+      <c r="F517" s="4" t="inlineStr"/>
       <c r="G517" s="4" t="inlineStr"/>
       <c r="H517" s="4" t="inlineStr"/>
-      <c r="I517" s="4" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr"/>
@@ -14523,10 +13234,9 @@
       </c>
       <c r="D518" t="inlineStr"/>
       <c r="E518" t="inlineStr"/>
-      <c r="F518" t="inlineStr"/>
+      <c r="F518" s="4" t="inlineStr"/>
       <c r="G518" s="4" t="inlineStr"/>
       <c r="H518" s="4" t="inlineStr"/>
-      <c r="I518" s="4" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr"/>
@@ -14542,10 +13252,9 @@
       </c>
       <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr"/>
-      <c r="F519" t="inlineStr"/>
+      <c r="F519" s="4" t="inlineStr"/>
       <c r="G519" s="4" t="inlineStr"/>
       <c r="H519" s="4" t="inlineStr"/>
-      <c r="I519" s="4" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr"/>
@@ -14561,10 +13270,9 @@
       </c>
       <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr"/>
-      <c r="F520" t="inlineStr"/>
+      <c r="F520" s="4" t="inlineStr"/>
       <c r="G520" s="4" t="inlineStr"/>
       <c r="H520" s="4" t="inlineStr"/>
-      <c r="I520" s="4" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr"/>
@@ -14580,10 +13288,9 @@
       </c>
       <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr"/>
-      <c r="F521" t="inlineStr"/>
+      <c r="F521" s="4" t="inlineStr"/>
       <c r="G521" s="4" t="inlineStr"/>
-      <c r="H521" s="4" t="inlineStr"/>
-      <c r="I521" s="3" t="inlineStr">
+      <c r="H521" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -14603,10 +13310,9 @@
       </c>
       <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr"/>
-      <c r="F522" t="inlineStr"/>
+      <c r="F522" s="4" t="inlineStr"/>
       <c r="G522" s="4" t="inlineStr"/>
       <c r="H522" s="4" t="inlineStr"/>
-      <c r="I522" s="4" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr"/>
@@ -14622,10 +13328,9 @@
       </c>
       <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr"/>
-      <c r="F523" t="inlineStr"/>
+      <c r="F523" s="4" t="inlineStr"/>
       <c r="G523" s="4" t="inlineStr"/>
       <c r="H523" s="4" t="inlineStr"/>
-      <c r="I523" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backlinks.xlsx
+++ b/backlinks.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提交总表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,35 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -68,20 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,40 +415,34 @@
   </sheetPr>
   <dimension ref="A1:F523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>提交地址</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>extractkeywords.com</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>heicpdf.to</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>tryschedule.com</t>
         </is>
@@ -499,22 +459,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>93</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -531,22 +489,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -563,22 +519,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -595,22 +549,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="C5" t="n">
+        <v>87</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -627,22 +579,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="C6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -659,22 +609,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="C7" t="n">
+        <v>79</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -691,22 +639,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="C8" t="n">
+        <v>78</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -723,22 +669,20 @@
           <t>form</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="C9" t="n">
+        <v>77</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -755,22 +699,20 @@
           <t>form</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C10" t="n">
+        <v>77</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -787,22 +729,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" t="n">
+        <v>75</v>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -819,22 +759,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="C12" t="n">
+        <v>74</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -851,22 +789,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="C13" t="n">
+        <v>74</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -883,22 +819,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" t="n">
+        <v>73</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -915,22 +849,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="C15" t="n">
+        <v>72</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -947,22 +879,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="C16" t="n">
+        <v>71</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
@@ -979,22 +909,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="C17" t="n">
+        <v>69</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1011,18 +939,16 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="C18" t="n">
+        <v>68</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1035,22 +961,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="C19" t="n">
+        <v>67</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1067,18 +991,16 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="C20" t="n">
+        <v>63</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1091,18 +1013,16 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>62</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1115,18 +1035,16 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="C22" t="n">
+        <v>60</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1139,18 +1057,16 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>60</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1163,18 +1079,16 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="C24" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1187,14 +1101,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>55</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1207,14 +1119,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>54</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1227,22 +1137,20 @@
           <t>form</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="C27" t="n">
+        <v>54</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1259,14 +1167,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>54</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1279,18 +1185,16 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="C29" t="n">
+        <v>52</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1303,22 +1207,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="C30" t="n">
+        <v>48</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
@@ -1335,14 +1237,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>42</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1355,14 +1255,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>41</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1375,14 +1273,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>40</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1395,14 +1291,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>38</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1415,22 +1309,20 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="C35" t="n">
+        <v>35</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1447,14 +1339,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>35</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1467,14 +1357,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="C37" t="n">
+        <v>35</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1487,14 +1375,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>32</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1507,14 +1393,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="C39" t="n">
+        <v>13</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1527,14 +1411,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr"/>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="C40" t="n">
+        <v>13</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1547,14 +1429,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr"/>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1567,14 +1447,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr"/>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1587,14 +1465,12 @@
           <t>directory</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1608,17 +1484,17 @@
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1636,9 +1512,9 @@
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="4" t="inlineStr"/>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1652,17 +1528,17 @@
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1680,17 +1556,17 @@
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1708,17 +1584,17 @@
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1736,9 +1612,9 @@
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1752,9 +1628,9 @@
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1768,9 +1644,9 @@
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr"/>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1784,9 +1660,9 @@
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1800,9 +1676,9 @@
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="4" t="inlineStr"/>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1816,13 +1692,13 @@
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" s="4" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1840,9 +1716,9 @@
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" s="4" t="inlineStr"/>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1856,9 +1732,9 @@
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" s="4" t="inlineStr"/>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1872,13 +1748,13 @@
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" s="4" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1896,13 +1772,13 @@
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -1920,9 +1796,9 @@
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" s="4" t="inlineStr"/>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1936,9 +1812,9 @@
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" s="4" t="inlineStr"/>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1952,9 +1828,9 @@
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" s="4" t="inlineStr"/>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1968,9 +1844,9 @@
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" s="4" t="inlineStr"/>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1984,9 +1860,9 @@
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" s="4" t="inlineStr"/>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2000,17 +1876,17 @@
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2024,9 +1900,9 @@
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" s="4" t="inlineStr"/>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2040,13 +1916,13 @@
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2060,9 +1936,9 @@
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" s="4" t="inlineStr"/>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2076,13 +1952,13 @@
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2096,13 +1972,13 @@
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2116,17 +1992,17 @@
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -2144,13 +2020,13 @@
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2164,17 +2040,17 @@
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2192,13 +2068,13 @@
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2212,17 +2088,17 @@
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2240,13 +2116,13 @@
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2260,17 +2136,17 @@
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -2288,13 +2164,13 @@
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2308,13 +2184,13 @@
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2328,13 +2204,13 @@
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2348,13 +2224,13 @@
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2368,13 +2244,13 @@
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2388,17 +2264,17 @@
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2416,13 +2292,13 @@
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2436,17 +2312,17 @@
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2464,17 +2340,17 @@
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -2492,9 +2368,9 @@
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" s="4" t="inlineStr"/>
-      <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2508,13 +2384,13 @@
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2528,13 +2404,13 @@
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2548,13 +2424,13 @@
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2568,13 +2444,13 @@
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2588,13 +2464,13 @@
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2608,13 +2484,13 @@
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2628,13 +2504,13 @@
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2648,9 +2524,9 @@
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" s="4" t="inlineStr"/>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2664,13 +2540,13 @@
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2684,13 +2560,13 @@
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2704,9 +2580,9 @@
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" s="4" t="inlineStr"/>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2720,9 +2596,9 @@
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" s="4" t="inlineStr"/>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2736,13 +2612,13 @@
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2756,13 +2632,13 @@
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2776,17 +2652,17 @@
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -2804,9 +2680,9 @@
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
-      <c r="D102" s="4" t="inlineStr"/>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2820,13 +2696,13 @@
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2840,17 +2716,17 @@
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -2868,9 +2744,9 @@
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
-      <c r="D105" s="4" t="inlineStr"/>
-      <c r="E105" s="4" t="inlineStr"/>
-      <c r="F105" s="4" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2884,13 +2760,13 @@
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr"/>
-      <c r="F106" s="4" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2904,9 +2780,9 @@
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
-      <c r="D107" s="4" t="inlineStr"/>
-      <c r="E107" s="4" t="inlineStr"/>
-      <c r="F107" s="4" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2920,9 +2796,9 @@
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
-      <c r="D108" s="4" t="inlineStr"/>
-      <c r="E108" s="4" t="inlineStr"/>
-      <c r="F108" s="4" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2936,9 +2812,9 @@
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
-      <c r="D109" s="4" t="inlineStr"/>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2952,13 +2828,13 @@
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2972,9 +2848,9 @@
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
-      <c r="D111" s="4" t="inlineStr"/>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2988,9 +2864,9 @@
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
-      <c r="D112" s="4" t="inlineStr"/>
-      <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3004,9 +2880,9 @@
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
-      <c r="D113" s="4" t="inlineStr"/>
-      <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3020,9 +2896,9 @@
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
-      <c r="D114" s="4" t="inlineStr"/>
-      <c r="E114" s="4" t="inlineStr"/>
-      <c r="F114" s="4" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3036,13 +2912,13 @@
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr"/>
-      <c r="F115" s="4" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3056,9 +2932,9 @@
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
-      <c r="D116" s="4" t="inlineStr"/>
-      <c r="E116" s="4" t="inlineStr"/>
-      <c r="F116" s="4" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3072,13 +2948,13 @@
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3092,9 +2968,9 @@
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
-      <c r="D118" s="4" t="inlineStr"/>
-      <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3108,17 +2984,17 @@
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -3136,13 +3012,13 @@
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
-      <c r="D120" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3156,13 +3032,13 @@
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3176,17 +3052,17 @@
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -3204,13 +3080,13 @@
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="inlineStr"/>
-      <c r="F123" s="4" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3224,17 +3100,17 @@
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -3252,13 +3128,13 @@
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr"/>
-      <c r="F125" s="4" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3272,13 +3148,13 @@
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
-      <c r="D126" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr"/>
-      <c r="F126" s="4" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3292,13 +3168,13 @@
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr"/>
-      <c r="F127" s="4" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3312,13 +3188,13 @@
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3332,13 +3208,13 @@
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr"/>
-      <c r="F129" s="4" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3352,13 +3228,13 @@
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3372,13 +3248,13 @@
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr"/>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3392,13 +3268,13 @@
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3412,17 +3288,17 @@
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -3440,17 +3316,17 @@
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -3468,13 +3344,13 @@
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr"/>
-      <c r="F135" s="4" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3488,13 +3364,13 @@
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr"/>
-      <c r="F136" s="4" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3508,13 +3384,13 @@
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
-      <c r="D137" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="inlineStr"/>
-      <c r="F137" s="4" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3528,13 +3404,13 @@
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
-      <c r="D138" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="inlineStr"/>
-      <c r="F138" s="4" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3548,17 +3424,17 @@
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -3576,17 +3452,17 @@
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -3604,17 +3480,17 @@
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -3632,13 +3508,13 @@
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
-      <c r="D142" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="inlineStr"/>
-      <c r="F142" s="4" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3652,13 +3528,13 @@
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="inlineStr"/>
-      <c r="F143" s="4" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3672,9 +3548,9 @@
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
-      <c r="D144" s="4" t="inlineStr"/>
-      <c r="E144" s="4" t="inlineStr"/>
-      <c r="F144" s="4" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3688,9 +3564,9 @@
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
-      <c r="D145" s="4" t="inlineStr"/>
-      <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3704,9 +3580,9 @@
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
-      <c r="D146" s="4" t="inlineStr"/>
-      <c r="E146" s="4" t="inlineStr"/>
-      <c r="F146" s="4" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3720,9 +3596,9 @@
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
-      <c r="D147" s="4" t="inlineStr"/>
-      <c r="E147" s="4" t="inlineStr"/>
-      <c r="F147" s="4" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3736,9 +3612,9 @@
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
-      <c r="D148" s="4" t="inlineStr"/>
-      <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3752,9 +3628,9 @@
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
-      <c r="D149" s="4" t="inlineStr"/>
-      <c r="E149" s="4" t="inlineStr"/>
-      <c r="F149" s="4" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3768,9 +3644,9 @@
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" s="4" t="inlineStr"/>
-      <c r="E150" s="4" t="inlineStr"/>
-      <c r="F150" s="4" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3784,9 +3660,9 @@
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
-      <c r="D151" s="4" t="inlineStr"/>
-      <c r="E151" s="4" t="inlineStr"/>
-      <c r="F151" s="4" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3800,9 +3676,9 @@
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
-      <c r="D152" s="4" t="inlineStr"/>
-      <c r="E152" s="4" t="inlineStr"/>
-      <c r="F152" s="4" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3816,9 +3692,9 @@
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
-      <c r="D153" s="4" t="inlineStr"/>
-      <c r="E153" s="4" t="inlineStr"/>
-      <c r="F153" s="4" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3832,9 +3708,9 @@
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
-      <c r="D154" s="4" t="inlineStr"/>
-      <c r="E154" s="4" t="inlineStr"/>
-      <c r="F154" s="4" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3848,9 +3724,9 @@
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
-      <c r="D155" s="4" t="inlineStr"/>
-      <c r="E155" s="4" t="inlineStr"/>
-      <c r="F155" s="4" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3864,9 +3740,9 @@
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
-      <c r="D156" s="4" t="inlineStr"/>
-      <c r="E156" s="4" t="inlineStr"/>
-      <c r="F156" s="4" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3880,9 +3756,9 @@
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
-      <c r="D157" s="4" t="inlineStr"/>
-      <c r="E157" s="4" t="inlineStr"/>
-      <c r="F157" s="4" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3896,9 +3772,9 @@
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
-      <c r="D158" s="4" t="inlineStr"/>
-      <c r="E158" s="4" t="inlineStr"/>
-      <c r="F158" s="4" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3912,9 +3788,9 @@
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
-      <c r="D159" s="4" t="inlineStr"/>
-      <c r="E159" s="4" t="inlineStr"/>
-      <c r="F159" s="4" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3928,9 +3804,9 @@
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
-      <c r="D160" s="4" t="inlineStr"/>
-      <c r="E160" s="4" t="inlineStr"/>
-      <c r="F160" s="4" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3944,9 +3820,9 @@
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
-      <c r="D161" s="4" t="inlineStr"/>
-      <c r="E161" s="4" t="inlineStr"/>
-      <c r="F161" s="4" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3960,9 +3836,9 @@
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
-      <c r="D162" s="4" t="inlineStr"/>
-      <c r="E162" s="4" t="inlineStr"/>
-      <c r="F162" s="4" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3976,9 +3852,9 @@
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
-      <c r="D163" s="4" t="inlineStr"/>
-      <c r="E163" s="4" t="inlineStr"/>
-      <c r="F163" s="4" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3992,9 +3868,9 @@
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
-      <c r="D164" s="4" t="inlineStr"/>
-      <c r="E164" s="4" t="inlineStr"/>
-      <c r="F164" s="4" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4008,9 +3884,9 @@
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
-      <c r="D165" s="4" t="inlineStr"/>
-      <c r="E165" s="4" t="inlineStr"/>
-      <c r="F165" s="4" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4024,9 +3900,9 @@
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
-      <c r="D166" s="4" t="inlineStr"/>
-      <c r="E166" s="4" t="inlineStr"/>
-      <c r="F166" s="4" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4040,9 +3916,9 @@
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
-      <c r="D167" s="4" t="inlineStr"/>
-      <c r="E167" s="4" t="inlineStr"/>
-      <c r="F167" s="4" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4056,9 +3932,9 @@
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
-      <c r="D168" s="4" t="inlineStr"/>
-      <c r="E168" s="4" t="inlineStr"/>
-      <c r="F168" s="4" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4072,9 +3948,9 @@
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
-      <c r="D169" s="4" t="inlineStr"/>
-      <c r="E169" s="4" t="inlineStr"/>
-      <c r="F169" s="4" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4088,9 +3964,9 @@
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
-      <c r="D170" s="4" t="inlineStr"/>
-      <c r="E170" s="4" t="inlineStr"/>
-      <c r="F170" s="4" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4104,9 +3980,9 @@
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
-      <c r="D171" s="4" t="inlineStr"/>
-      <c r="E171" s="4" t="inlineStr"/>
-      <c r="F171" s="4" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4120,9 +3996,9 @@
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
-      <c r="D172" s="4" t="inlineStr"/>
-      <c r="E172" s="4" t="inlineStr"/>
-      <c r="F172" s="4" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4136,9 +4012,9 @@
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
-      <c r="D173" s="4" t="inlineStr"/>
-      <c r="E173" s="4" t="inlineStr"/>
-      <c r="F173" s="4" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4152,9 +4028,9 @@
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
-      <c r="D174" s="4" t="inlineStr"/>
-      <c r="E174" s="4" t="inlineStr"/>
-      <c r="F174" s="4" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4168,9 +4044,9 @@
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
-      <c r="D175" s="4" t="inlineStr"/>
-      <c r="E175" s="4" t="inlineStr"/>
-      <c r="F175" s="4" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4184,9 +4060,9 @@
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
-      <c r="D176" s="4" t="inlineStr"/>
-      <c r="E176" s="4" t="inlineStr"/>
-      <c r="F176" s="4" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4200,9 +4076,9 @@
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
-      <c r="D177" s="4" t="inlineStr"/>
-      <c r="E177" s="4" t="inlineStr"/>
-      <c r="F177" s="4" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4216,9 +4092,9 @@
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
-      <c r="D178" s="4" t="inlineStr"/>
-      <c r="E178" s="4" t="inlineStr"/>
-      <c r="F178" s="4" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4232,9 +4108,9 @@
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
-      <c r="D179" s="4" t="inlineStr"/>
-      <c r="E179" s="4" t="inlineStr"/>
-      <c r="F179" s="4" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4248,9 +4124,9 @@
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
-      <c r="D180" s="4" t="inlineStr"/>
-      <c r="E180" s="4" t="inlineStr"/>
-      <c r="F180" s="4" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4264,9 +4140,9 @@
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
-      <c r="D181" s="4" t="inlineStr"/>
-      <c r="E181" s="4" t="inlineStr"/>
-      <c r="F181" s="4" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4280,9 +4156,9 @@
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
-      <c r="D182" s="4" t="inlineStr"/>
-      <c r="E182" s="4" t="inlineStr"/>
-      <c r="F182" s="4" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4296,9 +4172,9 @@
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
-      <c r="D183" s="4" t="inlineStr"/>
-      <c r="E183" s="4" t="inlineStr"/>
-      <c r="F183" s="4" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4312,9 +4188,9 @@
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
-      <c r="D184" s="4" t="inlineStr"/>
-      <c r="E184" s="4" t="inlineStr"/>
-      <c r="F184" s="4" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4328,9 +4204,9 @@
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
-      <c r="D185" s="4" t="inlineStr"/>
-      <c r="E185" s="4" t="inlineStr"/>
-      <c r="F185" s="4" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4344,9 +4220,9 @@
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
-      <c r="D186" s="4" t="inlineStr"/>
-      <c r="E186" s="4" t="inlineStr"/>
-      <c r="F186" s="4" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4360,9 +4236,9 @@
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
-      <c r="D187" s="4" t="inlineStr"/>
-      <c r="E187" s="4" t="inlineStr"/>
-      <c r="F187" s="4" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4376,9 +4252,9 @@
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
-      <c r="D188" s="4" t="inlineStr"/>
-      <c r="E188" s="4" t="inlineStr"/>
-      <c r="F188" s="4" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4392,9 +4268,9 @@
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
-      <c r="D189" s="4" t="inlineStr"/>
-      <c r="E189" s="4" t="inlineStr"/>
-      <c r="F189" s="4" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4408,9 +4284,9 @@
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
-      <c r="D190" s="4" t="inlineStr"/>
-      <c r="E190" s="4" t="inlineStr"/>
-      <c r="F190" s="4" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4424,9 +4300,9 @@
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
-      <c r="D191" s="4" t="inlineStr"/>
-      <c r="E191" s="4" t="inlineStr"/>
-      <c r="F191" s="4" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4440,9 +4316,9 @@
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
-      <c r="D192" s="4" t="inlineStr"/>
-      <c r="E192" s="4" t="inlineStr"/>
-      <c r="F192" s="4" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4456,9 +4332,9 @@
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
-      <c r="D193" s="4" t="inlineStr"/>
-      <c r="E193" s="4" t="inlineStr"/>
-      <c r="F193" s="4" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4472,9 +4348,9 @@
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
-      <c r="D194" s="4" t="inlineStr"/>
-      <c r="E194" s="4" t="inlineStr"/>
-      <c r="F194" s="4" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4488,9 +4364,9 @@
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
-      <c r="D195" s="4" t="inlineStr"/>
-      <c r="E195" s="4" t="inlineStr"/>
-      <c r="F195" s="4" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4504,9 +4380,9 @@
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
-      <c r="D196" s="4" t="inlineStr"/>
-      <c r="E196" s="4" t="inlineStr"/>
-      <c r="F196" s="4" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4520,9 +4396,9 @@
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
-      <c r="D197" s="4" t="inlineStr"/>
-      <c r="E197" s="4" t="inlineStr"/>
-      <c r="F197" s="4" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4536,9 +4412,9 @@
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
-      <c r="D198" s="4" t="inlineStr"/>
-      <c r="E198" s="4" t="inlineStr"/>
-      <c r="F198" s="4" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4552,9 +4428,9 @@
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
-      <c r="D199" s="4" t="inlineStr"/>
-      <c r="E199" s="4" t="inlineStr"/>
-      <c r="F199" s="4" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4568,9 +4444,9 @@
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
-      <c r="D200" s="4" t="inlineStr"/>
-      <c r="E200" s="4" t="inlineStr"/>
-      <c r="F200" s="4" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4584,9 +4460,9 @@
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
-      <c r="D201" s="4" t="inlineStr"/>
-      <c r="E201" s="4" t="inlineStr"/>
-      <c r="F201" s="4" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4600,9 +4476,9 @@
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
-      <c r="D202" s="4" t="inlineStr"/>
-      <c r="E202" s="4" t="inlineStr"/>
-      <c r="F202" s="4" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4616,9 +4492,9 @@
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
-      <c r="D203" s="4" t="inlineStr"/>
-      <c r="E203" s="4" t="inlineStr"/>
-      <c r="F203" s="4" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4632,9 +4508,9 @@
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
-      <c r="D204" s="4" t="inlineStr"/>
-      <c r="E204" s="4" t="inlineStr"/>
-      <c r="F204" s="4" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4648,9 +4524,9 @@
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
-      <c r="D205" s="4" t="inlineStr"/>
-      <c r="E205" s="4" t="inlineStr"/>
-      <c r="F205" s="4" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4664,9 +4540,9 @@
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
-      <c r="D206" s="4" t="inlineStr"/>
-      <c r="E206" s="4" t="inlineStr"/>
-      <c r="F206" s="4" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4680,9 +4556,9 @@
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
-      <c r="D207" s="4" t="inlineStr"/>
-      <c r="E207" s="4" t="inlineStr"/>
-      <c r="F207" s="4" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4696,9 +4572,9 @@
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
-      <c r="D208" s="4" t="inlineStr"/>
-      <c r="E208" s="4" t="inlineStr"/>
-      <c r="F208" s="4" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4712,9 +4588,9 @@
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
-      <c r="D209" s="4" t="inlineStr"/>
-      <c r="E209" s="4" t="inlineStr"/>
-      <c r="F209" s="4" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4728,9 +4604,9 @@
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
-      <c r="D210" s="4" t="inlineStr"/>
-      <c r="E210" s="4" t="inlineStr"/>
-      <c r="F210" s="4" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4744,9 +4620,9 @@
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
-      <c r="D211" s="4" t="inlineStr"/>
-      <c r="E211" s="4" t="inlineStr"/>
-      <c r="F211" s="4" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4760,9 +4636,9 @@
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
-      <c r="D212" s="4" t="inlineStr"/>
-      <c r="E212" s="4" t="inlineStr"/>
-      <c r="F212" s="4" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4776,9 +4652,9 @@
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
-      <c r="D213" s="4" t="inlineStr"/>
-      <c r="E213" s="4" t="inlineStr"/>
-      <c r="F213" s="4" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4792,9 +4668,9 @@
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
-      <c r="D214" s="4" t="inlineStr"/>
-      <c r="E214" s="4" t="inlineStr"/>
-      <c r="F214" s="4" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4808,9 +4684,9 @@
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
-      <c r="D215" s="4" t="inlineStr"/>
-      <c r="E215" s="4" t="inlineStr"/>
-      <c r="F215" s="4" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4824,9 +4700,9 @@
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
-      <c r="D216" s="4" t="inlineStr"/>
-      <c r="E216" s="4" t="inlineStr"/>
-      <c r="F216" s="4" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4840,9 +4716,9 @@
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
-      <c r="D217" s="4" t="inlineStr"/>
-      <c r="E217" s="4" t="inlineStr"/>
-      <c r="F217" s="4" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4856,9 +4732,9 @@
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
-      <c r="D218" s="4" t="inlineStr"/>
-      <c r="E218" s="4" t="inlineStr"/>
-      <c r="F218" s="4" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4872,9 +4748,9 @@
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
-      <c r="D219" s="4" t="inlineStr"/>
-      <c r="E219" s="4" t="inlineStr"/>
-      <c r="F219" s="4" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4888,9 +4764,9 @@
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
-      <c r="D220" s="4" t="inlineStr"/>
-      <c r="E220" s="4" t="inlineStr"/>
-      <c r="F220" s="4" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4904,9 +4780,9 @@
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
-      <c r="D221" s="4" t="inlineStr"/>
-      <c r="E221" s="4" t="inlineStr"/>
-      <c r="F221" s="4" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4920,9 +4796,9 @@
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
-      <c r="D222" s="4" t="inlineStr"/>
-      <c r="E222" s="4" t="inlineStr"/>
-      <c r="F222" s="4" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4936,9 +4812,9 @@
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
-      <c r="D223" s="4" t="inlineStr"/>
-      <c r="E223" s="4" t="inlineStr"/>
-      <c r="F223" s="4" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4952,9 +4828,9 @@
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
-      <c r="D224" s="4" t="inlineStr"/>
-      <c r="E224" s="4" t="inlineStr"/>
-      <c r="F224" s="4" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4968,9 +4844,9 @@
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
-      <c r="D225" s="4" t="inlineStr"/>
-      <c r="E225" s="4" t="inlineStr"/>
-      <c r="F225" s="4" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4984,9 +4860,9 @@
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
-      <c r="D226" s="4" t="inlineStr"/>
-      <c r="E226" s="4" t="inlineStr"/>
-      <c r="F226" s="4" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5000,9 +4876,9 @@
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
-      <c r="D227" s="4" t="inlineStr"/>
-      <c r="E227" s="4" t="inlineStr"/>
-      <c r="F227" s="4" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5016,9 +4892,9 @@
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
-      <c r="D228" s="4" t="inlineStr"/>
-      <c r="E228" s="4" t="inlineStr"/>
-      <c r="F228" s="4" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5032,9 +4908,9 @@
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
-      <c r="D229" s="4" t="inlineStr"/>
-      <c r="E229" s="4" t="inlineStr"/>
-      <c r="F229" s="4" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5048,9 +4924,9 @@
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
-      <c r="D230" s="4" t="inlineStr"/>
-      <c r="E230" s="4" t="inlineStr"/>
-      <c r="F230" s="4" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5064,9 +4940,9 @@
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
-      <c r="D231" s="4" t="inlineStr"/>
-      <c r="E231" s="4" t="inlineStr"/>
-      <c r="F231" s="4" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5080,9 +4956,9 @@
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
-      <c r="D232" s="4" t="inlineStr"/>
-      <c r="E232" s="4" t="inlineStr"/>
-      <c r="F232" s="4" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5096,9 +4972,9 @@
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
-      <c r="D233" s="4" t="inlineStr"/>
-      <c r="E233" s="4" t="inlineStr"/>
-      <c r="F233" s="4" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5112,9 +4988,9 @@
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
-      <c r="D234" s="4" t="inlineStr"/>
-      <c r="E234" s="4" t="inlineStr"/>
-      <c r="F234" s="4" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5128,9 +5004,9 @@
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
-      <c r="D235" s="4" t="inlineStr"/>
-      <c r="E235" s="4" t="inlineStr"/>
-      <c r="F235" s="4" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5144,9 +5020,9 @@
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
-      <c r="D236" s="4" t="inlineStr"/>
-      <c r="E236" s="4" t="inlineStr"/>
-      <c r="F236" s="4" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5160,9 +5036,9 @@
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
-      <c r="D237" s="4" t="inlineStr"/>
-      <c r="E237" s="4" t="inlineStr"/>
-      <c r="F237" s="4" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5176,9 +5052,9 @@
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
-      <c r="D238" s="4" t="inlineStr"/>
-      <c r="E238" s="4" t="inlineStr"/>
-      <c r="F238" s="4" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5192,9 +5068,9 @@
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
-      <c r="D239" s="4" t="inlineStr"/>
-      <c r="E239" s="4" t="inlineStr"/>
-      <c r="F239" s="4" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5208,9 +5084,9 @@
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
-      <c r="D240" s="4" t="inlineStr"/>
-      <c r="E240" s="4" t="inlineStr"/>
-      <c r="F240" s="4" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5224,9 +5100,9 @@
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
-      <c r="D241" s="4" t="inlineStr"/>
-      <c r="E241" s="4" t="inlineStr"/>
-      <c r="F241" s="4" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5240,9 +5116,9 @@
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
-      <c r="D242" s="4" t="inlineStr"/>
-      <c r="E242" s="4" t="inlineStr"/>
-      <c r="F242" s="4" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5256,9 +5132,9 @@
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
-      <c r="D243" s="4" t="inlineStr"/>
-      <c r="E243" s="4" t="inlineStr"/>
-      <c r="F243" s="4" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5272,9 +5148,9 @@
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
-      <c r="D244" s="4" t="inlineStr"/>
-      <c r="E244" s="4" t="inlineStr"/>
-      <c r="F244" s="4" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5288,9 +5164,9 @@
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
-      <c r="D245" s="4" t="inlineStr"/>
-      <c r="E245" s="4" t="inlineStr"/>
-      <c r="F245" s="4" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5304,9 +5180,9 @@
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
-      <c r="D246" s="4" t="inlineStr"/>
-      <c r="E246" s="4" t="inlineStr"/>
-      <c r="F246" s="4" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5320,9 +5196,9 @@
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
-      <c r="D247" s="4" t="inlineStr"/>
-      <c r="E247" s="4" t="inlineStr"/>
-      <c r="F247" s="4" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5336,9 +5212,9 @@
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
-      <c r="D248" s="4" t="inlineStr"/>
-      <c r="E248" s="4" t="inlineStr"/>
-      <c r="F248" s="4" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5352,9 +5228,9 @@
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
-      <c r="D249" s="4" t="inlineStr"/>
-      <c r="E249" s="4" t="inlineStr"/>
-      <c r="F249" s="4" t="inlineStr"/>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5368,9 +5244,9 @@
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
-      <c r="D250" s="4" t="inlineStr"/>
-      <c r="E250" s="4" t="inlineStr"/>
-      <c r="F250" s="4" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5384,9 +5260,9 @@
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
-      <c r="D251" s="4" t="inlineStr"/>
-      <c r="E251" s="4" t="inlineStr"/>
-      <c r="F251" s="4" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5400,9 +5276,9 @@
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
-      <c r="D252" s="4" t="inlineStr"/>
-      <c r="E252" s="4" t="inlineStr"/>
-      <c r="F252" s="4" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5416,9 +5292,9 @@
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
-      <c r="D253" s="4" t="inlineStr"/>
-      <c r="E253" s="4" t="inlineStr"/>
-      <c r="F253" s="4" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5432,9 +5308,9 @@
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
-      <c r="D254" s="4" t="inlineStr"/>
-      <c r="E254" s="4" t="inlineStr"/>
-      <c r="F254" s="4" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5448,9 +5324,9 @@
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
-      <c r="D255" s="4" t="inlineStr"/>
-      <c r="E255" s="4" t="inlineStr"/>
-      <c r="F255" s="4" t="inlineStr"/>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5464,9 +5340,9 @@
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
-      <c r="D256" s="4" t="inlineStr"/>
-      <c r="E256" s="4" t="inlineStr"/>
-      <c r="F256" s="4" t="inlineStr"/>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5480,9 +5356,9 @@
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
-      <c r="D257" s="4" t="inlineStr"/>
-      <c r="E257" s="4" t="inlineStr"/>
-      <c r="F257" s="4" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5496,9 +5372,9 @@
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
-      <c r="D258" s="4" t="inlineStr"/>
-      <c r="E258" s="4" t="inlineStr"/>
-      <c r="F258" s="4" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5512,9 +5388,9 @@
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
-      <c r="D259" s="4" t="inlineStr"/>
-      <c r="E259" s="4" t="inlineStr"/>
-      <c r="F259" s="4" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5528,9 +5404,9 @@
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
-      <c r="D260" s="4" t="inlineStr"/>
-      <c r="E260" s="4" t="inlineStr"/>
-      <c r="F260" s="4" t="inlineStr"/>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5544,9 +5420,9 @@
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
-      <c r="D261" s="4" t="inlineStr"/>
-      <c r="E261" s="4" t="inlineStr"/>
-      <c r="F261" s="4" t="inlineStr"/>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5560,9 +5436,9 @@
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
-      <c r="D262" s="4" t="inlineStr"/>
-      <c r="E262" s="4" t="inlineStr"/>
-      <c r="F262" s="4" t="inlineStr"/>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5576,9 +5452,9 @@
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
-      <c r="D263" s="4" t="inlineStr"/>
-      <c r="E263" s="4" t="inlineStr"/>
-      <c r="F263" s="4" t="inlineStr"/>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5592,9 +5468,9 @@
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
-      <c r="D264" s="4" t="inlineStr"/>
-      <c r="E264" s="4" t="inlineStr"/>
-      <c r="F264" s="4" t="inlineStr"/>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5608,9 +5484,9 @@
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
-      <c r="D265" s="4" t="inlineStr"/>
-      <c r="E265" s="4" t="inlineStr"/>
-      <c r="F265" s="4" t="inlineStr"/>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -5624,9 +5500,9 @@
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
-      <c r="D266" s="4" t="inlineStr"/>
-      <c r="E266" s="4" t="inlineStr"/>
-      <c r="F266" s="4" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -5640,9 +5516,9 @@
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
-      <c r="D267" s="4" t="inlineStr"/>
-      <c r="E267" s="4" t="inlineStr"/>
-      <c r="F267" s="4" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -5656,9 +5532,9 @@
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
-      <c r="D268" s="4" t="inlineStr"/>
-      <c r="E268" s="4" t="inlineStr"/>
-      <c r="F268" s="4" t="inlineStr"/>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5672,9 +5548,9 @@
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
-      <c r="D269" s="4" t="inlineStr"/>
-      <c r="E269" s="4" t="inlineStr"/>
-      <c r="F269" s="4" t="inlineStr"/>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5688,9 +5564,9 @@
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
-      <c r="D270" s="4" t="inlineStr"/>
-      <c r="E270" s="4" t="inlineStr"/>
-      <c r="F270" s="4" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5704,9 +5580,9 @@
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
-      <c r="D271" s="4" t="inlineStr"/>
-      <c r="E271" s="4" t="inlineStr"/>
-      <c r="F271" s="4" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5720,9 +5596,9 @@
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
-      <c r="D272" s="4" t="inlineStr"/>
-      <c r="E272" s="4" t="inlineStr"/>
-      <c r="F272" s="4" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5736,9 +5612,9 @@
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
-      <c r="D273" s="4" t="inlineStr"/>
-      <c r="E273" s="4" t="inlineStr"/>
-      <c r="F273" s="4" t="inlineStr"/>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -5752,9 +5628,9 @@
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
-      <c r="D274" s="4" t="inlineStr"/>
-      <c r="E274" s="4" t="inlineStr"/>
-      <c r="F274" s="4" t="inlineStr"/>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5768,9 +5644,9 @@
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
-      <c r="D275" s="4" t="inlineStr"/>
-      <c r="E275" s="4" t="inlineStr"/>
-      <c r="F275" s="4" t="inlineStr"/>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5784,9 +5660,9 @@
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
-      <c r="D276" s="4" t="inlineStr"/>
-      <c r="E276" s="4" t="inlineStr"/>
-      <c r="F276" s="4" t="inlineStr"/>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5800,9 +5676,9 @@
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
-      <c r="D277" s="4" t="inlineStr"/>
-      <c r="E277" s="4" t="inlineStr"/>
-      <c r="F277" s="4" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -5816,9 +5692,9 @@
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
-      <c r="D278" s="4" t="inlineStr"/>
-      <c r="E278" s="4" t="inlineStr"/>
-      <c r="F278" s="4" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -5832,9 +5708,9 @@
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
-      <c r="D279" s="4" t="inlineStr"/>
-      <c r="E279" s="4" t="inlineStr"/>
-      <c r="F279" s="4" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -5848,9 +5724,9 @@
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
-      <c r="D280" s="4" t="inlineStr"/>
-      <c r="E280" s="4" t="inlineStr"/>
-      <c r="F280" s="4" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -5864,9 +5740,9 @@
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
-      <c r="D281" s="4" t="inlineStr"/>
-      <c r="E281" s="4" t="inlineStr"/>
-      <c r="F281" s="4" t="inlineStr"/>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -5880,9 +5756,9 @@
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
-      <c r="D282" s="4" t="inlineStr"/>
-      <c r="E282" s="4" t="inlineStr"/>
-      <c r="F282" s="4" t="inlineStr"/>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -5896,9 +5772,9 @@
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
-      <c r="D283" s="4" t="inlineStr"/>
-      <c r="E283" s="4" t="inlineStr"/>
-      <c r="F283" s="4" t="inlineStr"/>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5912,9 +5788,9 @@
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
-      <c r="D284" s="4" t="inlineStr"/>
-      <c r="E284" s="4" t="inlineStr"/>
-      <c r="F284" s="4" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -5928,9 +5804,9 @@
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
-      <c r="D285" s="4" t="inlineStr"/>
-      <c r="E285" s="4" t="inlineStr"/>
-      <c r="F285" s="4" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5944,9 +5820,9 @@
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
-      <c r="D286" s="4" t="inlineStr"/>
-      <c r="E286" s="4" t="inlineStr"/>
-      <c r="F286" s="4" t="inlineStr"/>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5960,9 +5836,9 @@
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
-      <c r="D287" s="4" t="inlineStr"/>
-      <c r="E287" s="4" t="inlineStr"/>
-      <c r="F287" s="4" t="inlineStr"/>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5976,9 +5852,9 @@
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
-      <c r="D288" s="4" t="inlineStr"/>
-      <c r="E288" s="4" t="inlineStr"/>
-      <c r="F288" s="4" t="inlineStr"/>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5992,9 +5868,9 @@
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
-      <c r="D289" s="4" t="inlineStr"/>
-      <c r="E289" s="4" t="inlineStr"/>
-      <c r="F289" s="4" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6008,9 +5884,9 @@
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
-      <c r="D290" s="4" t="inlineStr"/>
-      <c r="E290" s="4" t="inlineStr"/>
-      <c r="F290" s="4" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6024,9 +5900,9 @@
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
-      <c r="D291" s="4" t="inlineStr"/>
-      <c r="E291" s="4" t="inlineStr"/>
-      <c r="F291" s="4" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6040,9 +5916,9 @@
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
-      <c r="D292" s="4" t="inlineStr"/>
-      <c r="E292" s="4" t="inlineStr"/>
-      <c r="F292" s="4" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6056,9 +5932,9 @@
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
-      <c r="D293" s="4" t="inlineStr"/>
-      <c r="E293" s="4" t="inlineStr"/>
-      <c r="F293" s="4" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6072,9 +5948,9 @@
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
-      <c r="D294" s="4" t="inlineStr"/>
-      <c r="E294" s="4" t="inlineStr"/>
-      <c r="F294" s="4" t="inlineStr"/>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6088,9 +5964,9 @@
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
-      <c r="D295" s="4" t="inlineStr"/>
-      <c r="E295" s="4" t="inlineStr"/>
-      <c r="F295" s="4" t="inlineStr"/>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6104,9 +5980,9 @@
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
-      <c r="D296" s="4" t="inlineStr"/>
-      <c r="E296" s="4" t="inlineStr"/>
-      <c r="F296" s="4" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6120,9 +5996,9 @@
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
-      <c r="D297" s="4" t="inlineStr"/>
-      <c r="E297" s="4" t="inlineStr"/>
-      <c r="F297" s="4" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6136,9 +6012,9 @@
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
-      <c r="D298" s="4" t="inlineStr"/>
-      <c r="E298" s="4" t="inlineStr"/>
-      <c r="F298" s="4" t="inlineStr"/>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -6152,9 +6028,9 @@
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
-      <c r="D299" s="4" t="inlineStr"/>
-      <c r="E299" s="4" t="inlineStr"/>
-      <c r="F299" s="4" t="inlineStr"/>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -6168,9 +6044,9 @@
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
-      <c r="D300" s="4" t="inlineStr"/>
-      <c r="E300" s="4" t="inlineStr"/>
-      <c r="F300" s="4" t="inlineStr"/>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -6184,9 +6060,9 @@
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
-      <c r="D301" s="4" t="inlineStr"/>
-      <c r="E301" s="4" t="inlineStr"/>
-      <c r="F301" s="4" t="inlineStr"/>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -6200,9 +6076,9 @@
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
-      <c r="D302" s="4" t="inlineStr"/>
-      <c r="E302" s="4" t="inlineStr"/>
-      <c r="F302" s="4" t="inlineStr"/>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -6216,9 +6092,9 @@
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
-      <c r="D303" s="4" t="inlineStr"/>
-      <c r="E303" s="4" t="inlineStr"/>
-      <c r="F303" s="4" t="inlineStr"/>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -6232,9 +6108,9 @@
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
-      <c r="D304" s="4" t="inlineStr"/>
-      <c r="E304" s="4" t="inlineStr"/>
-      <c r="F304" s="4" t="inlineStr"/>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6248,9 +6124,9 @@
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
-      <c r="D305" s="4" t="inlineStr"/>
-      <c r="E305" s="4" t="inlineStr"/>
-      <c r="F305" s="4" t="inlineStr"/>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6264,9 +6140,9 @@
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
-      <c r="D306" s="4" t="inlineStr"/>
-      <c r="E306" s="4" t="inlineStr"/>
-      <c r="F306" s="4" t="inlineStr"/>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6280,9 +6156,9 @@
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
-      <c r="D307" s="4" t="inlineStr"/>
-      <c r="E307" s="4" t="inlineStr"/>
-      <c r="F307" s="4" t="inlineStr"/>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6296,9 +6172,9 @@
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
-      <c r="D308" s="4" t="inlineStr"/>
-      <c r="E308" s="4" t="inlineStr"/>
-      <c r="F308" s="4" t="inlineStr"/>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6312,9 +6188,9 @@
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
-      <c r="D309" s="4" t="inlineStr"/>
-      <c r="E309" s="4" t="inlineStr"/>
-      <c r="F309" s="4" t="inlineStr"/>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6328,9 +6204,9 @@
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
-      <c r="D310" s="4" t="inlineStr"/>
-      <c r="E310" s="4" t="inlineStr"/>
-      <c r="F310" s="4" t="inlineStr"/>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6344,9 +6220,9 @@
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
-      <c r="D311" s="4" t="inlineStr"/>
-      <c r="E311" s="4" t="inlineStr"/>
-      <c r="F311" s="4" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6360,9 +6236,9 @@
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
-      <c r="D312" s="4" t="inlineStr"/>
-      <c r="E312" s="4" t="inlineStr"/>
-      <c r="F312" s="4" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr"/>
+      <c r="F312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6376,9 +6252,9 @@
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
-      <c r="D313" s="4" t="inlineStr"/>
-      <c r="E313" s="4" t="inlineStr"/>
-      <c r="F313" s="4" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr"/>
+      <c r="F313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6392,9 +6268,9 @@
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
-      <c r="D314" s="4" t="inlineStr"/>
-      <c r="E314" s="4" t="inlineStr"/>
-      <c r="F314" s="4" t="inlineStr"/>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6408,9 +6284,9 @@
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
-      <c r="D315" s="4" t="inlineStr"/>
-      <c r="E315" s="4" t="inlineStr"/>
-      <c r="F315" s="4" t="inlineStr"/>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6424,9 +6300,9 @@
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
-      <c r="D316" s="4" t="inlineStr"/>
-      <c r="E316" s="4" t="inlineStr"/>
-      <c r="F316" s="4" t="inlineStr"/>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6440,9 +6316,9 @@
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
-      <c r="D317" s="4" t="inlineStr"/>
-      <c r="E317" s="4" t="inlineStr"/>
-      <c r="F317" s="4" t="inlineStr"/>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6456,9 +6332,9 @@
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
-      <c r="D318" s="4" t="inlineStr"/>
-      <c r="E318" s="4" t="inlineStr"/>
-      <c r="F318" s="4" t="inlineStr"/>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6472,17 +6348,17 @@
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
-      <c r="D319" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E319" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F319" s="2" t="inlineStr">
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6500,17 +6376,17 @@
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
-      <c r="D320" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E320" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F320" s="2" t="inlineStr">
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6528,17 +6404,17 @@
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
-      <c r="D321" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E321" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F321" s="2" t="inlineStr">
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6556,17 +6432,17 @@
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
-      <c r="D322" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E322" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F322" s="2" t="inlineStr">
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6584,17 +6460,17 @@
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
-      <c r="D323" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F323" s="2" t="inlineStr">
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6612,17 +6488,17 @@
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
-      <c r="D324" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E324" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F324" s="2" t="inlineStr">
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6640,17 +6516,17 @@
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
-      <c r="D325" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E325" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F325" s="2" t="inlineStr">
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6668,17 +6544,17 @@
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
-      <c r="D326" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E326" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F326" s="2" t="inlineStr">
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6696,17 +6572,17 @@
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
-      <c r="D327" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E327" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F327" s="2" t="inlineStr">
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6724,17 +6600,17 @@
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
-      <c r="D328" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E328" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F328" s="2" t="inlineStr">
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6752,17 +6628,17 @@
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
-      <c r="D329" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E329" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F329" s="2" t="inlineStr">
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6780,17 +6656,17 @@
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
-      <c r="D330" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E330" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F330" s="2" t="inlineStr">
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6808,17 +6684,17 @@
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
-      <c r="D331" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E331" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F331" s="2" t="inlineStr">
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -6836,9 +6712,9 @@
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
-      <c r="D332" s="4" t="inlineStr"/>
-      <c r="E332" s="4" t="inlineStr"/>
-      <c r="F332" s="4" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6852,9 +6728,9 @@
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
-      <c r="D333" s="4" t="inlineStr"/>
-      <c r="E333" s="4" t="inlineStr"/>
-      <c r="F333" s="4" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6868,9 +6744,9 @@
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
-      <c r="D334" s="4" t="inlineStr"/>
-      <c r="E334" s="4" t="inlineStr"/>
-      <c r="F334" s="4" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6884,9 +6760,9 @@
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
-      <c r="D335" s="4" t="inlineStr"/>
-      <c r="E335" s="4" t="inlineStr"/>
-      <c r="F335" s="4" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6900,9 +6776,9 @@
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
-      <c r="D336" s="4" t="inlineStr"/>
-      <c r="E336" s="4" t="inlineStr"/>
-      <c r="F336" s="4" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6916,9 +6792,9 @@
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
-      <c r="D337" s="4" t="inlineStr"/>
-      <c r="E337" s="4" t="inlineStr"/>
-      <c r="F337" s="4" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6932,9 +6808,9 @@
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
-      <c r="D338" s="4" t="inlineStr"/>
-      <c r="E338" s="4" t="inlineStr"/>
-      <c r="F338" s="4" t="inlineStr"/>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6948,9 +6824,9 @@
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
-      <c r="D339" s="4" t="inlineStr"/>
-      <c r="E339" s="4" t="inlineStr"/>
-      <c r="F339" s="4" t="inlineStr"/>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6964,9 +6840,9 @@
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
-      <c r="D340" s="4" t="inlineStr"/>
-      <c r="E340" s="4" t="inlineStr"/>
-      <c r="F340" s="4" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6980,9 +6856,9 @@
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
-      <c r="D341" s="4" t="inlineStr"/>
-      <c r="E341" s="4" t="inlineStr"/>
-      <c r="F341" s="4" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -6996,9 +6872,9 @@
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
-      <c r="D342" s="4" t="inlineStr"/>
-      <c r="E342" s="4" t="inlineStr"/>
-      <c r="F342" s="4" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7012,9 +6888,9 @@
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
-      <c r="D343" s="4" t="inlineStr"/>
-      <c r="E343" s="4" t="inlineStr"/>
-      <c r="F343" s="4" t="inlineStr"/>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -7028,9 +6904,9 @@
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
-      <c r="D344" s="4" t="inlineStr"/>
-      <c r="E344" s="4" t="inlineStr"/>
-      <c r="F344" s="4" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -7044,9 +6920,9 @@
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
-      <c r="D345" s="4" t="inlineStr"/>
-      <c r="E345" s="4" t="inlineStr"/>
-      <c r="F345" s="4" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -7060,9 +6936,9 @@
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
-      <c r="D346" s="4" t="inlineStr"/>
-      <c r="E346" s="4" t="inlineStr"/>
-      <c r="F346" s="4" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -7076,9 +6952,9 @@
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
-      <c r="D347" s="4" t="inlineStr"/>
-      <c r="E347" s="4" t="inlineStr"/>
-      <c r="F347" s="4" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -7092,9 +6968,9 @@
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
-      <c r="D348" s="4" t="inlineStr"/>
-      <c r="E348" s="4" t="inlineStr"/>
-      <c r="F348" s="4" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -7108,9 +6984,9 @@
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
-      <c r="D349" s="4" t="inlineStr"/>
-      <c r="E349" s="4" t="inlineStr"/>
-      <c r="F349" s="4" t="inlineStr"/>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -7124,9 +7000,9 @@
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
-      <c r="D350" s="4" t="inlineStr"/>
-      <c r="E350" s="4" t="inlineStr"/>
-      <c r="F350" s="4" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -7140,9 +7016,9 @@
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
-      <c r="D351" s="4" t="inlineStr"/>
-      <c r="E351" s="4" t="inlineStr"/>
-      <c r="F351" s="4" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -7156,17 +7032,17 @@
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
-      <c r="D352" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E352" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F352" s="4" t="inlineStr">
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -7184,17 +7060,17 @@
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
-      <c r="D353" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E353" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F353" s="2" t="inlineStr">
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7212,17 +7088,17 @@
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
-      <c r="D354" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E354" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F354" s="2" t="inlineStr">
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7240,17 +7116,17 @@
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
-      <c r="D355" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E355" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F355" s="2" t="inlineStr">
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7268,17 +7144,17 @@
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
-      <c r="D356" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E356" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F356" s="4" t="inlineStr">
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -7296,17 +7172,17 @@
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
-      <c r="D357" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E357" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F357" s="2" t="inlineStr">
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7324,13 +7200,13 @@
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
-      <c r="D358" s="4" t="inlineStr"/>
-      <c r="E358" s="3" t="inlineStr">
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="F358" s="3" t="inlineStr">
+      <c r="F358" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
@@ -7348,13 +7224,13 @@
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
-      <c r="D359" s="4" t="inlineStr"/>
-      <c r="E359" s="3" t="inlineStr">
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="F359" s="3" t="inlineStr">
+      <c r="F359" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
@@ -7372,17 +7248,17 @@
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
-      <c r="D360" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E360" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F360" s="2" t="inlineStr">
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7400,17 +7276,17 @@
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
-      <c r="D361" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E361" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F361" s="2" t="inlineStr">
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7428,17 +7304,17 @@
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
-      <c r="D362" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E362" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F362" s="2" t="inlineStr">
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7456,17 +7332,17 @@
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
-      <c r="D363" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E363" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F363" s="4" t="inlineStr">
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -7484,17 +7360,17 @@
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
-      <c r="D364" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E364" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F364" s="2" t="inlineStr">
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7512,13 +7388,13 @@
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
-      <c r="D365" s="4" t="inlineStr"/>
-      <c r="E365" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F365" s="4" t="inlineStr">
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -7536,13 +7412,13 @@
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
-      <c r="D366" s="4" t="inlineStr"/>
-      <c r="E366" s="3" t="inlineStr">
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="F366" s="3" t="inlineStr">
+      <c r="F366" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
@@ -7560,13 +7436,13 @@
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
-      <c r="D367" s="4" t="inlineStr"/>
-      <c r="E367" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F367" s="4" t="inlineStr">
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -7584,13 +7460,13 @@
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
-      <c r="D368" s="4" t="inlineStr"/>
-      <c r="E368" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F368" s="4" t="inlineStr">
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -7608,13 +7484,13 @@
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
-      <c r="D369" s="4" t="inlineStr"/>
-      <c r="E369" s="3" t="inlineStr">
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
       </c>
-      <c r="F369" s="3" t="inlineStr">
+      <c r="F369" t="inlineStr">
         <is>
           <t>需登录</t>
         </is>
@@ -7632,17 +7508,17 @@
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
-      <c r="D370" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E370" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F370" s="2" t="inlineStr">
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7660,17 +7536,17 @@
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
-      <c r="D371" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E371" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F371" s="2" t="inlineStr">
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7688,17 +7564,17 @@
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
-      <c r="D372" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E372" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F372" s="2" t="inlineStr">
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7716,13 +7592,13 @@
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
-      <c r="D373" s="4" t="inlineStr"/>
-      <c r="E373" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F373" s="4" t="inlineStr">
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -7740,13 +7616,13 @@
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
-      <c r="D374" s="4" t="inlineStr"/>
-      <c r="E374" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F374" s="4" t="inlineStr">
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -7764,17 +7640,17 @@
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
-      <c r="D375" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E375" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F375" s="2" t="inlineStr">
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7792,13 +7668,13 @@
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
-      <c r="D376" s="4" t="inlineStr"/>
-      <c r="E376" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F376" s="4" t="inlineStr">
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -7816,17 +7692,17 @@
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
-      <c r="D377" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E377" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F377" s="2" t="inlineStr">
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7844,17 +7720,17 @@
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
-      <c r="D378" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E378" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F378" s="2" t="inlineStr">
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7872,17 +7748,17 @@
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
-      <c r="D379" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E379" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F379" s="2" t="inlineStr">
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7900,17 +7776,17 @@
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
-      <c r="D380" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E380" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F380" s="2" t="inlineStr">
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7928,17 +7804,17 @@
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
-      <c r="D381" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E381" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F381" s="2" t="inlineStr">
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7956,17 +7832,17 @@
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
-      <c r="D382" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E382" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F382" s="2" t="inlineStr">
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -7984,17 +7860,17 @@
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
-      <c r="D383" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E383" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F383" s="4" t="inlineStr">
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -8012,17 +7888,17 @@
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
-      <c r="D384" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E384" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F384" s="2" t="inlineStr">
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8040,9 +7916,9 @@
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
-      <c r="D385" s="4" t="inlineStr"/>
-      <c r="E385" s="4" t="inlineStr"/>
-      <c r="F385" s="4" t="inlineStr"/>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -8056,9 +7932,9 @@
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
-      <c r="D386" s="4" t="inlineStr"/>
-      <c r="E386" s="4" t="inlineStr"/>
-      <c r="F386" s="4" t="inlineStr"/>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -8072,9 +7948,9 @@
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
-      <c r="D387" s="4" t="inlineStr"/>
-      <c r="E387" s="4" t="inlineStr"/>
-      <c r="F387" s="4" t="inlineStr"/>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -8088,9 +7964,9 @@
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
-      <c r="D388" s="4" t="inlineStr"/>
-      <c r="E388" s="4" t="inlineStr"/>
-      <c r="F388" s="4" t="inlineStr"/>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -8104,9 +7980,9 @@
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
-      <c r="D389" s="4" t="inlineStr"/>
-      <c r="E389" s="4" t="inlineStr"/>
-      <c r="F389" s="4" t="inlineStr"/>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -8120,13 +7996,13 @@
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
-      <c r="D390" s="4" t="inlineStr"/>
-      <c r="E390" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F390" s="4" t="inlineStr">
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -8144,13 +8020,13 @@
         </is>
       </c>
       <c r="C391" t="inlineStr"/>
-      <c r="D391" s="4" t="inlineStr"/>
-      <c r="E391" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F391" s="4" t="inlineStr">
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -8168,13 +8044,13 @@
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
-      <c r="D392" s="4" t="inlineStr"/>
-      <c r="E392" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F392" s="2" t="inlineStr">
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8192,13 +8068,13 @@
         </is>
       </c>
       <c r="C393" t="inlineStr"/>
-      <c r="D393" s="4" t="inlineStr"/>
-      <c r="E393" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F393" s="4" t="inlineStr">
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -8216,9 +8092,9 @@
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
-      <c r="D394" s="4" t="inlineStr"/>
-      <c r="E394" s="4" t="inlineStr"/>
-      <c r="F394" s="4" t="inlineStr"/>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -8232,9 +8108,9 @@
         </is>
       </c>
       <c r="C395" t="inlineStr"/>
-      <c r="D395" s="4" t="inlineStr"/>
-      <c r="E395" s="4" t="inlineStr"/>
-      <c r="F395" s="4" t="inlineStr"/>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -8248,9 +8124,9 @@
         </is>
       </c>
       <c r="C396" t="inlineStr"/>
-      <c r="D396" s="4" t="inlineStr"/>
-      <c r="E396" s="4" t="inlineStr"/>
-      <c r="F396" s="4" t="inlineStr"/>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -8264,9 +8140,9 @@
         </is>
       </c>
       <c r="C397" t="inlineStr"/>
-      <c r="D397" s="4" t="inlineStr"/>
-      <c r="E397" s="4" t="inlineStr"/>
-      <c r="F397" s="4" t="inlineStr"/>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -8280,17 +8156,17 @@
         </is>
       </c>
       <c r="C398" t="inlineStr"/>
-      <c r="D398" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E398" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F398" s="2" t="inlineStr">
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8308,17 +8184,17 @@
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
-      <c r="D399" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E399" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F399" s="2" t="inlineStr">
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8336,9 +8212,9 @@
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
-      <c r="D400" s="4" t="inlineStr"/>
-      <c r="E400" s="4" t="inlineStr"/>
-      <c r="F400" s="4" t="inlineStr"/>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -8352,17 +8228,17 @@
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
-      <c r="D401" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E401" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F401" s="2" t="inlineStr">
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8380,17 +8256,17 @@
         </is>
       </c>
       <c r="C402" t="inlineStr"/>
-      <c r="D402" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E402" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F402" s="2" t="inlineStr">
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8408,17 +8284,17 @@
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
-      <c r="D403" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E403" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F403" s="2" t="inlineStr">
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8436,9 +8312,9 @@
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
-      <c r="D404" s="4" t="inlineStr"/>
-      <c r="E404" s="4" t="inlineStr"/>
-      <c r="F404" s="4" t="inlineStr"/>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -8452,13 +8328,13 @@
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
-      <c r="D405" s="4" t="inlineStr"/>
-      <c r="E405" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F405" s="4" t="inlineStr">
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -8476,17 +8352,17 @@
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
-      <c r="D406" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E406" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F406" s="2" t="inlineStr">
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8504,13 +8380,13 @@
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
-      <c r="D407" s="4" t="inlineStr"/>
-      <c r="E407" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F407" s="4" t="inlineStr">
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -8528,13 +8404,13 @@
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
-      <c r="D408" s="4" t="inlineStr"/>
-      <c r="E408" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F408" s="4" t="inlineStr">
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -8552,17 +8428,17 @@
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
-      <c r="D409" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E409" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F409" s="2" t="inlineStr">
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8580,17 +8456,17 @@
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
-      <c r="D410" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E410" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F410" s="2" t="inlineStr">
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8608,15 +8484,19 @@
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
-      <c r="D411" s="4" t="inlineStr"/>
-      <c r="E411" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F411" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>已提交</t>
         </is>
       </c>
     </row>
@@ -8632,17 +8512,17 @@
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E412" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F412" s="2" t="inlineStr">
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8660,9 +8540,9 @@
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
-      <c r="D413" s="4" t="inlineStr"/>
-      <c r="E413" s="4" t="inlineStr"/>
-      <c r="F413" s="4" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -8676,13 +8556,13 @@
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
-      <c r="D414" s="4" t="inlineStr"/>
-      <c r="E414" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F414" s="4" t="inlineStr">
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
@@ -8700,17 +8580,17 @@
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
-      <c r="D415" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E415" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F415" s="2" t="inlineStr">
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8728,17 +8608,17 @@
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
-      <c r="D416" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E416" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F416" s="2" t="inlineStr">
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8756,9 +8636,9 @@
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
-      <c r="D417" s="4" t="inlineStr"/>
-      <c r="E417" s="4" t="inlineStr"/>
-      <c r="F417" s="4" t="inlineStr"/>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -8772,9 +8652,9 @@
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
-      <c r="D418" s="4" t="inlineStr"/>
-      <c r="E418" s="4" t="inlineStr"/>
-      <c r="F418" s="4" t="inlineStr"/>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -8788,9 +8668,9 @@
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
-      <c r="D419" s="4" t="inlineStr"/>
-      <c r="E419" s="4" t="inlineStr"/>
-      <c r="F419" s="4" t="inlineStr"/>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -8804,17 +8684,17 @@
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
-      <c r="D420" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E420" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F420" s="2" t="inlineStr">
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8832,9 +8712,9 @@
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
-      <c r="D421" s="4" t="inlineStr"/>
-      <c r="E421" s="4" t="inlineStr"/>
-      <c r="F421" s="4" t="inlineStr"/>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -8848,17 +8728,17 @@
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
-      <c r="D422" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E422" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F422" s="2" t="inlineStr">
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -8876,9 +8756,9 @@
         </is>
       </c>
       <c r="C423" t="inlineStr"/>
-      <c r="D423" s="4" t="inlineStr"/>
-      <c r="E423" s="4" t="inlineStr"/>
-      <c r="F423" s="4" t="inlineStr"/>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -8892,9 +8772,9 @@
         </is>
       </c>
       <c r="C424" t="inlineStr"/>
-      <c r="D424" s="4" t="inlineStr"/>
-      <c r="E424" s="4" t="inlineStr"/>
-      <c r="F424" s="4" t="inlineStr"/>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -8908,9 +8788,9 @@
         </is>
       </c>
       <c r="C425" t="inlineStr"/>
-      <c r="D425" s="4" t="inlineStr"/>
-      <c r="E425" s="4" t="inlineStr"/>
-      <c r="F425" s="4" t="inlineStr"/>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -8924,9 +8804,9 @@
         </is>
       </c>
       <c r="C426" t="inlineStr"/>
-      <c r="D426" s="4" t="inlineStr"/>
-      <c r="E426" s="4" t="inlineStr"/>
-      <c r="F426" s="4" t="inlineStr"/>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -8940,9 +8820,9 @@
         </is>
       </c>
       <c r="C427" t="inlineStr"/>
-      <c r="D427" s="4" t="inlineStr"/>
-      <c r="E427" s="4" t="inlineStr"/>
-      <c r="F427" s="4" t="inlineStr"/>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -8956,9 +8836,9 @@
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
-      <c r="D428" s="4" t="inlineStr"/>
-      <c r="E428" s="4" t="inlineStr"/>
-      <c r="F428" s="4" t="inlineStr"/>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -8972,9 +8852,9 @@
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" s="4" t="inlineStr"/>
-      <c r="E429" s="4" t="inlineStr"/>
-      <c r="F429" s="4" t="inlineStr"/>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -8988,9 +8868,9 @@
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" s="4" t="inlineStr"/>
-      <c r="E430" s="4" t="inlineStr"/>
-      <c r="F430" s="4" t="inlineStr"/>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -9004,9 +8884,9 @@
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" s="4" t="inlineStr"/>
-      <c r="E431" s="4" t="inlineStr"/>
-      <c r="F431" s="4" t="inlineStr"/>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -9020,9 +8900,9 @@
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" s="4" t="inlineStr"/>
-      <c r="E432" s="4" t="inlineStr"/>
-      <c r="F432" s="4" t="inlineStr"/>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -9036,9 +8916,9 @@
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" s="4" t="inlineStr"/>
-      <c r="E433" s="4" t="inlineStr"/>
-      <c r="F433" s="4" t="inlineStr"/>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -9052,9 +8932,9 @@
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" s="4" t="inlineStr"/>
-      <c r="E434" s="4" t="inlineStr"/>
-      <c r="F434" s="4" t="inlineStr"/>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -9068,9 +8948,9 @@
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" s="4" t="inlineStr"/>
-      <c r="E435" s="4" t="inlineStr"/>
-      <c r="F435" s="4" t="inlineStr"/>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -9084,9 +8964,9 @@
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" s="4" t="inlineStr"/>
-      <c r="E436" s="4" t="inlineStr"/>
-      <c r="F436" s="4" t="inlineStr"/>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -9100,9 +8980,9 @@
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" s="4" t="inlineStr"/>
-      <c r="E437" s="4" t="inlineStr"/>
-      <c r="F437" s="4" t="inlineStr"/>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -9116,9 +8996,9 @@
         </is>
       </c>
       <c r="C438" t="inlineStr"/>
-      <c r="D438" s="4" t="inlineStr"/>
-      <c r="E438" s="4" t="inlineStr"/>
-      <c r="F438" s="4" t="inlineStr"/>
+      <c r="D438" t="inlineStr"/>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -9132,9 +9012,9 @@
         </is>
       </c>
       <c r="C439" t="inlineStr"/>
-      <c r="D439" s="4" t="inlineStr"/>
-      <c r="E439" s="4" t="inlineStr"/>
-      <c r="F439" s="4" t="inlineStr"/>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -9148,9 +9028,9 @@
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
-      <c r="D440" s="4" t="inlineStr"/>
-      <c r="E440" s="4" t="inlineStr"/>
-      <c r="F440" s="4" t="inlineStr"/>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -9164,9 +9044,9 @@
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
-      <c r="D441" s="4" t="inlineStr"/>
-      <c r="E441" s="4" t="inlineStr"/>
-      <c r="F441" s="4" t="inlineStr"/>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -9180,9 +9060,9 @@
         </is>
       </c>
       <c r="C442" t="inlineStr"/>
-      <c r="D442" s="4" t="inlineStr"/>
-      <c r="E442" s="4" t="inlineStr"/>
-      <c r="F442" s="4" t="inlineStr"/>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -9196,9 +9076,9 @@
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
-      <c r="D443" s="4" t="inlineStr"/>
-      <c r="E443" s="4" t="inlineStr"/>
-      <c r="F443" s="4" t="inlineStr"/>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -9212,9 +9092,9 @@
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
-      <c r="D444" s="4" t="inlineStr"/>
-      <c r="E444" s="4" t="inlineStr"/>
-      <c r="F444" s="4" t="inlineStr"/>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -9228,9 +9108,9 @@
         </is>
       </c>
       <c r="C445" t="inlineStr"/>
-      <c r="D445" s="4" t="inlineStr"/>
-      <c r="E445" s="4" t="inlineStr"/>
-      <c r="F445" s="4" t="inlineStr"/>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -9244,9 +9124,9 @@
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" s="4" t="inlineStr"/>
-      <c r="E446" s="4" t="inlineStr"/>
-      <c r="F446" s="4" t="inlineStr"/>
+      <c r="D446" t="inlineStr"/>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -9260,9 +9140,9 @@
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" s="4" t="inlineStr"/>
-      <c r="E447" s="4" t="inlineStr"/>
-      <c r="F447" s="4" t="inlineStr"/>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -9276,9 +9156,9 @@
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" s="4" t="inlineStr"/>
-      <c r="E448" s="4" t="inlineStr"/>
-      <c r="F448" s="4" t="inlineStr"/>
+      <c r="D448" t="inlineStr"/>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -9292,9 +9172,9 @@
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" s="4" t="inlineStr"/>
-      <c r="E449" s="4" t="inlineStr"/>
-      <c r="F449" s="4" t="inlineStr"/>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -9308,9 +9188,9 @@
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" s="4" t="inlineStr"/>
-      <c r="E450" s="4" t="inlineStr"/>
-      <c r="F450" s="4" t="inlineStr"/>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -9324,9 +9204,9 @@
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" s="4" t="inlineStr"/>
-      <c r="E451" s="4" t="inlineStr"/>
-      <c r="F451" s="4" t="inlineStr"/>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -9340,9 +9220,9 @@
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" s="4" t="inlineStr"/>
-      <c r="E452" s="4" t="inlineStr"/>
-      <c r="F452" s="4" t="inlineStr"/>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -9356,9 +9236,9 @@
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" s="4" t="inlineStr"/>
-      <c r="E453" s="4" t="inlineStr"/>
-      <c r="F453" s="4" t="inlineStr"/>
+      <c r="D453" t="inlineStr"/>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -9372,9 +9252,9 @@
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" s="4" t="inlineStr"/>
-      <c r="E454" s="4" t="inlineStr"/>
-      <c r="F454" s="4" t="inlineStr"/>
+      <c r="D454" t="inlineStr"/>
+      <c r="E454" t="inlineStr"/>
+      <c r="F454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -9388,9 +9268,9 @@
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" s="4" t="inlineStr"/>
-      <c r="E455" s="4" t="inlineStr"/>
-      <c r="F455" s="4" t="inlineStr"/>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" t="inlineStr"/>
+      <c r="F455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -9404,9 +9284,9 @@
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" s="4" t="inlineStr"/>
-      <c r="E456" s="4" t="inlineStr"/>
-      <c r="F456" s="4" t="inlineStr"/>
+      <c r="D456" t="inlineStr"/>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -9420,9 +9300,9 @@
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
-      <c r="D457" s="4" t="inlineStr"/>
-      <c r="E457" s="4" t="inlineStr"/>
-      <c r="F457" s="4" t="inlineStr"/>
+      <c r="D457" t="inlineStr"/>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -9436,9 +9316,9 @@
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" s="4" t="inlineStr"/>
-      <c r="E458" s="4" t="inlineStr"/>
-      <c r="F458" s="4" t="inlineStr"/>
+      <c r="D458" t="inlineStr"/>
+      <c r="E458" t="inlineStr"/>
+      <c r="F458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -9452,9 +9332,9 @@
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" s="4" t="inlineStr"/>
-      <c r="E459" s="4" t="inlineStr"/>
-      <c r="F459" s="4" t="inlineStr"/>
+      <c r="D459" t="inlineStr"/>
+      <c r="E459" t="inlineStr"/>
+      <c r="F459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -9468,9 +9348,9 @@
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
-      <c r="D460" s="4" t="inlineStr"/>
-      <c r="E460" s="4" t="inlineStr"/>
-      <c r="F460" s="4" t="inlineStr"/>
+      <c r="D460" t="inlineStr"/>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -9484,9 +9364,9 @@
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
-      <c r="D461" s="4" t="inlineStr"/>
-      <c r="E461" s="4" t="inlineStr"/>
-      <c r="F461" s="4" t="inlineStr"/>
+      <c r="D461" t="inlineStr"/>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -9500,9 +9380,9 @@
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
-      <c r="D462" s="4" t="inlineStr"/>
-      <c r="E462" s="4" t="inlineStr"/>
-      <c r="F462" s="4" t="inlineStr"/>
+      <c r="D462" t="inlineStr"/>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -9516,9 +9396,9 @@
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
-      <c r="D463" s="4" t="inlineStr"/>
-      <c r="E463" s="4" t="inlineStr"/>
-      <c r="F463" s="4" t="inlineStr"/>
+      <c r="D463" t="inlineStr"/>
+      <c r="E463" t="inlineStr"/>
+      <c r="F463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -9532,9 +9412,9 @@
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
-      <c r="D464" s="4" t="inlineStr"/>
-      <c r="E464" s="4" t="inlineStr"/>
-      <c r="F464" s="4" t="inlineStr"/>
+      <c r="D464" t="inlineStr"/>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -9548,9 +9428,9 @@
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
-      <c r="D465" s="4" t="inlineStr"/>
-      <c r="E465" s="4" t="inlineStr"/>
-      <c r="F465" s="4" t="inlineStr"/>
+      <c r="D465" t="inlineStr"/>
+      <c r="E465" t="inlineStr"/>
+      <c r="F465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -9564,9 +9444,9 @@
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
-      <c r="D466" s="4" t="inlineStr"/>
-      <c r="E466" s="4" t="inlineStr"/>
-      <c r="F466" s="4" t="inlineStr"/>
+      <c r="D466" t="inlineStr"/>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -9580,13 +9460,13 @@
         </is>
       </c>
       <c r="C467" t="inlineStr"/>
-      <c r="D467" s="4" t="inlineStr"/>
-      <c r="E467" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F467" s="2" t="inlineStr">
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -9604,9 +9484,9 @@
         </is>
       </c>
       <c r="C468" t="inlineStr"/>
-      <c r="D468" s="4" t="inlineStr"/>
-      <c r="E468" s="4" t="inlineStr"/>
-      <c r="F468" s="4" t="inlineStr"/>
+      <c r="D468" t="inlineStr"/>
+      <c r="E468" t="inlineStr"/>
+      <c r="F468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -9620,9 +9500,9 @@
         </is>
       </c>
       <c r="C469" t="inlineStr"/>
-      <c r="D469" s="4" t="inlineStr"/>
-      <c r="E469" s="4" t="inlineStr"/>
-      <c r="F469" s="4" t="inlineStr"/>
+      <c r="D469" t="inlineStr"/>
+      <c r="E469" t="inlineStr"/>
+      <c r="F469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -9636,9 +9516,9 @@
         </is>
       </c>
       <c r="C470" t="inlineStr"/>
-      <c r="D470" s="4" t="inlineStr"/>
-      <c r="E470" s="4" t="inlineStr"/>
-      <c r="F470" s="4" t="inlineStr"/>
+      <c r="D470" t="inlineStr"/>
+      <c r="E470" t="inlineStr"/>
+      <c r="F470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -9652,9 +9532,9 @@
         </is>
       </c>
       <c r="C471" t="inlineStr"/>
-      <c r="D471" s="4" t="inlineStr"/>
-      <c r="E471" s="4" t="inlineStr"/>
-      <c r="F471" s="4" t="inlineStr"/>
+      <c r="D471" t="inlineStr"/>
+      <c r="E471" t="inlineStr"/>
+      <c r="F471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -9668,9 +9548,9 @@
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" s="4" t="inlineStr"/>
-      <c r="E472" s="4" t="inlineStr"/>
-      <c r="F472" s="4" t="inlineStr"/>
+      <c r="D472" t="inlineStr"/>
+      <c r="E472" t="inlineStr"/>
+      <c r="F472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -9684,9 +9564,9 @@
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" s="4" t="inlineStr"/>
-      <c r="E473" s="4" t="inlineStr"/>
-      <c r="F473" s="4" t="inlineStr"/>
+      <c r="D473" t="inlineStr"/>
+      <c r="E473" t="inlineStr"/>
+      <c r="F473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -9700,9 +9580,9 @@
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" s="4" t="inlineStr"/>
-      <c r="E474" s="4" t="inlineStr"/>
-      <c r="F474" s="4" t="inlineStr"/>
+      <c r="D474" t="inlineStr"/>
+      <c r="E474" t="inlineStr"/>
+      <c r="F474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -9716,9 +9596,9 @@
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" s="4" t="inlineStr"/>
-      <c r="E475" s="4" t="inlineStr"/>
-      <c r="F475" s="4" t="inlineStr"/>
+      <c r="D475" t="inlineStr"/>
+      <c r="E475" t="inlineStr"/>
+      <c r="F475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -9732,9 +9612,9 @@
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" s="4" t="inlineStr"/>
-      <c r="E476" s="4" t="inlineStr"/>
-      <c r="F476" s="4" t="inlineStr"/>
+      <c r="D476" t="inlineStr"/>
+      <c r="E476" t="inlineStr"/>
+      <c r="F476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -9748,9 +9628,9 @@
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" s="4" t="inlineStr"/>
-      <c r="E477" s="4" t="inlineStr"/>
-      <c r="F477" s="4" t="inlineStr"/>
+      <c r="D477" t="inlineStr"/>
+      <c r="E477" t="inlineStr"/>
+      <c r="F477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -9764,9 +9644,9 @@
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" s="4" t="inlineStr"/>
-      <c r="E478" s="4" t="inlineStr"/>
-      <c r="F478" s="4" t="inlineStr"/>
+      <c r="D478" t="inlineStr"/>
+      <c r="E478" t="inlineStr"/>
+      <c r="F478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -9780,9 +9660,9 @@
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" s="4" t="inlineStr"/>
-      <c r="E479" s="4" t="inlineStr"/>
-      <c r="F479" s="4" t="inlineStr"/>
+      <c r="D479" t="inlineStr"/>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -9796,9 +9676,9 @@
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" s="4" t="inlineStr"/>
-      <c r="E480" s="4" t="inlineStr"/>
-      <c r="F480" s="4" t="inlineStr"/>
+      <c r="D480" t="inlineStr"/>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -9812,17 +9692,17 @@
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E481" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F481" s="2" t="inlineStr">
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -9840,9 +9720,9 @@
         </is>
       </c>
       <c r="C482" t="inlineStr"/>
-      <c r="D482" s="4" t="inlineStr"/>
-      <c r="E482" s="4" t="inlineStr"/>
-      <c r="F482" s="4" t="inlineStr"/>
+      <c r="D482" t="inlineStr"/>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -9856,9 +9736,9 @@
         </is>
       </c>
       <c r="C483" t="inlineStr"/>
-      <c r="D483" s="4" t="inlineStr"/>
-      <c r="E483" s="4" t="inlineStr"/>
-      <c r="F483" s="4" t="inlineStr"/>
+      <c r="D483" t="inlineStr"/>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -9872,9 +9752,9 @@
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
-      <c r="D484" s="4" t="inlineStr"/>
-      <c r="E484" s="4" t="inlineStr"/>
-      <c r="F484" s="4" t="inlineStr"/>
+      <c r="D484" t="inlineStr"/>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -9888,9 +9768,9 @@
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
-      <c r="D485" s="4" t="inlineStr"/>
-      <c r="E485" s="4" t="inlineStr"/>
-      <c r="F485" s="4" t="inlineStr"/>
+      <c r="D485" t="inlineStr"/>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -9904,17 +9784,17 @@
         </is>
       </c>
       <c r="C486" t="inlineStr"/>
-      <c r="D486" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E486" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F486" s="2" t="inlineStr">
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -9932,9 +9812,9 @@
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
-      <c r="D487" s="4" t="inlineStr"/>
-      <c r="E487" s="4" t="inlineStr"/>
-      <c r="F487" s="4" t="inlineStr"/>
+      <c r="D487" t="inlineStr"/>
+      <c r="E487" t="inlineStr"/>
+      <c r="F487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -9948,9 +9828,9 @@
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
-      <c r="D488" s="4" t="inlineStr"/>
-      <c r="E488" s="4" t="inlineStr"/>
-      <c r="F488" s="4" t="inlineStr"/>
+      <c r="D488" t="inlineStr"/>
+      <c r="E488" t="inlineStr"/>
+      <c r="F488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -9964,9 +9844,9 @@
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
-      <c r="D489" s="4" t="inlineStr"/>
-      <c r="E489" s="4" t="inlineStr"/>
-      <c r="F489" s="4" t="inlineStr"/>
+      <c r="D489" t="inlineStr"/>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -9980,9 +9860,9 @@
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" s="4" t="inlineStr"/>
-      <c r="E490" s="4" t="inlineStr"/>
-      <c r="F490" s="4" t="inlineStr"/>
+      <c r="D490" t="inlineStr"/>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -9996,9 +9876,21 @@
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" s="4" t="inlineStr"/>
-      <c r="E491" s="4" t="inlineStr"/>
-      <c r="F491" s="4" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -10012,9 +9904,9 @@
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" s="4" t="inlineStr"/>
-      <c r="E492" s="4" t="inlineStr"/>
-      <c r="F492" s="4" t="inlineStr"/>
+      <c r="D492" t="inlineStr"/>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -10028,9 +9920,9 @@
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" s="4" t="inlineStr"/>
-      <c r="E493" s="4" t="inlineStr"/>
-      <c r="F493" s="4" t="inlineStr"/>
+      <c r="D493" t="inlineStr"/>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -10044,17 +9936,17 @@
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
-      <c r="D494" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E494" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="F494" s="2" t="inlineStr">
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10072,9 +9964,9 @@
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" s="4" t="inlineStr"/>
-      <c r="E495" s="4" t="inlineStr"/>
-      <c r="F495" s="4" t="inlineStr"/>
+      <c r="D495" t="inlineStr"/>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -10088,9 +9980,9 @@
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" s="4" t="inlineStr"/>
-      <c r="E496" s="4" t="inlineStr"/>
-      <c r="F496" s="4" t="inlineStr"/>
+      <c r="D496" t="inlineStr"/>
+      <c r="E496" t="inlineStr"/>
+      <c r="F496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -10104,9 +9996,9 @@
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
-      <c r="D497" s="4" t="inlineStr"/>
-      <c r="E497" s="4" t="inlineStr"/>
-      <c r="F497" s="4" t="inlineStr"/>
+      <c r="D497" t="inlineStr"/>
+      <c r="E497" t="inlineStr"/>
+      <c r="F497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -10120,9 +10012,9 @@
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
-      <c r="D498" s="4" t="inlineStr"/>
-      <c r="E498" s="4" t="inlineStr"/>
-      <c r="F498" s="4" t="inlineStr"/>
+      <c r="D498" t="inlineStr"/>
+      <c r="E498" t="inlineStr"/>
+      <c r="F498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -10136,9 +10028,9 @@
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" s="4" t="inlineStr"/>
-      <c r="E499" s="4" t="inlineStr"/>
-      <c r="F499" s="4" t="inlineStr"/>
+      <c r="D499" t="inlineStr"/>
+      <c r="E499" t="inlineStr"/>
+      <c r="F499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -10152,9 +10044,9 @@
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" s="4" t="inlineStr"/>
-      <c r="E500" s="4" t="inlineStr"/>
-      <c r="F500" s="4" t="inlineStr"/>
+      <c r="D500" t="inlineStr"/>
+      <c r="E500" t="inlineStr"/>
+      <c r="F500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -10168,9 +10060,9 @@
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" s="4" t="inlineStr"/>
-      <c r="E501" s="4" t="inlineStr"/>
-      <c r="F501" s="4" t="inlineStr"/>
+      <c r="D501" t="inlineStr"/>
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -10184,9 +10076,9 @@
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" s="4" t="inlineStr"/>
-      <c r="E502" s="4" t="inlineStr"/>
-      <c r="F502" s="4" t="inlineStr"/>
+      <c r="D502" t="inlineStr"/>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -10200,9 +10092,9 @@
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" s="4" t="inlineStr"/>
-      <c r="E503" s="4" t="inlineStr"/>
-      <c r="F503" s="4" t="inlineStr"/>
+      <c r="D503" t="inlineStr"/>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -10216,9 +10108,9 @@
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
-      <c r="D504" s="4" t="inlineStr"/>
-      <c r="E504" s="4" t="inlineStr"/>
-      <c r="F504" s="4" t="inlineStr"/>
+      <c r="D504" t="inlineStr"/>
+      <c r="E504" t="inlineStr"/>
+      <c r="F504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -10232,9 +10124,9 @@
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" s="4" t="inlineStr"/>
-      <c r="E505" s="4" t="inlineStr"/>
-      <c r="F505" s="4" t="inlineStr"/>
+      <c r="D505" t="inlineStr"/>
+      <c r="E505" t="inlineStr"/>
+      <c r="F505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -10248,9 +10140,9 @@
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
-      <c r="D506" s="4" t="inlineStr"/>
-      <c r="E506" s="4" t="inlineStr"/>
-      <c r="F506" s="4" t="inlineStr"/>
+      <c r="D506" t="inlineStr"/>
+      <c r="E506" t="inlineStr"/>
+      <c r="F506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -10264,9 +10156,9 @@
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
-      <c r="D507" s="4" t="inlineStr"/>
-      <c r="E507" s="4" t="inlineStr"/>
-      <c r="F507" s="4" t="inlineStr"/>
+      <c r="D507" t="inlineStr"/>
+      <c r="E507" t="inlineStr"/>
+      <c r="F507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -10280,17 +10172,17 @@
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
-      <c r="D508" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="E508" s="2" t="inlineStr">
-        <is>
-          <t>已提交</t>
-        </is>
-      </c>
-      <c r="F508" s="2" t="inlineStr">
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -10308,9 +10200,9 @@
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" s="4" t="inlineStr"/>
-      <c r="E509" s="4" t="inlineStr"/>
-      <c r="F509" s="4" t="inlineStr"/>
+      <c r="D509" t="inlineStr"/>
+      <c r="E509" t="inlineStr"/>
+      <c r="F509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -10324,9 +10216,9 @@
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
-      <c r="D510" s="4" t="inlineStr"/>
-      <c r="E510" s="4" t="inlineStr"/>
-      <c r="F510" s="4" t="inlineStr"/>
+      <c r="D510" t="inlineStr"/>
+      <c r="E510" t="inlineStr"/>
+      <c r="F510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -10340,13 +10232,13 @@
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E511" s="4" t="inlineStr"/>
-      <c r="F511" s="4" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr"/>
+      <c r="F511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -10360,9 +10252,9 @@
         </is>
       </c>
       <c r="C512" t="inlineStr"/>
-      <c r="D512" s="4" t="inlineStr"/>
-      <c r="E512" s="4" t="inlineStr"/>
-      <c r="F512" s="4" t="inlineStr"/>
+      <c r="D512" t="inlineStr"/>
+      <c r="E512" t="inlineStr"/>
+      <c r="F512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -10376,13 +10268,13 @@
         </is>
       </c>
       <c r="C513" t="inlineStr"/>
-      <c r="D513" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E513" s="4" t="inlineStr"/>
-      <c r="F513" s="4" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr"/>
+      <c r="F513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -10396,9 +10288,9 @@
         </is>
       </c>
       <c r="C514" t="inlineStr"/>
-      <c r="D514" s="4" t="inlineStr"/>
-      <c r="E514" s="4" t="inlineStr"/>
-      <c r="F514" s="4" t="inlineStr"/>
+      <c r="D514" t="inlineStr"/>
+      <c r="E514" t="inlineStr"/>
+      <c r="F514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -10412,9 +10304,9 @@
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
-      <c r="D515" s="4" t="inlineStr"/>
-      <c r="E515" s="4" t="inlineStr"/>
-      <c r="F515" s="4" t="inlineStr"/>
+      <c r="D515" t="inlineStr"/>
+      <c r="E515" t="inlineStr"/>
+      <c r="F515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -10428,17 +10320,17 @@
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
-      <c r="D516" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E516" s="3" t="inlineStr">
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
         <is>
           <t>需付费</t>
         </is>
       </c>
-      <c r="F516" s="4" t="inlineStr"/>
+      <c r="F516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -10452,9 +10344,9 @@
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
-      <c r="D517" s="4" t="inlineStr"/>
-      <c r="E517" s="4" t="inlineStr"/>
-      <c r="F517" s="4" t="inlineStr"/>
+      <c r="D517" t="inlineStr"/>
+      <c r="E517" t="inlineStr"/>
+      <c r="F517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -10468,13 +10360,13 @@
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
-      <c r="D518" s="4" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E518" s="4" t="inlineStr"/>
-      <c r="F518" s="4" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -10488,9 +10380,9 @@
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
-      <c r="D519" s="4" t="inlineStr"/>
-      <c r="E519" s="4" t="inlineStr"/>
-      <c r="F519" s="4" t="inlineStr"/>
+      <c r="D519" t="inlineStr"/>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -10504,9 +10396,9 @@
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
-      <c r="D520" s="4" t="inlineStr"/>
-      <c r="E520" s="4" t="inlineStr"/>
-      <c r="F520" s="4" t="inlineStr"/>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -10520,9 +10412,9 @@
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
-      <c r="D521" s="4" t="inlineStr"/>
-      <c r="E521" s="4" t="inlineStr"/>
-      <c r="F521" s="4" t="inlineStr"/>
+      <c r="D521" t="inlineStr"/>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -10536,9 +10428,9 @@
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
-      <c r="D522" s="4" t="inlineStr"/>
-      <c r="E522" s="4" t="inlineStr"/>
-      <c r="F522" s="4" t="inlineStr"/>
+      <c r="D522" t="inlineStr"/>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -10552,9 +10444,9 @@
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
-      <c r="D523" s="4" t="inlineStr"/>
-      <c r="E523" s="4" t="inlineStr"/>
-      <c r="F523" s="4" t="inlineStr"/>
+      <c r="D523" t="inlineStr"/>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backlinks.xlsx
+++ b/backlinks.xlsx
@@ -1180,7 +1180,11 @@
           <t>91</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
     </row>
@@ -1304,9 +1308,21 @@
           <t>90</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1541,7 +1557,11 @@
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1684,7 +1704,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
     </row>
@@ -1704,7 +1728,11 @@
           <t>80</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
     </row>
@@ -1882,7 +1910,11 @@
       </c>
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1900,7 +1932,11 @@
           <t>79</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
     </row>
@@ -1921,7 +1957,11 @@
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
@@ -2090,7 +2130,11 @@
       </c>
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2201,7 +2245,11 @@
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
@@ -2221,7 +2269,11 @@
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="F77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
@@ -2240,7 +2292,11 @@
           <t>75</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr"/>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
     </row>
@@ -2440,9 +2496,21 @@
           <t>74</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr"/>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2460,9 +2528,17 @@
           <t>74</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr"/>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2480,7 +2556,11 @@
           <t>74</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr"/>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
     </row>
@@ -2502,7 +2582,11 @@
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2520,7 +2604,11 @@
           <t>74</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr"/>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
     </row>
@@ -2540,7 +2628,11 @@
           <t>74</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
     </row>
@@ -2561,7 +2653,11 @@
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="F91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
@@ -2740,7 +2836,11 @@
           <t>73</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
     </row>
@@ -3138,7 +3238,11 @@
           <t>已提交</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3261,7 +3365,11 @@
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
-      <c r="E118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
@@ -3333,7 +3441,11 @@
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
-      <c r="E121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
@@ -3352,9 +3464,17 @@
           <t>67</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr"/>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E122" s="2" t="inlineStr"/>
-      <c r="F122" s="2" t="inlineStr"/>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3496,9 +3616,17 @@
           <t>65</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr"/>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3889,7 +4017,11 @@
           <t>已提交</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr"/>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="F143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
@@ -3908,7 +4040,11 @@
           <t>62</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr"/>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr"/>
     </row>
@@ -4002,7 +4138,11 @@
       </c>
       <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="2" t="inlineStr"/>
-      <c r="F148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4020,7 +4160,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr"/>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
     </row>
@@ -4064,7 +4208,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr"/>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr"/>
     </row>
@@ -4086,7 +4234,11 @@
       </c>
       <c r="D152" s="2" t="inlineStr"/>
       <c r="E152" s="2" t="inlineStr"/>
-      <c r="F152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4104,7 +4256,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr"/>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
     </row>
@@ -4396,7 +4552,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr"/>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" s="2" t="inlineStr"/>
     </row>
@@ -4508,7 +4668,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr"/>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr"/>
     </row>
@@ -4606,7 +4770,11 @@
       </c>
       <c r="D174" s="2" t="inlineStr"/>
       <c r="E174" s="2" t="inlineStr"/>
-      <c r="F174" s="2" t="inlineStr"/>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4766,7 +4934,11 @@
           <t>已提交</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr"/>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4916,7 +5088,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr"/>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr"/>
     </row>
@@ -4938,7 +5114,11 @@
       </c>
       <c r="D188" s="2" t="inlineStr"/>
       <c r="E188" s="2" t="inlineStr"/>
-      <c r="F188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4958,7 +5138,11 @@
       </c>
       <c r="D189" s="2" t="inlineStr"/>
       <c r="E189" s="2" t="inlineStr"/>
-      <c r="F189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5180,7 +5364,11 @@
           <t>54</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr"/>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E197" s="2" t="inlineStr"/>
       <c r="F197" s="2" t="inlineStr"/>
     </row>
@@ -5272,7 +5460,11 @@
           <t>53</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr"/>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E201" s="2" t="inlineStr"/>
       <c r="F201" s="2" t="inlineStr"/>
     </row>
@@ -5509,7 +5701,11 @@
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr"/>
-      <c r="E211" s="2" t="inlineStr"/>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
@@ -5702,7 +5898,11 @@
       </c>
       <c r="D218" s="2" t="inlineStr"/>
       <c r="E218" s="2" t="inlineStr"/>
-      <c r="F218" s="2" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5722,7 +5922,11 @@
       </c>
       <c r="D219" s="2" t="inlineStr"/>
       <c r="E219" s="2" t="inlineStr"/>
-      <c r="F219" s="2" t="inlineStr"/>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5740,7 +5944,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr"/>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E220" s="2" t="inlineStr"/>
       <c r="F220" s="2" t="inlineStr"/>
     </row>
@@ -5801,7 +6009,11 @@
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr"/>
-      <c r="E223" s="2" t="inlineStr"/>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
@@ -5820,7 +6032,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr"/>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E224" s="2" t="inlineStr"/>
       <c r="F224" s="2" t="inlineStr"/>
     </row>
@@ -5881,7 +6097,11 @@
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr"/>
-      <c r="E227" s="2" t="inlineStr"/>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
@@ -5902,7 +6122,11 @@
       </c>
       <c r="D228" s="2" t="inlineStr"/>
       <c r="E228" s="2" t="inlineStr"/>
-      <c r="F228" s="2" t="inlineStr"/>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6064,7 +6288,11 @@
           <t>48</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr"/>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E235" s="2" t="inlineStr"/>
       <c r="F235" s="2" t="inlineStr"/>
     </row>
@@ -6224,9 +6452,17 @@
           <t>47</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr"/>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E241" s="2" t="inlineStr"/>
-      <c r="F241" s="2" t="inlineStr"/>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6340,8 +6576,16 @@
           <t>45</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr"/>
-      <c r="E246" s="2" t="inlineStr"/>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
@@ -6364,7 +6608,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr"/>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E247" s="2" t="inlineStr"/>
       <c r="F247" s="2" t="inlineStr"/>
     </row>
@@ -6468,7 +6716,11 @@
           <t>44</t>
         </is>
       </c>
-      <c r="D251" s="2" t="inlineStr"/>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E251" s="2" t="inlineStr"/>
       <c r="F251" s="3" t="inlineStr">
         <is>
@@ -6492,8 +6744,16 @@
           <t>44</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr"/>
-      <c r="E252" s="2" t="inlineStr"/>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
@@ -6516,7 +6776,11 @@
           <t>44</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr"/>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E253" s="2" t="inlineStr"/>
       <c r="F253" s="3" t="inlineStr">
         <is>
@@ -6700,7 +6964,11 @@
           <t>43</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr"/>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E260" s="2" t="inlineStr"/>
       <c r="F260" s="2" t="inlineStr"/>
     </row>
@@ -6752,7 +7020,11 @@
           <t>43</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr"/>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E262" s="2" t="inlineStr"/>
       <c r="F262" s="3" t="inlineStr">
         <is>
@@ -6860,7 +7132,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="D266" s="2" t="inlineStr"/>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E266" s="2" t="inlineStr"/>
       <c r="F266" s="2" t="inlineStr"/>
     </row>
@@ -6880,7 +7156,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="D267" s="2" t="inlineStr"/>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E267" s="2" t="inlineStr"/>
       <c r="F267" s="2" t="inlineStr"/>
     </row>
@@ -6900,7 +7180,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr"/>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E268" s="2" t="inlineStr"/>
       <c r="F268" s="2" t="inlineStr"/>
     </row>
@@ -6921,7 +7205,11 @@
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr"/>
-      <c r="E269" s="2" t="inlineStr"/>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F269" s="2" t="inlineStr"/>
     </row>
     <row r="270">
@@ -7065,7 +7353,11 @@
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr"/>
-      <c r="E275" s="2" t="inlineStr"/>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F275" s="2" t="inlineStr"/>
     </row>
     <row r="276">
@@ -7337,7 +7629,11 @@
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr"/>
-      <c r="E285" s="2" t="inlineStr"/>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F285" s="2" t="inlineStr"/>
     </row>
     <row r="286">
@@ -7356,7 +7652,11 @@
           <t>39</t>
         </is>
       </c>
-      <c r="D286" s="2" t="inlineStr"/>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E286" s="2" t="inlineStr"/>
       <c r="F286" s="2" t="inlineStr"/>
     </row>
@@ -7378,7 +7678,11 @@
       </c>
       <c r="D287" s="2" t="inlineStr"/>
       <c r="E287" s="2" t="inlineStr"/>
-      <c r="F287" s="2" t="inlineStr"/>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -7612,7 +7916,11 @@
           <t>38</t>
         </is>
       </c>
-      <c r="D297" s="2" t="inlineStr"/>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E297" s="2" t="inlineStr"/>
       <c r="F297" s="2" t="inlineStr"/>
     </row>
@@ -7637,7 +7945,11 @@
           <t>已提交</t>
         </is>
       </c>
-      <c r="E298" s="2" t="inlineStr"/>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
           <t>已提交</t>
@@ -7932,8 +8244,16 @@
           <t>36</t>
         </is>
       </c>
-      <c r="D309" s="2" t="inlineStr"/>
-      <c r="E309" s="2" t="inlineStr"/>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="F309" s="2" t="inlineStr"/>
     </row>
     <row r="310">
@@ -7978,7 +8298,11 @@
       </c>
       <c r="D311" s="2" t="inlineStr"/>
       <c r="E311" s="2" t="inlineStr"/>
-      <c r="F311" s="2" t="inlineStr"/>
+      <c r="F311" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -8198,7 +8522,11 @@
           <t>已提交</t>
         </is>
       </c>
-      <c r="F320" s="2" t="inlineStr"/>
+      <c r="F320" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -8217,7 +8545,11 @@
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr"/>
-      <c r="E321" s="2" t="inlineStr"/>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="F321" s="2" t="inlineStr"/>
     </row>
     <row r="322">
@@ -8474,7 +8806,11 @@
       </c>
       <c r="D332" s="2" t="inlineStr"/>
       <c r="E332" s="2" t="inlineStr"/>
-      <c r="F332" s="2" t="inlineStr"/>
+      <c r="F332" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -9164,7 +9500,11 @@
           <t>29</t>
         </is>
       </c>
-      <c r="D361" s="2" t="inlineStr"/>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E361" s="2" t="inlineStr"/>
       <c r="F361" s="2" t="inlineStr"/>
     </row>
@@ -9325,7 +9665,11 @@
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr"/>
-      <c r="E368" s="2" t="inlineStr"/>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="F368" s="2" t="inlineStr"/>
     </row>
     <row r="369">
@@ -9462,7 +9806,11 @@
       </c>
       <c r="D374" s="2" t="inlineStr"/>
       <c r="E374" s="2" t="inlineStr"/>
-      <c r="F374" s="2" t="inlineStr"/>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -9792,9 +10140,21 @@
           <t>24</t>
         </is>
       </c>
-      <c r="D389" s="2" t="inlineStr"/>
-      <c r="E389" s="2" t="inlineStr"/>
-      <c r="F389" s="2" t="inlineStr"/>
+      <c r="D389" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E389" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F389" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -10276,7 +10636,11 @@
           <t>18</t>
         </is>
       </c>
-      <c r="D411" s="2" t="inlineStr"/>
+      <c r="D411" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
       <c r="E411" s="2" t="inlineStr"/>
       <c r="F411" s="2" t="inlineStr"/>
     </row>
@@ -10692,9 +11056,21 @@
           <t>14</t>
         </is>
       </c>
-      <c r="D428" s="2" t="inlineStr"/>
-      <c r="E428" s="2" t="inlineStr"/>
-      <c r="F428" s="2" t="inlineStr"/>
+      <c r="D428" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="E428" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="F428" s="3" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -12660,7 +13036,11 @@
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
-      <c r="D521" s="2" t="inlineStr"/>
+      <c r="D521" s="2" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="E521" s="2" t="inlineStr"/>
       <c r="F521" s="3" t="inlineStr">
         <is>
